--- a/docs/holdtiming/results/cell12_R2xYZxRSI.xlsx
+++ b/docs/holdtiming/results/cell12_R2xYZxRSI.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수익률_평균" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시대별_23-24_중앙" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시대별_25-26_중앙" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YZ상주_검증" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,12 +22,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -100,6 +102,18 @@
       <b val="1"/>
       <color rgb="FF1976D2"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="5">
@@ -209,7 +223,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -425,6 +439,36 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="10" fontId="9" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -808,7 +852,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성 2026-09-08 23:22 KST   ·   MagicFormula/scripts/cell12_report.py  (원자료: LLV core+extend parquet)</t>
+          <t>생성 2026-09-09 12:13 KST   ·   MagicFormula/scripts/cell12_report.py  (원자료: LLV core+extend parquet)</t>
         </is>
       </c>
     </row>
@@ -906,7 +950,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (평균으로 재면 기준선이 +0.12% 로 거의 0 인 것이 같은 사실의 뒷면이다 — 평균 종목 ≈ BM, 중앙 종목 &lt; BM).</t>
+          <t xml:space="preserve">   (평균으로 재면 기준선이 +0.10% 로 거의 0 인 것이 같은 사실의 뒷면이다 — 평균 종목 ≈ BM, 중앙 종목 &lt; BM).</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1048,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ◎ YZ低·과매수 2셀 전부 음(−) : R²高 Δ중앙 -1.8%p / R²低 Δ중앙 -2.1%p 이고 **창이 길어질수록 나빠진다**(120일 -8.3%p / -11.6%p).</t>
+          <t xml:space="preserve">   ◎ YZ低·과매수 2셀 전부 음(−) : R²高 Δ중앙 -1.8%p / R²低 Δ중앙 -2.1%p 이고 **창이 길어질수록 나빠진다**(120일 -8.2%p / -11.6%p).</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1062,7 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ○ R²低·YZ高·중간 : Δ가 양쪽 다 양수이고 창이 길수록 커진다(20일 +0.2%/+1.5%p → 120일 +1.8%/+8.4%p). 표본도 35,479건으로 크다.</t>
+          <t xml:space="preserve">   ○ R²低·YZ高·중간 : Δ가 양쪽 다 양수이고 창이 길수록 커진다(20일 +0.2%/+1.5%p → 120일 +1.8%/+8.4%p). 표본도 35,532건으로 크다.</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1081,7 +1125,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>전 기간 유효 관측 167,002건 (종목×일)   ·   '상승비율' = 회귀 기울기 b&gt;0 인 비율</t>
+          <t>전 기간 유효 관측 167,208건 (종목×일)   ·   '상승비율' = 회귀 기울기 b&gt;0 인 비율</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1201,7 @@
         <v>1055</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.006317289613298045</v>
+        <v>0.006309506722166403</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>116</v>
@@ -1194,37 +1238,37 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>38938</v>
+        <v>38986</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>0.2331588843247386</v>
+        <v>0.233158700540644</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>190</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.6854776730686193</v>
+        <v>0.6853473965712442</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.04019817522284791</v>
+        <v>0.04022241071159036</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>51.68288931370442</v>
+        <v>51.67520591703067</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>0.0044494606335106</v>
+        <v>0.004443321984879348</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.6627202218912117</v>
+        <v>0.6619299235623044</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.2289778905400508</v>
+        <v>0.2283185840707964</v>
       </c>
       <c r="K6" s="8" t="n">
         <v>18943</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>19995</v>
+        <v>20043</v>
       </c>
     </row>
     <row r="7">
@@ -1237,7 +1281,7 @@
         <v>4506</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>0.02698171279385875</v>
+        <v>0.02694847136500646</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>165</v>
@@ -1277,7 +1321,7 @@
         <v>1401</v>
       </c>
       <c r="C8" s="27" t="n">
-        <v>0.008389121088370199</v>
+        <v>0.0083787857040333</v>
       </c>
       <c r="D8" s="26" t="n">
         <v>142</v>
@@ -1314,37 +1358,37 @@
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>35342</v>
+        <v>35397</v>
       </c>
       <c r="C9" s="27" t="n">
-        <v>0.2116262080693644</v>
+        <v>0.211694416535094</v>
       </c>
       <c r="D9" s="26" t="n">
         <v>186</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>0.6604190916817165</v>
+        <v>0.6602839430029476</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>0.02224773351494805</v>
+        <v>0.02225763840568366</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>48.93446246654259</v>
+        <v>48.93128115800169</v>
       </c>
       <c r="H9" s="30" t="n">
-        <v>-0.001537410274443924</v>
+        <v>-0.001538427534750311</v>
       </c>
       <c r="I9" s="31" t="n">
-        <v>0.4468620904306491</v>
+        <v>0.4468175269090601</v>
       </c>
       <c r="J9" s="32" t="n">
-        <v>-0.04347826086956519</v>
+        <v>-0.04357625845229152</v>
       </c>
       <c r="K9" s="26" t="n">
         <v>18608</v>
       </c>
       <c r="L9" s="26" t="n">
-        <v>16734</v>
+        <v>16789</v>
       </c>
     </row>
     <row r="10">
@@ -1357,7 +1401,7 @@
         <v>2401</v>
       </c>
       <c r="C10" s="35" t="n">
-        <v>0.01437707332846313</v>
+        <v>0.01435936079613416</v>
       </c>
       <c r="D10" s="34" t="n">
         <v>133</v>
@@ -1397,7 +1441,7 @@
         <v>824</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>0.004934072645836577</v>
+        <v>0.004927993875891106</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>133</v>
@@ -1434,37 +1478,37 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>35479</v>
+        <v>35532</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.2124465575262572</v>
+        <v>0.2125017941725276</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>191</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.1510473360830225</v>
+        <v>0.150926666391757</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0.03762341041594788</v>
+        <v>0.03764399886264937</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>49.28999350306504</v>
+        <v>49.2953888859128</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.0004794182415151984</v>
+        <v>0.000477295942012662</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0.5745652357732743</v>
+        <v>0.5740740740740741</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>0.04329896907216502</v>
+        <v>0.04298642533936659</v>
       </c>
       <c r="K12" s="8" t="n">
         <v>18720</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>16759</v>
+        <v>16812</v>
       </c>
     </row>
     <row r="13">
@@ -1474,37 +1518,37 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>2694</v>
+        <v>2696</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>0.01613154333481036</v>
+        <v>0.01612363044830391</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>161</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>0.1583365384864762</v>
+        <v>0.1581573914519595</v>
       </c>
       <c r="F13" s="20" t="n">
-        <v>0.03720024493325056</v>
+        <v>0.03720138411687211</v>
       </c>
       <c r="G13" s="21" t="n">
         <v>75.09198966447441</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>0.001774533062968874</v>
+        <v>0.001774005490129748</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>0.7765404602821084</v>
+        <v>0.7763353115727003</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.2914385440039891</v>
+        <v>0.2913835770528683</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1088</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>1606</v>
+        <v>1608</v>
       </c>
     </row>
     <row r="14">
@@ -1517,7 +1561,7 @@
         <v>878</v>
       </c>
       <c r="C14" s="27" t="n">
-        <v>0.005257422066801595</v>
+        <v>0.005250944930864552</v>
       </c>
       <c r="D14" s="26" t="n">
         <v>136</v>
@@ -1554,37 +1598,37 @@
         </is>
       </c>
       <c r="B15" s="26" t="n">
-        <v>41161</v>
+        <v>41209</v>
       </c>
       <c r="C15" s="27" t="n">
-        <v>0.2464701021544652</v>
+        <v>0.2464535189703842</v>
       </c>
       <c r="D15" s="26" t="n">
         <v>185</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>0.1403774344909657</v>
+        <v>0.1401760823943062</v>
       </c>
       <c r="F15" s="28" t="n">
-        <v>0.02226971321998654</v>
+        <v>0.02228088237773147</v>
       </c>
       <c r="G15" s="29" t="n">
-        <v>49.98630576255442</v>
+        <v>49.98616541935175</v>
       </c>
       <c r="H15" s="41" t="n">
-        <v>4.691584957742155e-05</v>
+        <v>4.644268798243801e-05</v>
       </c>
       <c r="I15" s="31" t="n">
-        <v>0.5159981535919924</v>
+        <v>0.5158581863185226</v>
       </c>
       <c r="J15" s="42" t="n">
-        <v>0.004103967168262557</v>
+        <v>0.004024144869215318</v>
       </c>
       <c r="K15" s="26" t="n">
         <v>19979</v>
       </c>
       <c r="L15" s="26" t="n">
-        <v>21182</v>
+        <v>21230</v>
       </c>
     </row>
     <row r="16">
@@ -1597,7 +1641,7 @@
         <v>2323</v>
       </c>
       <c r="C16" s="35" t="n">
-        <v>0.01391001305373588</v>
+        <v>0.01389287593895029</v>
       </c>
       <c r="D16" s="34" t="n">
         <v>158</v>
@@ -1658,7 +1702,7 @@
     <row r="22">
       <c r="A22" s="43" t="inlineStr">
         <is>
-          <t>④ R²低·YZ低·중간(41,161건, 24.6%)이 유일한 '진짜 횡보'다. 과거60일 +0.4%, 기울기 ≈0, 상승 52%. 시장의 기본값이 여기다.</t>
+          <t>④ R²低·YZ低·중간(41,209건, 24.6%)이 유일한 '진짜 횡보'다. 과거60일 +0.4%, 기울기 ≈0, 상승 52%. 시장의 기본값이 여기다.</t>
         </is>
       </c>
     </row>
@@ -1752,7 +1796,7 @@
         </is>
       </c>
       <c r="B29" s="45" t="n">
-        <v>167002</v>
+        <v>167208</v>
       </c>
       <c r="C29" s="46" t="n">
         <v>1</v>
@@ -1761,28 +1805,28 @@
         <v>206</v>
       </c>
       <c r="E29" s="47" t="n">
-        <v>0.4292591798322072</v>
+        <v>0.4290955901431661</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>0.02991350914651212</v>
+        <v>0.02993330568541613</v>
       </c>
       <c r="G29" s="48" t="n">
-        <v>50.70409205154468</v>
+        <v>50.70244436382978</v>
       </c>
       <c r="H29" s="49" t="n">
-        <v>0.0005570172608598785</v>
+        <v>0.0005544112241437126</v>
       </c>
       <c r="I29" s="50" t="n">
-        <v>0.5655201734110968</v>
+        <v>0.565164346203531</v>
       </c>
       <c r="J29" s="51" t="n">
-        <v>0.03924940213324724</v>
+        <v>0.03901524453431282</v>
       </c>
       <c r="K29" s="45" t="n">
         <v>83649</v>
       </c>
       <c r="L29" s="45" t="n">
-        <v>83353</v>
+        <v>83559</v>
       </c>
     </row>
     <row r="30">
@@ -1792,37 +1836,37 @@
         </is>
       </c>
       <c r="B30" s="26" t="n">
-        <v>83643</v>
+        <v>83746</v>
       </c>
       <c r="C30" s="27" t="n">
-        <v>0.5008502892180932</v>
+        <v>0.5008492416630783</v>
       </c>
       <c r="D30" s="26" t="n">
         <v>206</v>
       </c>
       <c r="E30" s="28" t="n">
-        <v>0.6778726039877105</v>
+        <v>0.6776731805068197</v>
       </c>
       <c r="F30" s="28" t="n">
-        <v>0.03082974282832589</v>
+        <v>0.03085119870346978</v>
       </c>
       <c r="G30" s="29" t="n">
-        <v>51.18075552999944</v>
+        <v>51.1700136579742</v>
       </c>
       <c r="H30" s="41" t="n">
-        <v>0.002368199033849468</v>
+        <v>0.002361685758504035</v>
       </c>
       <c r="I30" s="31" t="n">
-        <v>0.5790681826333345</v>
+        <v>0.5786425620328135</v>
       </c>
       <c r="J30" s="42" t="n">
-        <v>0.1039501039501038</v>
+        <v>0.1035447970501784</v>
       </c>
       <c r="K30" s="26" t="n">
         <v>41890</v>
       </c>
       <c r="L30" s="26" t="n">
-        <v>41753</v>
+        <v>41856</v>
       </c>
     </row>
     <row r="31">
@@ -1832,37 +1876,37 @@
         </is>
       </c>
       <c r="B31" s="34" t="n">
-        <v>83359</v>
+        <v>83462</v>
       </c>
       <c r="C31" s="35" t="n">
-        <v>0.4991497107819068</v>
+        <v>0.4991507583369217</v>
       </c>
       <c r="D31" s="34" t="n">
         <v>206</v>
       </c>
       <c r="E31" s="36" t="n">
-        <v>0.1461009894728824</v>
+        <v>0.1458729858544544</v>
       </c>
       <c r="F31" s="36" t="n">
-        <v>0.029077556106003</v>
+        <v>0.02909562809432063</v>
       </c>
       <c r="G31" s="37" t="n">
-        <v>50.25612249528858</v>
+        <v>50.25620197456221</v>
       </c>
       <c r="H31" s="38" t="n">
-        <v>0.0002156131606876075</v>
+        <v>0.0002140252645747704</v>
       </c>
       <c r="I31" s="39" t="n">
-        <v>0.5519260067899087</v>
+        <v>0.5516402674270926</v>
       </c>
       <c r="J31" s="40" t="n">
-        <v>0.02134831460674147</v>
+        <v>0.02123249588359422</v>
       </c>
       <c r="K31" s="34" t="n">
         <v>41759</v>
       </c>
       <c r="L31" s="34" t="n">
-        <v>41600</v>
+        <v>41703</v>
       </c>
     </row>
     <row r="32">
@@ -1872,37 +1916,37 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>83496</v>
+        <v>83599</v>
       </c>
       <c r="C32" s="9" t="n">
-        <v>0.4999700602387995</v>
+        <v>0.4999700971245395</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>192</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.4620515825019552</v>
+        <v>0.4617702038606974</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>0.03893388661934083</v>
+        <v>0.03895281353942246</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>51.57300817024614</v>
+        <v>51.56866724952538</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>0.001815031924222095</v>
+        <v>0.001806449415824785</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>0.6348088531187123</v>
+        <v>0.6342061507912774</v>
       </c>
       <c r="J32" s="16" t="n">
-        <v>0.1218592964824121</v>
+        <v>0.1214754408832146</v>
       </c>
       <c r="K32" s="8" t="n">
         <v>41825</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>41671</v>
+        <v>41774</v>
       </c>
     </row>
     <row r="33">
@@ -1912,37 +1956,37 @@
         </is>
       </c>
       <c r="B33" s="18" t="n">
-        <v>83506</v>
+        <v>83609</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.5000299397612005</v>
+        <v>0.5000299028754605</v>
       </c>
       <c r="D33" s="18" t="n">
         <v>191</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>0.3957937693552872</v>
+        <v>0.3957846265428563</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>0.02221382896825014</v>
+        <v>0.02222375393015153</v>
       </c>
       <c r="G33" s="21" t="n">
-        <v>49.90598753454936</v>
+        <v>49.90467226347825</v>
       </c>
       <c r="H33" s="52" t="n">
-        <v>-2.20691465958516e-05</v>
+        <v>-2.269681093346081e-05</v>
       </c>
       <c r="I33" s="23" t="n">
-        <v>0.4962397911527315</v>
+        <v>0.4961307993158631</v>
       </c>
       <c r="J33" s="24" t="n">
-        <v>0.001633319994664539</v>
+        <v>0.001529051987767538</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>41824</v>
       </c>
       <c r="L33" s="18" t="n">
-        <v>41682</v>
+        <v>41785</v>
       </c>
     </row>
     <row r="34">
@@ -1955,7 +1999,7 @@
         <v>4158</v>
       </c>
       <c r="C34" s="27" t="n">
-        <v>0.02489790541430642</v>
+        <v>0.02486723123295536</v>
       </c>
       <c r="D34" s="26" t="n">
         <v>205</v>
@@ -1992,37 +2036,37 @@
         </is>
       </c>
       <c r="B35" s="26" t="n">
-        <v>150920</v>
+        <v>151124</v>
       </c>
       <c r="C35" s="27" t="n">
-        <v>0.9037017520748255</v>
+        <v>0.9038084302186499</v>
       </c>
       <c r="D35" s="26" t="n">
         <v>206</v>
       </c>
       <c r="E35" s="28" t="n">
-        <v>0.4208388639543812</v>
+        <v>0.420749183708742</v>
       </c>
       <c r="F35" s="28" t="n">
-        <v>0.02982947769719136</v>
+        <v>0.02985090549276544</v>
       </c>
       <c r="G35" s="29" t="n">
-        <v>50.01809333525627</v>
+        <v>50.01613738950714</v>
       </c>
       <c r="H35" s="41" t="n">
-        <v>0.0004223083943298392</v>
+        <v>0.0004187842260105542</v>
       </c>
       <c r="I35" s="31" t="n">
-        <v>0.5514312218393851</v>
+        <v>0.5510574098091633</v>
       </c>
       <c r="J35" s="42" t="n">
-        <v>0.02851323828920571</v>
+        <v>0.02834467120181405</v>
       </c>
       <c r="K35" s="26" t="n">
         <v>76250</v>
       </c>
       <c r="L35" s="26" t="n">
-        <v>74670</v>
+        <v>74874</v>
       </c>
     </row>
     <row r="36">
@@ -2032,37 +2076,37 @@
         </is>
       </c>
       <c r="B36" s="34" t="n">
-        <v>11924</v>
+        <v>11926</v>
       </c>
       <c r="C36" s="35" t="n">
-        <v>0.07140034251086813</v>
+        <v>0.07132433854839482</v>
       </c>
       <c r="D36" s="34" t="n">
         <v>205</v>
       </c>
       <c r="E36" s="36" t="n">
-        <v>0.5085400921734744</v>
+        <v>0.5083502382874378</v>
       </c>
       <c r="F36" s="36" t="n">
-        <v>0.03289485755456206</v>
+        <v>0.03289911970543538</v>
       </c>
       <c r="G36" s="37" t="n">
         <v>74.9160356344936</v>
       </c>
       <c r="H36" s="38" t="n">
-        <v>0.003886933826842373</v>
+        <v>0.003886437237426723</v>
       </c>
       <c r="I36" s="39" t="n">
-        <v>0.894330761489433</v>
+        <v>0.8942646318966962</v>
       </c>
       <c r="J36" s="40" t="n">
-        <v>0.3817980022197558</v>
+        <v>0.3817365269461077</v>
       </c>
       <c r="K36" s="34" t="n">
         <v>4444</v>
       </c>
       <c r="L36" s="34" t="n">
-        <v>7480</v>
+        <v>7482</v>
       </c>
     </row>
     <row r="37">
@@ -2072,37 +2116,37 @@
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>44499</v>
+        <v>44547</v>
       </c>
       <c r="C37" s="9" t="n">
-        <v>0.2664578867318954</v>
+        <v>0.2664166786278169</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>190</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.6904234430467241</v>
+        <v>0.6902968346169733</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>0.04034152921679698</v>
+        <v>0.04035741324026729</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>52.90212919895188</v>
+        <v>52.89104217709205</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>0.004758141386199286</v>
+        <v>0.004752715022032841</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>0.6802849502236006</v>
+        <v>0.6795743821132736</v>
       </c>
       <c r="J37" s="16" t="n">
-        <v>0.2619380238760478</v>
+        <v>0.2615694164989939</v>
       </c>
       <c r="K37" s="8" t="n">
         <v>21445</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>23054</v>
+        <v>23102</v>
       </c>
     </row>
     <row r="38">
@@ -2112,37 +2156,37 @@
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>39144</v>
+        <v>39199</v>
       </c>
       <c r="C38" s="9" t="n">
-        <v>0.2343924024861978</v>
+        <v>0.2344325630352615</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>186</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0.6638804764477244</v>
+        <v>0.6637495076580315</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>0.02223305548002996</v>
+        <v>0.02224290126108189</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>49.28068926153357</v>
+        <v>49.2776897805286</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>-0.001409066485128878</v>
+        <v>-0.001409727965030592</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>0.4640047005926835</v>
+        <v>0.4639404066430266</v>
       </c>
       <c r="J38" s="14" t="n">
-        <v>-0.03368930088082278</v>
+        <v>-0.03372681281618883</v>
       </c>
       <c r="K38" s="8" t="n">
         <v>20445</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>18699</v>
+        <v>18754</v>
       </c>
     </row>
     <row r="39">
@@ -2152,37 +2196,37 @@
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>38997</v>
+        <v>39052</v>
       </c>
       <c r="C39" s="9" t="n">
-        <v>0.2335121735069041</v>
+        <v>0.2335534184967226</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>192</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>0.1510506845051409</v>
+        <v>0.150926666391757</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>0.03758247068321756</v>
+        <v>0.03760274952458108</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>50.00802921893109</v>
+        <v>50.0148053118144</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>0.0005378532318271194</v>
+        <v>0.000535719802229524</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>0.582916634612919</v>
+        <v>0.582454163679197</v>
       </c>
       <c r="J39" s="16" t="n">
-        <v>0.05235602094240832</v>
+        <v>0.05208327963974335</v>
       </c>
       <c r="K39" s="8" t="n">
         <v>20380</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>18617</v>
+        <v>18672</v>
       </c>
     </row>
     <row r="40">
@@ -2192,37 +2236,37 @@
         </is>
       </c>
       <c r="B40" s="18" t="n">
-        <v>44362</v>
+        <v>44410</v>
       </c>
       <c r="C40" s="19" t="n">
-        <v>0.2656375372750027</v>
+        <v>0.265597339840199</v>
       </c>
       <c r="D40" s="18" t="n">
         <v>185</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>0.1418535673477669</v>
+        <v>0.1416802986224325</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>0.02219832925522286</v>
+        <v>0.02220419848902573</v>
       </c>
       <c r="G40" s="21" t="n">
-        <v>50.44066855838543</v>
+        <v>50.43839806031573</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>7.531022626032319e-05</v>
+        <v>7.46909008204741e-05</v>
       </c>
       <c r="I40" s="23" t="n">
-        <v>0.5246832874983094</v>
+        <v>0.524544021616753</v>
       </c>
       <c r="J40" s="24" t="n">
-        <v>0.007266127701699432</v>
+        <v>0.007212468873333822</v>
       </c>
       <c r="K40" s="18" t="n">
         <v>21379</v>
       </c>
       <c r="L40" s="18" t="n">
-        <v>22983</v>
+        <v>23031</v>
       </c>
     </row>
     <row r="42">
@@ -2242,7 +2286,7 @@
     <row r="44">
       <c r="A44" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      YZ축   YZ高 63% / YZ低 50%                  ← 2위 (13.9%p)</t>
+          <t xml:space="preserve">      YZ축   YZ高 63% / YZ低 50%                  ← 2위 (13.8%p)</t>
         </is>
       </c>
     </row>
@@ -2256,96 +2300,110 @@
     <row r="46">
       <c r="A46" s="43" t="inlineStr">
         <is>
-          <t>⑦ ⚠ **YZ 가 방향을 가르는 건 예상 밖인데, 원인은 변동성이 아니라 종목 구성이다** (⑩ 참조). YZ 는 부호 없는 진폭 지표라 원래 방향과 무관해야 한다.</t>
+          <t>⑦ ⚠ **YZ 가 방향을 가르는 건 예상 밖이다** — YZ 는 부호 없는 진폭 지표라 원래 방향과 무관해야 한다.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   그런데 YZ高 의 과거60일이 +12.2%, YZ低 가 +0.2% 다. YZ高 에 상주하는 것이 바이오·반도체 중소형 성장주이고 YZ低 에 상주하는 것이 금융·통신·유틸리티라,</t>
+          <t xml:space="preserve">   그런데 YZ高 의 과거60일이 +12.1%, YZ低 가 +0.2% 다.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   2023~2026 강세장에서 전자가 오른 결과가 'YZ 가 방향을 가른다' 처럼 보이는 것이다. **섹터·스타일 효과이지 변동성 효과가 아니다.**</t>
+          <t xml:space="preserve">   ⚠⚠ **원인은 미규명이다.** 초판은 여기서 '섹터·스타일 효과' 라고 단정했는데 근거가 종목명 훑기뿐이었고, 재검증(YZ상주_검증 시트)에서 **틀린 것으로 판명**됐다 —</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → **YZ 를 방향 신호로 쓰지 말 것.** 진폭 축으로만 쓴다.</t>
+          <t xml:space="preserve">   YZ 상주를 가르는 것은 섹터 하나가 아니라 회전율·규모·섹터가 함께다. 그중 무엇이 방향까지 만드는지는 **이 표로 판정할 수 없다.**</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="43" t="inlineStr">
         <is>
-          <t>⑧ R²축은 방향은 못 가르지만 **크기**를 가른다: 기울기 중앙 R²高 +0.00237 / R²低 +0.00022 (11배), 과거60일 +10.4% / +2.1%.</t>
+          <t xml:space="preserve">   → 원인이 무엇이든 **YZ 를 방향 신호로 쓰지 말 것.** 부호 없는 지표에서 나온 방향성은 표본의 성질일 뿐 지표의 성질이 아니다. 진폭 축으로만 쓴다.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   즉 R² 가 높다는 건 '오른다'가 아니라 '**한 방향으로 크게 간다**'는 뜻이다 — 방향은 RSI 가, 진폭은 YZ 가, 크기·순도는 R² 가 담당한다. 세 축이 겹치지 않는다.</t>
+          <t>⑧ R²축은 방향은 못 가르지만 **크기**를 가른다: 기울기 중앙 R²高 +0.00236 / R²低 +0.00021 (11배), 과거60일 +10.4% / +2.1%.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="43" t="inlineStr">
         <is>
-          <t>⑨ 사분면 4개는 건수가 23.4%~26.6% 로 고르다. 상대 분할이라 당연하지만, 덕분에 사분면 간 비교는 표본 크기 차이를 걱정하지 않아도 된다.</t>
+          <t xml:space="preserve">   즉 R² 가 높다는 건 '오른다'가 아니라 '**한 방향으로 크게 간다**'는 뜻이다 — 방향은 RSI 가, 진폭은 YZ 가, 크기·순도는 R² 가 담당한다. 세 축이 겹치지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="43" t="inlineStr">
         <is>
-          <t>⑩ ★ **YZ 는 상태가 아니라 종목의 속성이다 — 이게 R²·RSI 와 결정적으로 다르다.**</t>
+          <t>⑨ 사분면 4개는 건수가 23.4%~26.6% 로 고르다. 상대 분할이라 당연하지만, 덕분에 사분면 간 비교는 표본 크기 차이를 걱정하지 않아도 된다.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   종목수를 보면 R²축은 高·低 모두 **206**(전 종목이 양쪽을 오간다)인데 YZ축은 **192 / 191** 다. 즉</t>
+          <t>⑩ ★ **YZ 는 상태가 아니라 종목의 속성이다 — 이게 R²·RSI 와 결정적으로 다르다.**</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   **15종목은 3.3년 내내 YZ高, 14종목은 내내 YZ低** 였다. 한 번도 반대편에 간 적이 없다.</t>
+          <t xml:space="preserve">   종목수를 보면 R²축은 高·低 모두 **206**(전 종목이 양쪽을 오간다)인데 YZ축은 **192 / 191** 다. 즉</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      항상 高 — 태성 · 하이젠알앤엠 · 펩트론 · 디앤디파마텍 · 보로노이 · 이수페타시스 · 삼천당제약 · 파두 · 브이엠 · 일진전기 · 제주반도체 · 엘앤에프 · 케어젠 · 이오테크닉스 · 유진테크</t>
+          <t xml:space="preserve">   **15종목은 3.3년 내내 YZ高, 14종목은 내내 YZ低** 였다. 한 번도 반대편에 간 적이 없다.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      항상 低 — 삼성바이오로직스 · BNK금융지주 · 에스원 · CJ제일제당 · KT&amp;G · 삼성카드 · 우리금융지주 · 대한항공 · KT · iM금융지주 · 강원랜드 · 기업은행 · LG유플러스 · 맥쿼리인프라</t>
+          <t xml:space="preserve">      항상 高 — 하이젠알앤엠 · 태성 · 펩트론 · 디앤디파마텍 · 보로노이 · 이수페타시스 · 삼천당제약 · 파두 · 브이엠 · 일진전기 · 제주반도체 · 엘앤에프 · 케어젠 · 이오테크닉스 · 유진테크</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   전자는 바이오·반도체 중소형 성장주, 후자는 금융·통신·유틸리티·필수소비재다. **YZ 분할은 사실상 스타일 분할**이고, ⑦ 의 방향성이 여기서 나온다.</t>
+          <t xml:space="preserve">      항상 低 — 삼성바이오로직스 · BNK금융지주 · 에스원 · CJ제일제당 · KT&amp;G · 삼성카드 · 우리금융지주 · 대한항공 · KT · iM금융지주 · 강원랜드 · 기업은행 · LG유플러스 · 맥쿼리인프라</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ **다만 '무엇의 속성인가' 는 이 명단으로 답할 수 없다** — 29종목으로 섹터 37개를 가를 수 없고, 우리 유니버스는 테크 계열에 쏠려 있어 섹터와 규모가 교란된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   206종목 전부를 놓고 재검증한 결과는 **YZ상주_검증 시트**에 있다. 요약: 회전율 &gt; 매출 &gt; 영업이익 &gt; 시총 &gt; 업력 순이고, 섹터는 규모로 환원되지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">   ※ BM(102110) 자신은 표본에서 제외했다 — 자기 대비 초과수익이 정의상 0 이고, 지수 ETF 라 내내 YZ低 에 상주해 편향이 한쪽에 몰리기 때문.</t>
         </is>
@@ -2498,19 +2556,19 @@
         <v>0.005997926726841629</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>0.01455861977963258</v>
+        <v>0.01461904224928601</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>0.01941499671532776</v>
+        <v>0.01940355475845568</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>0.02414657142164012</v>
+        <v>0.02424725379866494</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>0.01866640491164584</v>
+        <v>0.01863846038448425</v>
       </c>
       <c r="I5" s="53" t="n">
         <v>0.002119742087365983</v>
@@ -2519,25 +2577,25 @@
         <v>0.01774212949294141</v>
       </c>
       <c r="K5" s="54" t="n">
-        <v>0.01175523407848023</v>
+        <v>0.01179662044931518</v>
       </c>
       <c r="L5" s="53" t="n">
-        <v>0.02332595006055554</v>
+        <v>0.02341136967289409</v>
       </c>
       <c r="M5" s="53" t="n">
-        <v>0.03336609804963991</v>
+        <v>0.03343425729189275</v>
       </c>
       <c r="N5" s="53" t="n">
-        <v>0.04860300757857361</v>
+        <v>0.04854964081177676</v>
       </c>
       <c r="O5" s="53" t="n">
-        <v>0.05478496863060289</v>
+        <v>0.05473090156709204</v>
       </c>
       <c r="P5" s="53" t="n">
-        <v>0.04981680420354229</v>
+        <v>0.05014055709530491</v>
       </c>
       <c r="Q5" s="53" t="n">
-        <v>0.07137102290681763</v>
+        <v>0.07181359996078129</v>
       </c>
     </row>
     <row r="6">
@@ -2547,52 +2605,52 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>38938</v>
+        <v>38986</v>
       </c>
       <c r="C6" s="55" t="n">
-        <v>-0.009335718493165668</v>
+        <v>-0.009365378725599172</v>
       </c>
       <c r="D6" s="55" t="n">
-        <v>-0.01348625294837774</v>
+        <v>-0.01351665019092485</v>
       </c>
       <c r="E6" s="55" t="n">
-        <v>-0.02091352117678885</v>
+        <v>-0.02104236338250609</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>37796</v>
+        <v>37857</v>
       </c>
       <c r="G6" s="55" t="n">
-        <v>-0.03170769373552673</v>
+        <v>-0.03165849221819972</v>
       </c>
       <c r="H6" s="55" t="n">
-        <v>-0.03813140358897227</v>
+        <v>-0.03816037044820297</v>
       </c>
       <c r="I6" s="55" t="n">
-        <v>-0.04181099096430163</v>
+        <v>-0.04213190504123626</v>
       </c>
       <c r="J6" s="55" t="n">
-        <v>-0.05257453061176753</v>
+        <v>-0.05317988817259178</v>
       </c>
       <c r="K6" s="56" t="n">
-        <v>-0.003578411141527071</v>
+        <v>-0.003566685003125625</v>
       </c>
       <c r="L6" s="55" t="n">
-        <v>-0.004718922667454772</v>
+        <v>-0.004724322767316769</v>
       </c>
       <c r="M6" s="55" t="n">
-        <v>-0.006962419842476697</v>
+        <v>-0.007011660849069012</v>
       </c>
       <c r="N6" s="55" t="n">
-        <v>-0.00725125757859324</v>
+        <v>-0.007356105205087893</v>
       </c>
       <c r="O6" s="55" t="n">
-        <v>-0.002012839870015215</v>
+        <v>-0.002067929265595181</v>
       </c>
       <c r="P6" s="53" t="n">
-        <v>0.005886071151874672</v>
+        <v>0.00588890996670266</v>
       </c>
       <c r="Q6" s="53" t="n">
-        <v>0.001054362802108688</v>
+        <v>0.0008915822952481056</v>
       </c>
     </row>
     <row r="7">
@@ -2608,7 +2666,7 @@
         <v>-0.005946958179090633</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>-0.007313230479720545</v>
+        <v>-0.007279871416307926</v>
       </c>
       <c r="E7" s="57" t="n">
         <v>-0.01393749506542541</v>
@@ -2620,34 +2678,34 @@
         <v>-0.02354173706088591</v>
       </c>
       <c r="H7" s="57" t="n">
-        <v>-0.03030654607522654</v>
+        <v>-0.03083454029947896</v>
       </c>
       <c r="I7" s="57" t="n">
-        <v>-0.03551110535276314</v>
+        <v>-0.03696792593476339</v>
       </c>
       <c r="J7" s="57" t="n">
         <v>-0.07119427328742289</v>
       </c>
       <c r="K7" s="58" t="n">
-        <v>-0.000189650827452037</v>
+        <v>-0.0001482644566170865</v>
       </c>
       <c r="L7" s="59" t="n">
-        <v>0.001454099801202424</v>
+        <v>0.001512456007300156</v>
       </c>
       <c r="M7" s="59" t="n">
-        <v>1.360626888674554e-05</v>
+        <v>9.320746801166901e-05</v>
       </c>
       <c r="N7" s="59" t="n">
-        <v>0.0009146990960475776</v>
+        <v>0.0007606499522259114</v>
       </c>
       <c r="O7" s="59" t="n">
-        <v>0.005812017643730516</v>
+        <v>0.00525790088312883</v>
       </c>
       <c r="P7" s="59" t="n">
-        <v>0.01218595676341316</v>
+        <v>0.01105288907317553</v>
       </c>
       <c r="Q7" s="57" t="n">
-        <v>-0.01756537987354667</v>
+        <v>-0.01712280281958301</v>
       </c>
     </row>
     <row r="8">
@@ -2684,25 +2742,25 @@
         <v>-0.0510550537172495</v>
       </c>
       <c r="K8" s="62" t="n">
-        <v>0.01105263342888674</v>
+        <v>0.01109401979972169</v>
       </c>
       <c r="L8" s="60" t="n">
-        <v>0.0159435498990072</v>
+        <v>0.01596854704169232</v>
       </c>
       <c r="M8" s="60" t="n">
-        <v>0.01972994939010581</v>
+        <v>0.01980955058923073</v>
       </c>
       <c r="N8" s="60" t="n">
-        <v>0.03433948415792659</v>
+        <v>0.03418543501410493</v>
       </c>
       <c r="O8" s="60" t="n">
-        <v>0.02363455784745044</v>
+        <v>0.02360843531110118</v>
       </c>
       <c r="P8" s="60" t="n">
-        <v>0.008171374799537778</v>
+        <v>0.008495127691300397</v>
       </c>
       <c r="Q8" s="60" t="n">
-        <v>0.002573839696626723</v>
+        <v>0.003016416750590389</v>
       </c>
     </row>
     <row r="9">
@@ -2712,52 +2770,52 @@
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>35342</v>
+        <v>35397</v>
       </c>
       <c r="C9" s="61" t="n">
-        <v>-0.005234931752128413</v>
+        <v>-0.005267673141189033</v>
       </c>
       <c r="D9" s="61" t="n">
-        <v>-0.00855107949092887</v>
+        <v>-0.008628904652316305</v>
       </c>
       <c r="E9" s="61" t="n">
-        <v>-0.01454145546716629</v>
+        <v>-0.0146475611521204</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>34420</v>
+        <v>34461</v>
       </c>
       <c r="G9" s="61" t="n">
-        <v>-0.02673101820744361</v>
+        <v>-0.02639803188433659</v>
       </c>
       <c r="H9" s="61" t="n">
-        <v>-0.04055102567234115</v>
+        <v>-0.04044513390606685</v>
       </c>
       <c r="I9" s="61" t="n">
-        <v>-0.05222525779934778</v>
+        <v>-0.05238472783345127</v>
       </c>
       <c r="J9" s="61" t="n">
-        <v>-0.05707941483803558</v>
+        <v>-0.05729357036052485</v>
       </c>
       <c r="K9" s="62" t="n">
-        <v>0.0005223755995101831</v>
+        <v>0.0005310205812845137</v>
       </c>
       <c r="L9" s="60" t="n">
-        <v>0.0002162507899940991</v>
+        <v>0.0001634227712917768</v>
       </c>
       <c r="M9" s="61" t="n">
-        <v>-0.0005903541328541317</v>
+        <v>-0.0006168586186833247</v>
       </c>
       <c r="N9" s="61" t="n">
-        <v>-0.002274582050510121</v>
+        <v>-0.002095644871224767</v>
       </c>
       <c r="O9" s="61" t="n">
-        <v>-0.004432461953384093</v>
+        <v>-0.004352692723459062</v>
       </c>
       <c r="P9" s="61" t="n">
-        <v>-0.004528195683171476</v>
+        <v>-0.00436391282551235</v>
       </c>
       <c r="Q9" s="61" t="n">
-        <v>-0.003450521424159358</v>
+        <v>-0.00322209989268496</v>
       </c>
     </row>
     <row r="10">
@@ -2773,7 +2831,7 @@
         <v>-0.007354443812492506</v>
       </c>
       <c r="D10" s="63" t="n">
-        <v>-0.01280350380446349</v>
+        <v>-0.01280650269155792</v>
       </c>
       <c r="E10" s="63" t="n">
         <v>-0.03207481195947604</v>
@@ -2785,34 +2843,34 @@
         <v>-0.04470299617785312</v>
       </c>
       <c r="H10" s="63" t="n">
-        <v>-0.0612283816355027</v>
+        <v>-0.0611933895943324</v>
       </c>
       <c r="I10" s="63" t="n">
-        <v>-0.1391265025531311</v>
+        <v>-0.1401851199739492</v>
       </c>
       <c r="J10" s="63" t="n">
         <v>-0.136308980458466</v>
       </c>
       <c r="K10" s="64" t="n">
-        <v>-0.00159713646085391</v>
+        <v>-0.001555750090018959</v>
       </c>
       <c r="L10" s="63" t="n">
-        <v>-0.004036173523540521</v>
+        <v>-0.004014175267949838</v>
       </c>
       <c r="M10" s="63" t="n">
-        <v>-0.01812371062516388</v>
+        <v>-0.01804410942603896</v>
       </c>
       <c r="N10" s="63" t="n">
-        <v>-0.02024656002091962</v>
+        <v>-0.02040060916474129</v>
       </c>
       <c r="O10" s="63" t="n">
-        <v>-0.02510981791654565</v>
+        <v>-0.02510094841172461</v>
       </c>
       <c r="P10" s="63" t="n">
-        <v>-0.09142944043695478</v>
+        <v>-0.0921643049660103</v>
       </c>
       <c r="Q10" s="63" t="n">
-        <v>-0.08268008704458973</v>
+        <v>-0.08223750999062607</v>
       </c>
     </row>
     <row r="11">
@@ -2831,10 +2889,10 @@
         <v>0.0104086479672541</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>0.01861505874630698</v>
+        <v>0.01854093278061908</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="G11" s="53" t="n">
         <v>0.01485807363216951</v>
@@ -2849,25 +2907,25 @@
         <v>-0.02349552485604611</v>
       </c>
       <c r="K11" s="54" t="n">
-        <v>0.0162689689276595</v>
+        <v>0.01631035529849445</v>
       </c>
       <c r="L11" s="53" t="n">
-        <v>0.01917597824817707</v>
+        <v>0.01920097539086218</v>
       </c>
       <c r="M11" s="53" t="n">
-        <v>0.03256616008061913</v>
+        <v>0.03257163531405616</v>
       </c>
       <c r="N11" s="53" t="n">
-        <v>0.039314509789103</v>
+        <v>0.03916046064528134</v>
       </c>
       <c r="O11" s="53" t="n">
-        <v>0.04732991124319663</v>
+        <v>0.04730378870684737</v>
       </c>
       <c r="P11" s="53" t="n">
-        <v>0.01825057082457182</v>
+        <v>0.01857432371633444</v>
       </c>
       <c r="Q11" s="53" t="n">
-        <v>0.03013336855783011</v>
+        <v>0.03057594561179378</v>
       </c>
     </row>
     <row r="12">
@@ -2877,52 +2935,52 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>35479</v>
+        <v>35532</v>
       </c>
       <c r="C12" s="55" t="n">
-        <v>-0.006949839554129422</v>
+        <v>-0.006964210637633972</v>
       </c>
       <c r="D12" s="55" t="n">
-        <v>-0.009420983552588802</v>
+        <v>-0.009451339587625784</v>
       </c>
       <c r="E12" s="55" t="n">
-        <v>-0.01208124197388061</v>
+        <v>-0.01212377941202147</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>34526</v>
+        <v>34565</v>
       </c>
       <c r="G12" s="55" t="n">
-        <v>-0.01691378326731069</v>
+        <v>-0.01680984464844215</v>
       </c>
       <c r="H12" s="55" t="n">
-        <v>-0.02705375559932066</v>
+        <v>-0.02706392633500876</v>
       </c>
       <c r="I12" s="55" t="n">
-        <v>-0.03112637667245055</v>
+        <v>-0.03161411765961475</v>
       </c>
       <c r="J12" s="55" t="n">
-        <v>-0.03514955691256139</v>
+        <v>-0.03559329425037772</v>
       </c>
       <c r="K12" s="56" t="n">
-        <v>-0.001192532202490826</v>
+        <v>-0.001165516915160425</v>
       </c>
       <c r="L12" s="55" t="n">
-        <v>-0.0006536532716658328</v>
+        <v>-0.0006590121640177027</v>
       </c>
       <c r="M12" s="53" t="n">
-        <v>0.001869859360431547</v>
+        <v>0.001906923121415605</v>
       </c>
       <c r="N12" s="53" t="n">
-        <v>0.007542652889622803</v>
+        <v>0.007492542364669674</v>
       </c>
       <c r="O12" s="53" t="n">
-        <v>0.009064808119636392</v>
+        <v>0.009028514847599034</v>
       </c>
       <c r="P12" s="53" t="n">
-        <v>0.01657068544372575</v>
+        <v>0.01640669734832417</v>
       </c>
       <c r="Q12" s="53" t="n">
-        <v>0.01847933650131484</v>
+        <v>0.01847817621746217</v>
       </c>
     </row>
     <row r="13">
@@ -2932,52 +2990,52 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>2694</v>
+        <v>2696</v>
       </c>
       <c r="C13" s="57" t="n">
-        <v>-0.01081235697940508</v>
+        <v>-0.01069906380396934</v>
       </c>
       <c r="D13" s="57" t="n">
-        <v>-0.01612969460879676</v>
+        <v>-0.01613193823720138</v>
       </c>
       <c r="E13" s="57" t="n">
-        <v>-0.02017931417837482</v>
+        <v>-0.02022315962303572</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="G13" s="57" t="n">
         <v>-0.03758608064994173</v>
       </c>
       <c r="H13" s="57" t="n">
-        <v>-0.0405967074698127</v>
+        <v>-0.04080750218790752</v>
       </c>
       <c r="I13" s="57" t="n">
-        <v>-0.05105315469681038</v>
+        <v>-0.0523321082293533</v>
       </c>
       <c r="J13" s="57" t="n">
         <v>-0.06518802292877002</v>
       </c>
       <c r="K13" s="58" t="n">
-        <v>-0.005055049627766484</v>
+        <v>-0.004900370081495797</v>
       </c>
       <c r="L13" s="57" t="n">
-        <v>-0.007362364327873794</v>
+        <v>-0.0073396108135933</v>
       </c>
       <c r="M13" s="57" t="n">
-        <v>-0.006228212844062664</v>
+        <v>-0.006192457089598646</v>
       </c>
       <c r="N13" s="57" t="n">
-        <v>-0.01312964449300824</v>
+        <v>-0.01328369363682991</v>
       </c>
       <c r="O13" s="57" t="n">
-        <v>-0.004478143750855645</v>
+        <v>-0.004715061005299725</v>
       </c>
       <c r="P13" s="57" t="n">
-        <v>-0.003356092580634074</v>
+        <v>-0.004311293221414381</v>
       </c>
       <c r="Q13" s="57" t="n">
-        <v>-0.0115591295148938</v>
+        <v>-0.01111655246093013</v>
       </c>
     </row>
     <row r="14">
@@ -3011,28 +3069,28 @@
         <v>-0.02050677637525045</v>
       </c>
       <c r="J14" s="61" t="n">
-        <v>-0.01419432390839714</v>
+        <v>-0.01534262025889332</v>
       </c>
       <c r="K14" s="62" t="n">
-        <v>0.008317569180622764</v>
+        <v>0.008358955551457714</v>
       </c>
       <c r="L14" s="60" t="n">
-        <v>0.01867726859339597</v>
+        <v>0.01870226573608108</v>
       </c>
       <c r="M14" s="60" t="n">
-        <v>0.02519555218470132</v>
+        <v>0.02527515338382624</v>
       </c>
       <c r="N14" s="60" t="n">
-        <v>0.02050267660365868</v>
+        <v>0.02034862745983701</v>
       </c>
       <c r="O14" s="60" t="n">
-        <v>0.02695099691199265</v>
+        <v>0.02692487437564339</v>
       </c>
       <c r="P14" s="60" t="n">
-        <v>0.02719028574092586</v>
+        <v>0.02751403863268848</v>
       </c>
       <c r="Q14" s="60" t="n">
-        <v>0.03943456950547908</v>
+        <v>0.03872885020894656</v>
       </c>
     </row>
     <row r="15">
@@ -3042,52 +3100,52 @@
         </is>
       </c>
       <c r="B15" s="26" t="n">
-        <v>41161</v>
+        <v>41209</v>
       </c>
       <c r="C15" s="61" t="n">
-        <v>-0.004138259120960219</v>
+        <v>-0.004191757292032805</v>
       </c>
       <c r="D15" s="61" t="n">
-        <v>-0.00658818574564568</v>
+        <v>-0.006623432375192806</v>
       </c>
       <c r="E15" s="61" t="n">
-        <v>-0.01123775456262416</v>
+        <v>-0.01138990312635002</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>40056</v>
+        <v>40117</v>
       </c>
       <c r="G15" s="61" t="n">
-        <v>-0.02183070859648034</v>
+        <v>-0.02171773157362455</v>
       </c>
       <c r="H15" s="61" t="n">
-        <v>-0.03608718543344092</v>
+        <v>-0.03593547417493276</v>
       </c>
       <c r="I15" s="61" t="n">
-        <v>-0.05147883177805623</v>
+        <v>-0.05166198047840681</v>
       </c>
       <c r="J15" s="61" t="n">
-        <v>-0.05387935460001447</v>
+        <v>-0.05442961278961461</v>
       </c>
       <c r="K15" s="62" t="n">
-        <v>0.001619048230678377</v>
+        <v>0.001606936430440742</v>
       </c>
       <c r="L15" s="60" t="n">
-        <v>0.002179144535277289</v>
+        <v>0.002168895048415276</v>
       </c>
       <c r="M15" s="60" t="n">
-        <v>0.002713346771687997</v>
+        <v>0.002640799407087058</v>
       </c>
       <c r="N15" s="60" t="n">
-        <v>0.00262572756045315</v>
+        <v>0.002584655439487271</v>
       </c>
       <c r="O15" s="60" t="n">
-        <v>3.137828551613708e-05</v>
+        <v>0.0001569670076750351</v>
       </c>
       <c r="P15" s="61" t="n">
-        <v>-0.00378176966187993</v>
+        <v>-0.003641165470467889</v>
       </c>
       <c r="Q15" s="61" t="n">
-        <v>-0.0002504611861382511</v>
+        <v>-0.0003581423217747237</v>
       </c>
     </row>
     <row r="16">
@@ -3106,43 +3164,43 @@
         <v>-0.01300242194591861</v>
       </c>
       <c r="E16" s="63" t="n">
-        <v>-0.03543875644807115</v>
+        <v>-0.03544546434493639</v>
       </c>
       <c r="F16" s="34" t="n">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="G16" s="63" t="n">
-        <v>-0.06097599326126624</v>
+        <v>-0.0608946183977071</v>
       </c>
       <c r="H16" s="63" t="n">
         <v>-0.07408635717586709</v>
       </c>
       <c r="I16" s="63" t="n">
-        <v>-0.1357864676046643</v>
+        <v>-0.1378459527711136</v>
       </c>
       <c r="J16" s="63" t="n">
         <v>-0.1699136411639642</v>
       </c>
       <c r="K16" s="64" t="n">
-        <v>-0.002999428112827163</v>
+        <v>-0.002958041741992212</v>
       </c>
       <c r="L16" s="63" t="n">
-        <v>-0.004235091664995638</v>
+        <v>-0.004210094522310526</v>
       </c>
       <c r="M16" s="63" t="n">
-        <v>-0.021487655113759</v>
+        <v>-0.02141476181149932</v>
       </c>
       <c r="N16" s="63" t="n">
-        <v>-0.03651955710433274</v>
+        <v>-0.03659223138459528</v>
       </c>
       <c r="O16" s="63" t="n">
-        <v>-0.03796779345691004</v>
+        <v>-0.0379939159932593</v>
       </c>
       <c r="P16" s="63" t="n">
-        <v>-0.08808940548848804</v>
+        <v>-0.08982513776317469</v>
       </c>
       <c r="Q16" s="63" t="n">
-        <v>-0.116284747750088</v>
+        <v>-0.1158421706961243</v>
       </c>
     </row>
     <row r="17">
@@ -3152,31 +3210,31 @@
         </is>
       </c>
       <c r="B17" s="45" t="n">
-        <v>167002</v>
+        <v>167208</v>
       </c>
       <c r="C17" s="65" t="n">
-        <v>-0.005757307351638596</v>
+        <v>-0.005798693722473547</v>
       </c>
       <c r="D17" s="65" t="n">
-        <v>-0.008767330280922969</v>
+        <v>-0.008792327423608082</v>
       </c>
       <c r="E17" s="65" t="n">
-        <v>-0.01395110133431215</v>
+        <v>-0.01403070253343708</v>
       </c>
       <c r="F17" s="45" t="n">
-        <v>162796</v>
+        <v>163002</v>
       </c>
       <c r="G17" s="65" t="n">
-        <v>-0.02445643615693349</v>
+        <v>-0.02430238701311183</v>
       </c>
       <c r="H17" s="65" t="n">
-        <v>-0.03611856371895705</v>
+        <v>-0.03609244118260779</v>
       </c>
       <c r="I17" s="65" t="n">
-        <v>-0.0476970621161763</v>
+        <v>-0.04802081500793892</v>
       </c>
       <c r="J17" s="65" t="n">
-        <v>-0.05362889341387622</v>
+        <v>-0.05407147046783989</v>
       </c>
       <c r="K17" s="66" t="n"/>
       <c r="L17" s="67" t="n"/>
@@ -3354,19 +3412,19 @@
         <v>0.02380360516389505</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>0.03517823486696259</v>
+        <v>0.03518727601534961</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>0.05187752332444943</v>
+        <v>0.05161800700385025</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>0.06505635483764967</v>
+        <v>0.06539512903568963</v>
       </c>
       <c r="H5" s="53" t="n">
-        <v>0.08454656754506423</v>
+        <v>0.08402157664532717</v>
       </c>
       <c r="I5" s="53" t="n">
         <v>0.08675595412633187</v>
@@ -3375,25 +3433,25 @@
         <v>0.1578942815183549</v>
       </c>
       <c r="K5" s="54" t="n">
-        <v>0.0235079298756148</v>
+        <v>0.02354241915220472</v>
       </c>
       <c r="L5" s="53" t="n">
-        <v>0.03456359143276849</v>
+        <v>0.03461604478765869</v>
       </c>
       <c r="M5" s="53" t="n">
-        <v>0.05069584934167434</v>
+        <v>0.05059037898961761</v>
       </c>
       <c r="N5" s="53" t="n">
-        <v>0.06383956558633484</v>
+        <v>0.06408663465723881</v>
       </c>
       <c r="O5" s="53" t="n">
-        <v>0.08346712736312292</v>
+        <v>0.08294527401959891</v>
       </c>
       <c r="P5" s="53" t="n">
-        <v>0.0823527391233288</v>
+        <v>0.08269983106089047</v>
       </c>
       <c r="Q5" s="53" t="n">
-        <v>0.145327357588531</v>
+        <v>0.1457679585477918</v>
       </c>
     </row>
     <row r="6">
@@ -3403,52 +3461,52 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>38938</v>
+        <v>38986</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>0.001425500894952851</v>
+        <v>0.001378504259317452</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>0.002651931827813223</v>
+        <v>0.00260372118947745</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>0.00521715149459041</v>
+        <v>0.005005432849139976</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>37796</v>
+        <v>37857</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>0.01454670257641259</v>
+        <v>0.01458487354058872</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>0.03142758027712544</v>
+        <v>0.03125940501674232</v>
       </c>
       <c r="I6" s="53" t="n">
-        <v>0.05586397292178108</v>
+        <v>0.05536258463314101</v>
       </c>
       <c r="J6" s="53" t="n">
-        <v>0.08441445165887143</v>
+        <v>0.08367409008405952</v>
       </c>
       <c r="K6" s="54" t="n">
-        <v>0.001129825606672608</v>
+        <v>0.001117318247627124</v>
       </c>
       <c r="L6" s="53" t="n">
-        <v>0.002037288393619118</v>
+        <v>0.002032489961786527</v>
       </c>
       <c r="M6" s="53" t="n">
-        <v>0.004035477511815317</v>
+        <v>0.003977804834907333</v>
       </c>
       <c r="N6" s="53" t="n">
-        <v>0.01332991332509776</v>
+        <v>0.0132763791621379</v>
       </c>
       <c r="O6" s="53" t="n">
-        <v>0.03034814009518413</v>
+        <v>0.03018310239101406</v>
       </c>
       <c r="P6" s="53" t="n">
-        <v>0.05146075791877801</v>
+        <v>0.05130646156769961</v>
       </c>
       <c r="Q6" s="53" t="n">
-        <v>0.07184752772904748</v>
+        <v>0.07154776711349645</v>
       </c>
     </row>
     <row r="7">
@@ -3464,7 +3522,7 @@
         <v>0.01114235314421401</v>
       </c>
       <c r="D7" s="59" t="n">
-        <v>0.01895052723228124</v>
+        <v>0.01897662983615299</v>
       </c>
       <c r="E7" s="59" t="n">
         <v>0.04314617098035235</v>
@@ -3476,34 +3534,34 @@
         <v>0.08241813485694213</v>
       </c>
       <c r="H7" s="59" t="n">
-        <v>0.1105346360109081</v>
+        <v>0.1102628285315284</v>
       </c>
       <c r="I7" s="59" t="n">
-        <v>0.1799415285696109</v>
+        <v>0.1782669677253179</v>
       </c>
       <c r="J7" s="59" t="n">
-        <v>0.1646873674037797</v>
+        <v>0.1642774201491838</v>
       </c>
       <c r="K7" s="68" t="n">
-        <v>0.01084667785593377</v>
+        <v>0.01088116713252368</v>
       </c>
       <c r="L7" s="59" t="n">
-        <v>0.01833588379808714</v>
+        <v>0.01840539860846206</v>
       </c>
       <c r="M7" s="59" t="n">
-        <v>0.04196449699757726</v>
+        <v>0.04211854296611971</v>
       </c>
       <c r="N7" s="59" t="n">
-        <v>0.08120134560562731</v>
+        <v>0.08110964047849131</v>
       </c>
       <c r="O7" s="59" t="n">
-        <v>0.1094551958289668</v>
+        <v>0.1091865259058001</v>
       </c>
       <c r="P7" s="59" t="n">
-        <v>0.1755383135666078</v>
+        <v>0.1742108446598765</v>
       </c>
       <c r="Q7" s="59" t="n">
-        <v>0.1521204434739557</v>
+        <v>0.1521510971786207</v>
       </c>
     </row>
     <row r="8">
@@ -3540,25 +3598,25 @@
         <v>-0.03858121534941432</v>
       </c>
       <c r="K8" s="62" t="n">
-        <v>0.01031882083584574</v>
+        <v>0.01035331011243566</v>
       </c>
       <c r="L8" s="60" t="n">
-        <v>0.01254170659675449</v>
+        <v>0.01258511880325768</v>
       </c>
       <c r="M8" s="60" t="n">
-        <v>0.01695764553457227</v>
+        <v>0.01711169150311473</v>
       </c>
       <c r="N8" s="60" t="n">
-        <v>0.02791611988568563</v>
+        <v>0.02782441475854965</v>
       </c>
       <c r="O8" s="60" t="n">
-        <v>0.009241897564681877</v>
+        <v>0.009245035120894919</v>
       </c>
       <c r="P8" s="61" t="n">
-        <v>-0.04098203665912793</v>
+        <v>-0.04063494472156626</v>
       </c>
       <c r="Q8" s="61" t="n">
-        <v>-0.05114813927923826</v>
+        <v>-0.05070753831997738</v>
       </c>
     </row>
     <row r="9">
@@ -3568,52 +3626,52 @@
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>35342</v>
+        <v>35397</v>
       </c>
       <c r="C9" s="61" t="n">
-        <v>-0.002917629461637929</v>
+        <v>-0.002967757938527726</v>
       </c>
       <c r="D9" s="61" t="n">
-        <v>-0.005545280860366128</v>
+        <v>-0.005587032732951196</v>
       </c>
       <c r="E9" s="61" t="n">
-        <v>-0.01165819786121001</v>
+        <v>-0.01180049194715143</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>34420</v>
+        <v>34461</v>
       </c>
       <c r="G9" s="61" t="n">
-        <v>-0.02478707369714413</v>
+        <v>-0.02457043656150839</v>
       </c>
       <c r="H9" s="61" t="n">
-        <v>-0.04052686949110753</v>
+        <v>-0.04040226883355482</v>
       </c>
       <c r="I9" s="61" t="n">
-        <v>-0.05899700186942549</v>
+        <v>-0.05919517767962591</v>
       </c>
       <c r="J9" s="61" t="n">
-        <v>-0.05648277916589867</v>
+        <v>-0.05665323436827042</v>
       </c>
       <c r="K9" s="69" t="n">
-        <v>-0.003213304749918171</v>
+        <v>-0.003228943950218054</v>
       </c>
       <c r="L9" s="61" t="n">
-        <v>-0.006159924294560233</v>
+        <v>-0.006158263960642119</v>
       </c>
       <c r="M9" s="61" t="n">
-        <v>-0.0128398718439851</v>
+        <v>-0.01282811996138408</v>
       </c>
       <c r="N9" s="61" t="n">
-        <v>-0.02600386294845897</v>
+        <v>-0.02587893093995921</v>
       </c>
       <c r="O9" s="61" t="n">
-        <v>-0.04160630967304883</v>
+        <v>-0.04147857145928308</v>
       </c>
       <c r="P9" s="61" t="n">
-        <v>-0.06340021687242856</v>
+        <v>-0.06325130074506731</v>
       </c>
       <c r="Q9" s="61" t="n">
-        <v>-0.06904970309572261</v>
+        <v>-0.06877955733883348</v>
       </c>
     </row>
     <row r="10">
@@ -3629,7 +3687,7 @@
         <v>-0.005212910715732809</v>
       </c>
       <c r="D10" s="63" t="n">
-        <v>-0.01353182267805102</v>
+        <v>-0.0135444304930491</v>
       </c>
       <c r="E10" s="63" t="n">
         <v>-0.0236597112195582</v>
@@ -3641,34 +3699,34 @@
         <v>-0.04778697150993303</v>
       </c>
       <c r="H10" s="63" t="n">
-        <v>-0.08220306003991959</v>
+        <v>-0.08215225110148387</v>
       </c>
       <c r="I10" s="63" t="n">
-        <v>-0.1570531760892047</v>
+        <v>-0.1573173986226466</v>
       </c>
       <c r="J10" s="63" t="n">
         <v>-0.1458278315672663</v>
       </c>
       <c r="K10" s="64" t="n">
-        <v>-0.005508586004013052</v>
+        <v>-0.005474096727423138</v>
       </c>
       <c r="L10" s="63" t="n">
-        <v>-0.01414646611224513</v>
+        <v>-0.01411566172074002</v>
       </c>
       <c r="M10" s="63" t="n">
-        <v>-0.0248413852023333</v>
+        <v>-0.02468733923379084</v>
       </c>
       <c r="N10" s="63" t="n">
-        <v>-0.04900376076124786</v>
+        <v>-0.04909546588838385</v>
       </c>
       <c r="O10" s="63" t="n">
-        <v>-0.0832825002218609</v>
+        <v>-0.08322855372721213</v>
       </c>
       <c r="P10" s="63" t="n">
-        <v>-0.1614563910922078</v>
+        <v>-0.161373521688088</v>
       </c>
       <c r="Q10" s="63" t="n">
-        <v>-0.1583947554970903</v>
+        <v>-0.1579541545378294</v>
       </c>
     </row>
     <row r="11">
@@ -3687,10 +3745,10 @@
         <v>0.02298857006202292</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>0.03975233383404671</v>
+        <v>0.03951189892698089</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="G11" s="53" t="n">
         <v>0.06318186269195827</v>
@@ -3705,25 +3763,25 @@
         <v>0.1749805077577546</v>
       </c>
       <c r="K11" s="54" t="n">
-        <v>0.01375337026583687</v>
+        <v>0.01378785954242679</v>
       </c>
       <c r="L11" s="53" t="n">
-        <v>0.02237392662782881</v>
+        <v>0.02241733883433199</v>
       </c>
       <c r="M11" s="53" t="n">
-        <v>0.03857065985127162</v>
+        <v>0.03848427091274825</v>
       </c>
       <c r="N11" s="53" t="n">
-        <v>0.06196507344064344</v>
+        <v>0.06187336831350745</v>
       </c>
       <c r="O11" s="53" t="n">
-        <v>0.07891678494923793</v>
+        <v>0.07891992250545098</v>
       </c>
       <c r="P11" s="53" t="n">
-        <v>0.09235696624327633</v>
+        <v>0.09270405818083799</v>
       </c>
       <c r="Q11" s="53" t="n">
-        <v>0.1624135838279307</v>
+        <v>0.1628541847871916</v>
       </c>
     </row>
     <row r="12">
@@ -3733,52 +3791,52 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>35479</v>
+        <v>35532</v>
       </c>
       <c r="C12" s="53" t="n">
-        <v>0.002626974930215538</v>
+        <v>0.002614470094721536</v>
       </c>
       <c r="D12" s="53" t="n">
-        <v>0.007007444692338877</v>
+        <v>0.006939045591663749</v>
       </c>
       <c r="E12" s="53" t="n">
-        <v>0.0163468086040168</v>
+        <v>0.01624353894779447</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>34526</v>
+        <v>34565</v>
       </c>
       <c r="G12" s="53" t="n">
-        <v>0.03509225482127232</v>
+        <v>0.03508670945961254</v>
       </c>
       <c r="H12" s="53" t="n">
-        <v>0.05044274469647266</v>
+        <v>0.05029675172441643</v>
       </c>
       <c r="I12" s="53" t="n">
-        <v>0.0706176128660608</v>
+        <v>0.07028289721743725</v>
       </c>
       <c r="J12" s="53" t="n">
-        <v>0.09671964701172001</v>
+        <v>0.09627255566113595</v>
       </c>
       <c r="K12" s="54" t="n">
-        <v>0.002331299641935295</v>
+        <v>0.002353284083031208</v>
       </c>
       <c r="L12" s="53" t="n">
-        <v>0.006392801258144772</v>
+        <v>0.006367814363972827</v>
       </c>
       <c r="M12" s="53" t="n">
-        <v>0.0151651346212417</v>
+        <v>0.01521591093356183</v>
       </c>
       <c r="N12" s="53" t="n">
-        <v>0.03387546556995749</v>
+        <v>0.03377821508116172</v>
       </c>
       <c r="O12" s="53" t="n">
-        <v>0.04936330451453135</v>
+        <v>0.04922044909868817</v>
       </c>
       <c r="P12" s="53" t="n">
-        <v>0.06621439786305774</v>
+        <v>0.06622677415199585</v>
       </c>
       <c r="Q12" s="53" t="n">
-        <v>0.08415272308189606</v>
+        <v>0.08414623269057289</v>
       </c>
     </row>
     <row r="13">
@@ -3788,52 +3846,52 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>2694</v>
+        <v>2696</v>
       </c>
       <c r="C13" s="59" t="n">
-        <v>0.005832773433689562</v>
+        <v>0.005851036167249476</v>
       </c>
       <c r="D13" s="59" t="n">
-        <v>0.008894157675132904</v>
+        <v>0.008758892121998372</v>
       </c>
       <c r="E13" s="59" t="n">
-        <v>0.02958912749252926</v>
+        <v>0.02945514740321906</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="G13" s="59" t="n">
         <v>0.04758955645588826</v>
       </c>
       <c r="H13" s="59" t="n">
-        <v>0.07020437821349822</v>
+        <v>0.07012096600483732</v>
       </c>
       <c r="I13" s="59" t="n">
-        <v>0.1662822100978717</v>
+        <v>0.1647927960782097</v>
       </c>
       <c r="J13" s="59" t="n">
         <v>0.2251950020964874</v>
       </c>
       <c r="K13" s="68" t="n">
-        <v>0.005537098145409319</v>
+        <v>0.005589850155559148</v>
       </c>
       <c r="L13" s="59" t="n">
-        <v>0.0082795142409388</v>
+        <v>0.00818766089430745</v>
       </c>
       <c r="M13" s="59" t="n">
-        <v>0.02840745350975417</v>
+        <v>0.02842751938898642</v>
       </c>
       <c r="N13" s="59" t="n">
-        <v>0.04637276720457343</v>
+        <v>0.04628106207743744</v>
       </c>
       <c r="O13" s="59" t="n">
-        <v>0.06912493803155691</v>
+        <v>0.06904466337910906</v>
       </c>
       <c r="P13" s="59" t="n">
-        <v>0.1618789950948686</v>
+        <v>0.1607366730127683</v>
       </c>
       <c r="Q13" s="59" t="n">
-        <v>0.2126280781666635</v>
+        <v>0.2130686791259244</v>
       </c>
     </row>
     <row r="14">
@@ -3867,28 +3925,28 @@
         <v>-0.002820229154788798</v>
       </c>
       <c r="J14" s="61" t="n">
-        <v>-0.0001935647829084831</v>
+        <v>-0.0005811498185179922</v>
       </c>
       <c r="K14" s="62" t="n">
-        <v>0.005535167735657094</v>
+        <v>0.005569657012247009</v>
       </c>
       <c r="L14" s="60" t="n">
-        <v>0.01055647180107246</v>
+        <v>0.01059988400757564</v>
       </c>
       <c r="M14" s="60" t="n">
-        <v>0.02212036536222247</v>
+        <v>0.02227441133076492</v>
       </c>
       <c r="N14" s="60" t="n">
-        <v>0.007958791394669198</v>
+        <v>0.00786708626753321</v>
       </c>
       <c r="O14" s="61" t="n">
-        <v>-0.008526919063948602</v>
+        <v>-0.00852378150773556</v>
       </c>
       <c r="P14" s="61" t="n">
-        <v>-0.007223444157791863</v>
+        <v>-0.006876352220230201</v>
       </c>
       <c r="Q14" s="61" t="n">
-        <v>-0.01276048871273242</v>
+        <v>-0.01270747278908105</v>
       </c>
     </row>
     <row r="15">
@@ -3898,52 +3956,52 @@
         </is>
       </c>
       <c r="B15" s="26" t="n">
-        <v>41161</v>
+        <v>41209</v>
       </c>
       <c r="C15" s="61" t="n">
-        <v>-0.002229444016275834</v>
+        <v>-0.002269536626180071</v>
       </c>
       <c r="D15" s="61" t="n">
-        <v>-0.004569698354644277</v>
+        <v>-0.00459612360996666</v>
       </c>
       <c r="E15" s="61" t="n">
-        <v>-0.01098376084494831</v>
+        <v>-0.01116477180037653</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>40056</v>
+        <v>40117</v>
       </c>
       <c r="G15" s="61" t="n">
-        <v>-0.02876754744277505</v>
+        <v>-0.02861455836155558</v>
       </c>
       <c r="H15" s="61" t="n">
-        <v>-0.04611861196712046</v>
+        <v>-0.04589619668433604</v>
       </c>
       <c r="I15" s="61" t="n">
-        <v>-0.06157238124650874</v>
+        <v>-0.0617508123228831</v>
       </c>
       <c r="J15" s="61" t="n">
-        <v>-0.08794880874174438</v>
+        <v>-0.08843234430976027</v>
       </c>
       <c r="K15" s="69" t="n">
-        <v>-0.002525119304556077</v>
+        <v>-0.002530722637870399</v>
       </c>
       <c r="L15" s="61" t="n">
-        <v>-0.005184341788838382</v>
+        <v>-0.005167354837657583</v>
       </c>
       <c r="M15" s="61" t="n">
-        <v>-0.0121654348277234</v>
+        <v>-0.01219239981460917</v>
       </c>
       <c r="N15" s="61" t="n">
-        <v>-0.02998433669408989</v>
+        <v>-0.0299230527400064</v>
       </c>
       <c r="O15" s="61" t="n">
-        <v>-0.04719805214906176</v>
+        <v>-0.0469724993100643</v>
       </c>
       <c r="P15" s="61" t="n">
-        <v>-0.0659755962495118</v>
+        <v>-0.06580693538832449</v>
       </c>
       <c r="Q15" s="61" t="n">
-        <v>-0.1005157326715683</v>
+        <v>-0.1005586672803233</v>
       </c>
     </row>
     <row r="16">
@@ -3962,43 +4020,43 @@
         <v>-0.01178696598438872</v>
       </c>
       <c r="E16" s="63" t="n">
-        <v>-0.03338000825729476</v>
+        <v>-0.03346010377009126</v>
       </c>
       <c r="F16" s="34" t="n">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="G16" s="63" t="n">
-        <v>-0.05040843591337794</v>
+        <v>-0.05037569031343744</v>
       </c>
       <c r="H16" s="63" t="n">
         <v>-0.07440509927544374</v>
       </c>
       <c r="I16" s="63" t="n">
-        <v>-0.1379873259707958</v>
+        <v>-0.1386752844981032</v>
       </c>
       <c r="J16" s="63" t="n">
         <v>-0.1317367754195199</v>
       </c>
       <c r="K16" s="64" t="n">
-        <v>-0.006741424092360049</v>
+        <v>-0.006706934815770134</v>
       </c>
       <c r="L16" s="63" t="n">
-        <v>-0.01240160941858283</v>
+        <v>-0.01235819721207964</v>
       </c>
       <c r="M16" s="63" t="n">
-        <v>-0.03456168224006985</v>
+        <v>-0.03448773178432391</v>
       </c>
       <c r="N16" s="63" t="n">
-        <v>-0.05162522516469277</v>
+        <v>-0.05168418469188826</v>
       </c>
       <c r="O16" s="63" t="n">
-        <v>-0.07548453945738505</v>
+        <v>-0.075481401901172</v>
       </c>
       <c r="P16" s="63" t="n">
-        <v>-0.1423905409737989</v>
+        <v>-0.1427314075635446</v>
       </c>
       <c r="Q16" s="63" t="n">
-        <v>-0.1443036993493439</v>
+        <v>-0.143863098390083</v>
       </c>
     </row>
     <row r="17">
@@ -4008,31 +4066,31 @@
         </is>
       </c>
       <c r="B17" s="45" t="n">
-        <v>167002</v>
+        <v>167208</v>
       </c>
       <c r="C17" s="70" t="n">
-        <v>0.0002956752882802428</v>
+        <v>0.0002611860116903281</v>
       </c>
       <c r="D17" s="70" t="n">
-        <v>0.0006146434341941048</v>
+        <v>0.0005712312276909223</v>
       </c>
       <c r="E17" s="70" t="n">
-        <v>0.001181673982775094</v>
+        <v>0.001027628014232643</v>
       </c>
       <c r="F17" s="45" t="n">
-        <v>162796</v>
+        <v>163002</v>
       </c>
       <c r="G17" s="70" t="n">
-        <v>0.001216789251314833</v>
+        <v>0.001308494378450821</v>
       </c>
       <c r="H17" s="70" t="n">
-        <v>0.001079440181941306</v>
+        <v>0.001076302625728263</v>
       </c>
       <c r="I17" s="70" t="n">
-        <v>0.004403215003003065</v>
+        <v>0.004056123065441403</v>
       </c>
       <c r="J17" s="70" t="n">
-        <v>0.01256692392982394</v>
+        <v>0.01212632297056306</v>
       </c>
       <c r="K17" s="66" t="n"/>
       <c r="L17" s="67" t="n"/>
@@ -5066,19 +5124,19 @@
         <v>0.04020014386835302</v>
       </c>
       <c r="D5" s="53" t="n">
-        <v>0.05837008165719793</v>
+        <v>0.05829295479761742</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>0.08648081207577824</v>
+        <v>0.08556346301054241</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>0.0293949523625846</v>
-      </c>
-      <c r="H5" s="53" t="n">
-        <v>0.0008077576742979709</v>
+        <v>0.03146431127738075</v>
+      </c>
+      <c r="H5" s="55" t="n">
+        <v>-0.004460979274855559</v>
       </c>
       <c r="I5" s="55" t="n">
         <v>-0.09682662698039157</v>
@@ -5087,25 +5145,25 @@
         <v>-0.02563004295794991</v>
       </c>
       <c r="K5" s="54" t="n">
-        <v>0.05104979809936516</v>
+        <v>0.05110947744190719</v>
       </c>
       <c r="L5" s="53" t="n">
-        <v>0.076060168549415</v>
+        <v>0.07601348815284481</v>
       </c>
       <c r="M5" s="53" t="n">
-        <v>0.1186772172016277</v>
+        <v>0.1179520690042908</v>
       </c>
       <c r="N5" s="53" t="n">
-        <v>0.09471557285696752</v>
+        <v>0.09631221818341612</v>
       </c>
       <c r="O5" s="53" t="n">
-        <v>0.1155762257295476</v>
+        <v>0.1099958409586255</v>
       </c>
       <c r="P5" s="53" t="n">
-        <v>0.1042077555861943</v>
+        <v>0.1046937503440121</v>
       </c>
       <c r="Q5" s="53" t="n">
-        <v>0.2435211021096674</v>
+        <v>0.2439334286954388</v>
       </c>
     </row>
     <row r="6">
@@ -5115,52 +5173,52 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>19995</v>
+        <v>20043</v>
       </c>
       <c r="C6" s="55" t="n">
-        <v>-0.01510315491760572</v>
+        <v>-0.0151389240783375</v>
       </c>
       <c r="D6" s="55" t="n">
-        <v>-0.02275909204754628</v>
+        <v>-0.02278075093442067</v>
       </c>
       <c r="E6" s="55" t="n">
-        <v>-0.03927146106178969</v>
+        <v>-0.0395176071921855</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>18869</v>
+        <v>18930</v>
       </c>
       <c r="G6" s="55" t="n">
-        <v>-0.07055128562835522</v>
+        <v>-0.07022136061682482</v>
       </c>
       <c r="H6" s="55" t="n">
-        <v>-0.1075955803648472</v>
+        <v>-0.107468634332899</v>
       </c>
       <c r="I6" s="55" t="n">
-        <v>-0.1515822076848345</v>
+        <v>-0.1523440609247628</v>
       </c>
       <c r="J6" s="55" t="n">
-        <v>-0.1773674809384592</v>
+        <v>-0.1792886932327209</v>
       </c>
       <c r="K6" s="56" t="n">
-        <v>-0.004253500686593581</v>
+        <v>-0.004229590504783332</v>
       </c>
       <c r="L6" s="55" t="n">
-        <v>-0.005069005155329209</v>
+        <v>-0.005060217579193282</v>
       </c>
       <c r="M6" s="55" t="n">
-        <v>-0.007075055935940211</v>
+        <v>-0.007129001198437068</v>
       </c>
       <c r="N6" s="55" t="n">
-        <v>-0.005230665133972301</v>
+        <v>-0.005373453710789455</v>
       </c>
       <c r="O6" s="53" t="n">
-        <v>0.007172887690402474</v>
+        <v>0.006988185900582033</v>
       </c>
       <c r="P6" s="53" t="n">
-        <v>0.04945217488175135</v>
+        <v>0.04917631639964082</v>
       </c>
       <c r="Q6" s="53" t="n">
-        <v>0.09178366412915812</v>
+        <v>0.09027477842066778</v>
       </c>
     </row>
     <row r="7">
@@ -5176,7 +5234,7 @@
         <v>-0.009363119191734492</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>-0.01256864806064217</v>
+        <v>-0.01252466629378551</v>
       </c>
       <c r="E7" s="57" t="n">
         <v>-0.02466032603290702</v>
@@ -5188,34 +5246,34 @@
         <v>-0.05111466021047062</v>
       </c>
       <c r="H7" s="57" t="n">
-        <v>-0.07574558173784984</v>
+        <v>-0.07578200479748665</v>
       </c>
       <c r="I7" s="57" t="n">
-        <v>-0.1153099243315825</v>
+        <v>-0.1162127207293353</v>
       </c>
       <c r="J7" s="57" t="n">
         <v>-0.228987228987229</v>
       </c>
       <c r="K7" s="68" t="n">
-        <v>0.001486535039277648</v>
+        <v>0.001546214381819677</v>
       </c>
       <c r="L7" s="59" t="n">
-        <v>0.005121438831574898</v>
+        <v>0.005195867061441872</v>
       </c>
       <c r="M7" s="59" t="n">
-        <v>0.00753607909294246</v>
+        <v>0.007728279960841411</v>
       </c>
       <c r="N7" s="59" t="n">
-        <v>0.0142059602839123</v>
+        <v>0.01373324669556475</v>
       </c>
       <c r="O7" s="59" t="n">
-        <v>0.03902288631739981</v>
+        <v>0.03867481543599438</v>
       </c>
       <c r="P7" s="59" t="n">
-        <v>0.08572445823500341</v>
+        <v>0.08530765659506834</v>
       </c>
       <c r="Q7" s="59" t="n">
-        <v>0.04016391608038827</v>
+        <v>0.04057624266615967</v>
       </c>
     </row>
     <row r="8">
@@ -5252,25 +5310,25 @@
         <v>-0.3383564322553836</v>
       </c>
       <c r="K8" s="62" t="n">
-        <v>0.01711138060659056</v>
+        <v>0.01717105994913259</v>
       </c>
       <c r="L8" s="60" t="n">
-        <v>0.01892524959047137</v>
+        <v>0.01895569605348169</v>
       </c>
       <c r="M8" s="60" t="n">
-        <v>0.03755206263667377</v>
+        <v>0.03774426350457272</v>
       </c>
       <c r="N8" s="60" t="n">
-        <v>0.07392178252427406</v>
+        <v>0.07344906893592651</v>
       </c>
       <c r="O8" s="60" t="n">
-        <v>0.08311994102096865</v>
+        <v>0.08280829319920002</v>
       </c>
       <c r="P8" s="61" t="n">
-        <v>-0.0040120571872585</v>
+        <v>-0.003526062429440757</v>
       </c>
       <c r="Q8" s="61" t="n">
-        <v>-0.06920528718776631</v>
+        <v>-0.06879296060199491</v>
       </c>
     </row>
     <row r="9">
@@ -5280,52 +5338,52 @@
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>16734</v>
+        <v>16789</v>
       </c>
       <c r="C9" s="61" t="n">
-        <v>-0.009324095961696865</v>
+        <v>-0.009485199824739499</v>
       </c>
       <c r="D9" s="61" t="n">
-        <v>-0.01673128028248261</v>
+        <v>-0.01675787019929248</v>
       </c>
       <c r="E9" s="61" t="n">
-        <v>-0.03116664228577459</v>
+        <v>-0.03149427884434342</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>15812</v>
+        <v>15853</v>
       </c>
       <c r="G9" s="61" t="n">
-        <v>-0.06859186983078497</v>
+        <v>-0.06786103961504031</v>
       </c>
       <c r="H9" s="61" t="n">
-        <v>-0.1295315191015267</v>
+        <v>-0.12903753510559</v>
       </c>
       <c r="I9" s="61" t="n">
-        <v>-0.2426406955653005</v>
+        <v>-0.2426568009903758</v>
       </c>
       <c r="J9" s="61" t="n">
-        <v>-0.3325410577476655</v>
+        <v>-0.3324442265837717</v>
       </c>
       <c r="K9" s="62" t="n">
-        <v>0.001525558269315275</v>
+        <v>0.001424133748814671</v>
       </c>
       <c r="L9" s="60" t="n">
-        <v>0.0009588066097344639</v>
+        <v>0.0009626631559349064</v>
       </c>
       <c r="M9" s="60" t="n">
-        <v>0.001029762840074888</v>
+        <v>0.0008943271494050165</v>
       </c>
       <c r="N9" s="61" t="n">
-        <v>-0.003271249336402049</v>
+        <v>-0.00301313270900494</v>
       </c>
       <c r="O9" s="61" t="n">
-        <v>-0.01476305104627706</v>
+        <v>-0.01458071487210899</v>
       </c>
       <c r="P9" s="61" t="n">
-        <v>-0.04160631299871465</v>
+        <v>-0.04113642366597214</v>
       </c>
       <c r="Q9" s="61" t="n">
-        <v>-0.06338991268004823</v>
+        <v>-0.06288075493038303</v>
       </c>
     </row>
     <row r="10">
@@ -5353,34 +5411,34 @@
         <v>-0.06350120135444437</v>
       </c>
       <c r="H10" s="63" t="n">
-        <v>-0.1166867480598059</v>
+        <v>-0.116637502648999</v>
       </c>
       <c r="I10" s="63" t="n">
-        <v>-0.2527664232264034</v>
+        <v>-0.2536887790931559</v>
       </c>
       <c r="J10" s="63" t="n">
         <v>-0.2748015852896286</v>
       </c>
       <c r="K10" s="72" t="n">
-        <v>0.0006528231789789674</v>
+        <v>0.0007125025215209968</v>
       </c>
       <c r="L10" s="63" t="n">
-        <v>-0.004410754306847564</v>
+        <v>-0.00438030784383725</v>
       </c>
       <c r="M10" s="63" t="n">
-        <v>-0.01067257204816058</v>
+        <v>-0.01048037118026163</v>
       </c>
       <c r="N10" s="71" t="n">
-        <v>0.00181941913993855</v>
+        <v>0.001346705551590999</v>
       </c>
       <c r="O10" s="63" t="n">
-        <v>-0.001918280004556294</v>
+        <v>-0.002180682415517943</v>
       </c>
       <c r="P10" s="63" t="n">
-        <v>-0.05173204065981751</v>
+        <v>-0.05216840176875226</v>
       </c>
       <c r="Q10" s="63" t="n">
-        <v>-0.005650440222011333</v>
+        <v>-0.005238113636239938</v>
       </c>
     </row>
     <row r="11">
@@ -5399,10 +5457,10 @@
         <v>0.01769375239461957</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>0.0270880982634476</v>
+        <v>0.0268490182349731</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G11" s="55" t="n">
         <v>-0.02039504659014701</v>
@@ -5417,25 +5475,25 @@
         <v>0.02611055286619446</v>
       </c>
       <c r="K11" s="54" t="n">
-        <v>0.02441927991124881</v>
+        <v>0.02447895925379084</v>
       </c>
       <c r="L11" s="53" t="n">
-        <v>0.03538383928683664</v>
+        <v>0.03541428574984695</v>
       </c>
       <c r="M11" s="53" t="n">
-        <v>0.05928450338929708</v>
+        <v>0.05923762422872153</v>
       </c>
       <c r="N11" s="53" t="n">
-        <v>0.0449255739042359</v>
+        <v>0.04445286031588835</v>
       </c>
       <c r="O11" s="53" t="n">
-        <v>0.1052721837958546</v>
+        <v>0.1049605359740859</v>
       </c>
       <c r="P11" s="53" t="n">
-        <v>0.1447815891650992</v>
+        <v>0.1452675839229169</v>
       </c>
       <c r="Q11" s="53" t="n">
-        <v>0.2952616979338117</v>
+        <v>0.2956740245195831</v>
       </c>
     </row>
     <row r="12">
@@ -5445,52 +5503,52 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>16759</v>
+        <v>16812</v>
       </c>
       <c r="C12" s="55" t="n">
-        <v>-0.01109242217670481</v>
+        <v>-0.01113648280459623</v>
       </c>
       <c r="D12" s="55" t="n">
-        <v>-0.01582570732935951</v>
+        <v>-0.01585478108859456</v>
       </c>
       <c r="E12" s="55" t="n">
-        <v>-0.02665121889042354</v>
+        <v>-0.02675265913290037</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>15841</v>
+        <v>15880</v>
       </c>
       <c r="G12" s="55" t="n">
-        <v>-0.04980047706003976</v>
+        <v>-0.04926451726185221</v>
       </c>
       <c r="H12" s="55" t="n">
         <v>-0.09122154829567974</v>
       </c>
       <c r="I12" s="55" t="n">
-        <v>-0.1510393131495706</v>
+        <v>-0.1512578859730255</v>
       </c>
       <c r="J12" s="55" t="n">
-        <v>-0.188990522352418</v>
+        <v>-0.1899905646404416</v>
       </c>
       <c r="K12" s="56" t="n">
-        <v>-0.0002427679456926679</v>
+        <v>-0.0002271492310420564</v>
       </c>
       <c r="L12" s="53" t="n">
-        <v>0.001864379562857565</v>
+        <v>0.001865752266632825</v>
       </c>
       <c r="M12" s="53" t="n">
-        <v>0.005545186235425936</v>
+        <v>0.005635946860848062</v>
       </c>
       <c r="N12" s="53" t="n">
-        <v>0.01552014343434316</v>
+        <v>0.01558338964418315</v>
       </c>
       <c r="O12" s="53" t="n">
-        <v>0.02354691975956991</v>
+        <v>0.02323527193780128</v>
       </c>
       <c r="P12" s="53" t="n">
-        <v>0.04999506941701526</v>
+        <v>0.05026249135137817</v>
       </c>
       <c r="Q12" s="53" t="n">
-        <v>0.0801606227151993</v>
+        <v>0.07957290701294706</v>
       </c>
     </row>
     <row r="13">
@@ -5500,52 +5558,52 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="C13" s="57" t="n">
-        <v>-0.0116031451687626</v>
+        <v>-0.01157704306645435</v>
       </c>
       <c r="D13" s="57" t="n">
-        <v>-0.02406677767501475</v>
+        <v>-0.02421159985992183</v>
       </c>
       <c r="E13" s="57" t="n">
-        <v>-0.03240098490394105</v>
+        <v>-0.03244601579100104</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>1585</v>
+        <v>1586</v>
       </c>
       <c r="G13" s="57" t="n">
         <v>-0.07588882845319378</v>
       </c>
       <c r="H13" s="57" t="n">
-        <v>-0.1131065637640372</v>
+        <v>-0.1131575503036025</v>
       </c>
       <c r="I13" s="57" t="n">
-        <v>-0.1803539407460346</v>
+        <v>-0.1832947696697549</v>
       </c>
       <c r="J13" s="57" t="n">
         <v>-0.23256809555238</v>
       </c>
       <c r="K13" s="58" t="n">
-        <v>-0.0007534909377504562</v>
+        <v>-0.0006677094929001814</v>
       </c>
       <c r="L13" s="57" t="n">
-        <v>-0.006376690782797678</v>
+        <v>-0.006491066504694443</v>
       </c>
       <c r="M13" s="57" t="n">
-        <v>-0.0002045797780915737</v>
+        <v>-5.740979725260553e-05</v>
       </c>
       <c r="N13" s="57" t="n">
-        <v>-0.01056820795881086</v>
+        <v>-0.01104092154715841</v>
       </c>
       <c r="O13" s="59" t="n">
-        <v>0.001661904291212435</v>
+        <v>0.001299269929878499</v>
       </c>
       <c r="P13" s="59" t="n">
-        <v>0.02068044182055129</v>
+        <v>0.01822560765464876</v>
       </c>
       <c r="Q13" s="59" t="n">
-        <v>0.03658304951523728</v>
+        <v>0.03699537610100867</v>
       </c>
     </row>
     <row r="14">
@@ -5579,28 +5637,28 @@
         <v>-0.104844820604843</v>
       </c>
       <c r="J14" s="61" t="n">
-        <v>-0.2239630936352408</v>
+        <v>-0.2272541520355096</v>
       </c>
       <c r="K14" s="62" t="n">
-        <v>0.009859466743983969</v>
+        <v>0.009919146086525998</v>
       </c>
       <c r="L14" s="60" t="n">
-        <v>0.02114595744927461</v>
+        <v>0.02117640391228492</v>
       </c>
       <c r="M14" s="60" t="n">
-        <v>0.04288215954248237</v>
+        <v>0.04307436041038132</v>
       </c>
       <c r="N14" s="60" t="n">
-        <v>0.05041690763153517</v>
+        <v>0.04994419404318762</v>
       </c>
       <c r="O14" s="60" t="n">
-        <v>0.1314556669436343</v>
+        <v>0.1311440191218657</v>
       </c>
       <c r="P14" s="60" t="n">
-        <v>0.09618956196174289</v>
+        <v>0.09667555671956063</v>
       </c>
       <c r="Q14" s="60" t="n">
-        <v>0.04518805143237647</v>
+        <v>0.04230931961787909</v>
       </c>
     </row>
     <row r="15">
@@ -5610,52 +5668,52 @@
         </is>
       </c>
       <c r="B15" s="26" t="n">
-        <v>21182</v>
+        <v>21230</v>
       </c>
       <c r="C15" s="61" t="n">
-        <v>-0.01005841349416842</v>
+        <v>-0.01017032688710473</v>
       </c>
       <c r="D15" s="61" t="n">
-        <v>-0.01705792302527437</v>
+        <v>-0.01710038966777816</v>
       </c>
       <c r="E15" s="61" t="n">
-        <v>-0.03226984242750519</v>
+        <v>-0.03248639263481246</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>20081</v>
+        <v>20142</v>
       </c>
       <c r="G15" s="61" t="n">
-        <v>-0.07221374463692987</v>
+        <v>-0.07190022404703766</v>
       </c>
       <c r="H15" s="61" t="n">
-        <v>-0.1336869142790801</v>
+        <v>-0.1328246541459408</v>
       </c>
       <c r="I15" s="61" t="n">
-        <v>-0.2396235384320491</v>
+        <v>-0.239282484851286</v>
       </c>
       <c r="J15" s="61" t="n">
-        <v>-0.3343214276226479</v>
+        <v>-0.3346216638732686</v>
       </c>
       <c r="K15" s="62" t="n">
-        <v>0.0007912407368437235</v>
+        <v>0.0007390066864494393</v>
       </c>
       <c r="L15" s="60" t="n">
-        <v>0.0006321638669427032</v>
+        <v>0.0006201436874492261</v>
       </c>
       <c r="M15" s="61" t="n">
-        <v>-7.343730165570994e-05</v>
+        <v>-9.778664106402379e-05</v>
       </c>
       <c r="N15" s="61" t="n">
-        <v>-0.006893124142546947</v>
+        <v>-0.007052317141002296</v>
       </c>
       <c r="O15" s="61" t="n">
-        <v>-0.01891844622383049</v>
+        <v>-0.01836783391245977</v>
       </c>
       <c r="P15" s="61" t="n">
-        <v>-0.03858915586546319</v>
+        <v>-0.03776210752688236</v>
       </c>
       <c r="Q15" s="61" t="n">
-        <v>-0.06517028255503066</v>
+        <v>-0.06505819221987996</v>
       </c>
     </row>
     <row r="16">
@@ -5674,43 +5732,43 @@
         <v>-0.02264482161427489</v>
       </c>
       <c r="E16" s="63" t="n">
-        <v>-0.05752376511655732</v>
+        <v>-0.0576559970351298</v>
       </c>
       <c r="F16" s="34" t="n">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="G16" s="63" t="n">
-        <v>-0.07914015513733941</v>
+        <v>-0.07902584252915901</v>
       </c>
       <c r="H16" s="63" t="n">
         <v>-0.1230971397096432</v>
       </c>
       <c r="I16" s="63" t="n">
-        <v>-0.2594025479430868</v>
+        <v>-0.2598126555958944</v>
       </c>
       <c r="J16" s="63" t="n">
         <v>-0.3348660542707862</v>
       </c>
       <c r="K16" s="64" t="n">
-        <v>-0.001898607243257633</v>
+        <v>-0.001838927900715603</v>
       </c>
       <c r="L16" s="63" t="n">
-        <v>-0.004954734722057819</v>
+        <v>-0.004924288259047505</v>
       </c>
       <c r="M16" s="63" t="n">
-        <v>-0.02532735999070784</v>
+        <v>-0.02526739104138137</v>
       </c>
       <c r="N16" s="63" t="n">
-        <v>-0.01381953464295649</v>
+        <v>-0.01417793562312364</v>
       </c>
       <c r="O16" s="63" t="n">
-        <v>-0.008328671654393549</v>
+        <v>-0.008640319476162173</v>
       </c>
       <c r="P16" s="63" t="n">
-        <v>-0.05836816537650091</v>
+        <v>-0.05829227827149075</v>
       </c>
       <c r="Q16" s="63" t="n">
-        <v>-0.06571490920316891</v>
+        <v>-0.06530258261739752</v>
       </c>
     </row>
     <row r="17">
@@ -5720,31 +5778,31 @@
         </is>
       </c>
       <c r="B17" s="45" t="n">
-        <v>83353</v>
+        <v>83559</v>
       </c>
       <c r="C17" s="65" t="n">
-        <v>-0.01084965423101214</v>
+        <v>-0.01090933357355417</v>
       </c>
       <c r="D17" s="65" t="n">
-        <v>-0.01769008689221707</v>
+        <v>-0.01772053335522739</v>
       </c>
       <c r="E17" s="65" t="n">
-        <v>-0.03219640512584948</v>
+        <v>-0.03238860599374843</v>
       </c>
       <c r="F17" s="45" t="n">
-        <v>79210</v>
+        <v>79416</v>
       </c>
       <c r="G17" s="65" t="n">
-        <v>-0.06532062049438292</v>
+        <v>-0.06484790690603537</v>
       </c>
       <c r="H17" s="65" t="n">
-        <v>-0.1147684680552497</v>
+        <v>-0.114456820233481</v>
       </c>
       <c r="I17" s="65" t="n">
-        <v>-0.2010343825665859</v>
+        <v>-0.2015203773244036</v>
       </c>
       <c r="J17" s="65" t="n">
-        <v>-0.2691511450676173</v>
+        <v>-0.2695634716533887</v>
       </c>
       <c r="K17" s="66" t="n"/>
       <c r="L17" s="67" t="n"/>
@@ -5778,4 +5836,738 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J63"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="73" t="inlineStr">
+        <is>
+          <t>YZ 상주는 무엇의 속성인가 — 재검증</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>생성기 scripts/yz_persistence_probe.py   ·   206종목 (BM 제외)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="74" t="inlineStr">
+        <is>
+          <t>왜 다시 했나 (케인 지적 2026-09-08)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   초판 주석 ⑩ 은 '항상 高/低' 29종목의 **이름을 눈으로 훑고** "YZ 분할은 사실상 스타일(섹터) 분할" 이라고 단정했다. 세 가지가 틀렸다 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ① 29종목으로 섹터 37개를 가를 수 없다(자유도 부족)  ② 업종만 보고 시총·매출·영업이익·업력을 안 봤다</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ③ 유니버스가 테크 계열에 쏠려 있다(69종목 33.5%, 유효섹터수 27.0/37) — 섹터와 규모가 애초에 교란돼 있다</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="43" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="74" t="inlineStr">
+        <is>
+          <t>그래서 어떻게 고쳤나</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   종속변수를 **206종목 각각의 YZ高 비율**(0~1 연속)로 바꿨다. 29종목은 이 분포의 양 끝 꼬리로 자연히 포함된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   검정은 단독 설명력 → **교란 통제 후 증분** → 순열검정. 섹터는 수준이 37개라 우연히도 η² 가 커지므로 귀무분포로 판정한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="43" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="74" t="inlineStr">
+        <is>
+          <t>⚠ 교란의 크기 — 케인 지적이 옳았다는 증거</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   섹터가 이미 설명하고 있는 분산 η²: log_mcap 0.516 · log_rev 0.560 · age_yrs 0.259 · log_turnover 0.602</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   즉 섹터를 알면 시총·매출·회전율의 절반 이상이 따라온다. **통제 없이 '섹터 때문' 이라 말할 수 없다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>[A] 단독 설명력과 통제 후 — 연속변수는 스피어만 ρ, 범주형은 η²</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>변수</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>ρ</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>ρ²</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>회전율 통제 후 ρ</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>시총 통제 후 ρ</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>η²</t>
+        </is>
+      </c>
+      <c r="H19" s="6" t="inlineStr">
+        <is>
+          <t>회전율 통제 후 η²</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>시총 통제 후 η²</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>순열 p</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>회전율(로그)</t>
+        </is>
+      </c>
+      <c r="B20" s="8" t="n">
+        <v>206</v>
+      </c>
+      <c r="C20" s="75" t="n">
+        <v>0.7738674323464441</v>
+      </c>
+      <c r="D20" s="10" t="n">
+        <v>0.5988708028464782</v>
+      </c>
+      <c r="E20" s="75" t="n">
+        <v>0.1340945203457944</v>
+      </c>
+      <c r="F20" s="75" t="n">
+        <v>0.6581384893629434</v>
+      </c>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n"/>
+      <c r="I20" s="10" t="n"/>
+      <c r="J20" s="76" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="inlineStr">
+        <is>
+          <t>매출(로그)</t>
+        </is>
+      </c>
+      <c r="B21" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="C21" s="77" t="n">
+        <v>-0.6749096408208531</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <v>0.455503023272933</v>
+      </c>
+      <c r="E21" s="77" t="n">
+        <v>-0.449358909088061</v>
+      </c>
+      <c r="F21" s="77" t="n">
+        <v>-0.4290844579511722</v>
+      </c>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n"/>
+      <c r="I21" s="10" t="n"/>
+      <c r="J21" s="76" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>영업이익(로그·흑자만)</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="n">
+        <v>168</v>
+      </c>
+      <c r="C22" s="77" t="n">
+        <v>-0.6054238571341927</v>
+      </c>
+      <c r="D22" s="10" t="n">
+        <v>0.3665380467872433</v>
+      </c>
+      <c r="E22" s="77" t="n">
+        <v>-0.3488239075526041</v>
+      </c>
+      <c r="F22" s="77" t="n">
+        <v>-0.3254387252544784</v>
+      </c>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n"/>
+      <c r="I22" s="10" t="n"/>
+      <c r="J22" s="76" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>시총(로그)</t>
+        </is>
+      </c>
+      <c r="B23" s="8" t="n">
+        <v>206</v>
+      </c>
+      <c r="C23" s="77" t="n">
+        <v>-0.5021767770369202</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <v>0.2521815153951887</v>
+      </c>
+      <c r="E23" s="77" t="n">
+        <v>-0.2828835878059076</v>
+      </c>
+      <c r="F23" s="10" t="n"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n"/>
+      <c r="I23" s="10" t="n"/>
+      <c r="J23" s="76" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
+        <is>
+          <t>업력(년·우측절단)</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="n">
+        <v>204</v>
+      </c>
+      <c r="C24" s="77" t="n">
+        <v>-0.2532626350361538</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <v>0.06414196230545602</v>
+      </c>
+      <c r="E24" s="77" t="n">
+        <v>-0.2141871843911729</v>
+      </c>
+      <c r="F24" s="77" t="n">
+        <v>-0.244630208786202</v>
+      </c>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n"/>
+      <c r="I24" s="10" t="n"/>
+      <c r="J24" s="76" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>영업이익률</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="C25" s="77" t="n">
+        <v>-0.1203317092993867</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <v>0.01447972026291211</v>
+      </c>
+      <c r="E25" s="77" t="n">
+        <v>-0.01615650920711505</v>
+      </c>
+      <c r="F25" s="77" t="n">
+        <v>-0.01273957688783063</v>
+      </c>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+      <c r="I25" s="10" t="n"/>
+      <c r="J25" s="76" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>주가 수준</t>
+        </is>
+      </c>
+      <c r="B26" s="18" t="n">
+        <v>206</v>
+      </c>
+      <c r="C26" s="78" t="n">
+        <v>-0.1183833819804707</v>
+      </c>
+      <c r="D26" s="20" t="n">
+        <v>0.01401462512913404</v>
+      </c>
+      <c r="E26" s="78" t="n">
+        <v>-0.03669761293237209</v>
+      </c>
+      <c r="F26" s="79" t="n">
+        <v>0.140618586703343</v>
+      </c>
+      <c r="G26" s="20" t="n"/>
+      <c r="H26" s="20" t="n"/>
+      <c r="I26" s="20" t="n"/>
+      <c r="J26" s="80" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="25" t="inlineStr">
+        <is>
+          <t>섹터 (37개)</t>
+        </is>
+      </c>
+      <c r="B27" s="26" t="n">
+        <v>206</v>
+      </c>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="28" t="n"/>
+      <c r="E27" s="28" t="n"/>
+      <c r="F27" s="28" t="n"/>
+      <c r="G27" s="28" t="n">
+        <v>0.6120409539236005</v>
+      </c>
+      <c r="H27" s="28" t="n">
+        <v>0.3293645653429033</v>
+      </c>
+      <c r="I27" s="28" t="n">
+        <v>0.5868784135162091</v>
+      </c>
+      <c r="J27" s="81" t="n">
+        <v>0.0003332222592469177</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>시장 (KOSPI/KOSDAQ)</t>
+        </is>
+      </c>
+      <c r="B28" s="26" t="n">
+        <v>206</v>
+      </c>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="28" t="n">
+        <v>0.3783991360448898</v>
+      </c>
+      <c r="H28" s="28" t="n">
+        <v>0.1081882142326798</v>
+      </c>
+      <c r="I28" s="28" t="n">
+        <v>0.1598536679350999</v>
+      </c>
+      <c r="J28" s="81" t="n">
+        <v>0.0003332222592469177</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>테크 계열 여부</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n">
+        <v>206</v>
+      </c>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="28" t="n"/>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="28" t="n"/>
+      <c r="G29" s="28" t="n">
+        <v>0.1855391450359637</v>
+      </c>
+      <c r="H29" s="28" t="n">
+        <v>0.03544505258059982</v>
+      </c>
+      <c r="I29" s="28" t="n">
+        <v>0.08612769712434436</v>
+      </c>
+      <c r="J29" s="81" t="n">
+        <v>0.0003332222592469177</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>영업적자 여부</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n">
+        <v>206</v>
+      </c>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="28" t="n"/>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="28" t="n"/>
+      <c r="G30" s="28" t="n">
+        <v>0.1368531639520141</v>
+      </c>
+      <c r="H30" s="28" t="n">
+        <v>0.06315174347246741</v>
+      </c>
+      <c r="I30" s="28" t="n">
+        <v>0.07512081253859247</v>
+      </c>
+      <c r="J30" s="81" t="n">
+        <v>0.0003332222592469177</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="33" t="inlineStr">
+        <is>
+          <t>2010년 이전 상장</t>
+        </is>
+      </c>
+      <c r="B31" s="34" t="n">
+        <v>206</v>
+      </c>
+      <c r="C31" s="36" t="n"/>
+      <c r="D31" s="36" t="n"/>
+      <c r="E31" s="36" t="n"/>
+      <c r="F31" s="36" t="n"/>
+      <c r="G31" s="36" t="n">
+        <v>0.0647778250863848</v>
+      </c>
+      <c r="H31" s="36" t="n">
+        <v>0.0593447377557628</v>
+      </c>
+      <c r="I31" s="36" t="n">
+        <v>0.04471884977853955</v>
+      </c>
+      <c r="J31" s="82" t="n">
+        <v>0.0006664445184938354</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="43" t="inlineStr">
+        <is>
+          <t>읽기 — ⓐ 단일 최강은 **회전율**(ρ +0.774). 다만 거래량과 변동성은 정보 도착에 함께 반응하므로 **설명이라기보다 재진술**에 가깝다. 그래서 아래에서 이걸 통제한다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="43" t="inlineStr">
+        <is>
+          <t>ⓑ 규모 축에서 **매출(−0.675)이 시총(−0.502)보다 강하다.** 시총에는 기대(밸류에이션)가 섞여 있고 매출은 사업 규모 그 자체라, 사업이 작을수록 변동성이 크다는 쪽이 더 직접적이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="43" t="inlineStr">
+        <is>
+          <t>ⓒ **영업이익률(−0.120)·주가 수준(−0.118)은 사실상 무관하다.** '얼마나 잘 버느냐' 가 아니라 **'얼마나 크냐'** 가 가른다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="43" t="inlineStr">
+        <is>
+          <t>ⓓ 업력 −0.253 — 약하지만 있다. 다만 fundamentals 가 2010 시작이라 그 이전 상장이 전부 한 점에 몰리는 **우측중도절단**이라 과소추정이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="43" t="inlineStr">
+        <is>
+          <t>ⓔ 회전율을 통제해도 매출 −0.449, 섹터 η² 0.329(순열 p&lt;0.001)가 남는다 — **동어반복만은 아니다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>[B] 누적 설명력 (OLS R²)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>설명변수 묶음</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
+        <is>
+          <t>회전율</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="n">
+        <v>0.5693076051602309</v>
+      </c>
+      <c r="C41" s="8" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
+        <is>
+          <t>시총</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="n">
+        <v>0.2563199474273175</v>
+      </c>
+      <c r="C42" s="8" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
+        <is>
+          <t>매출</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="n">
+        <v>0.4074207973445131</v>
+      </c>
+      <c r="C43" s="8" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="inlineStr">
+        <is>
+          <t>시총+매출</t>
+        </is>
+      </c>
+      <c r="B44" s="10" t="n">
+        <v>0.4348527095223351</v>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="17" t="inlineStr">
+        <is>
+          <t>시총+매출+업력</t>
+        </is>
+      </c>
+      <c r="B45" s="20" t="n">
+        <v>0.454496614233509</v>
+      </c>
+      <c r="C45" s="18" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="25" t="inlineStr">
+        <is>
+          <t>회전율+시총</t>
+        </is>
+      </c>
+      <c r="B46" s="28" t="n">
+        <v>0.6095228506358021</v>
+      </c>
+      <c r="C46" s="26" t="n">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="25" t="inlineStr">
+        <is>
+          <t>회전율+시총+매출</t>
+        </is>
+      </c>
+      <c r="B47" s="28" t="n">
+        <v>0.6845328914900005</v>
+      </c>
+      <c r="C47" s="26" t="n">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="33" t="inlineStr">
+        <is>
+          <t>연속 4변수 전부</t>
+        </is>
+      </c>
+      <c r="B48" s="36" t="n">
+        <v>0.6847139722125093</v>
+      </c>
+      <c r="C48" s="34" t="n">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>[C] 최종 판정 — 규모를 전부 통제한 뒤에도 섹터가 남는가</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   연속 4변수(회전율·시총·매출·업력) R² = **0.685**  →  섹터 더미 추가 R² = **0.829**   증분 **+0.144** (n=182)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   섹터 라벨을 1,000회 섞은 귀무분포: 중앙 +0.062 · 95%분위 +0.087  →  **p = 0.0010**</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   반대 방향도 확인 — 시총 ρ 는 원자료 -0.502 에서 **섹터 내 편차만 쓰면 -0.426** 로, 거의 그대로 남는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="43" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⇒ **섹터와 규모는 서로를 대체하지 못한다. 둘 다 독립적으로 기여한다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     내 초판 문장 "**사실상** 스타일 분할" 은 이 점에서 **틀렸다** — 규모를 지운 자리에 섹터만 남는 구조가 아니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     동시에 "섹터는 규모의 그림자일 뿐" 이라는 반대편 주장도 성립하지 않는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="43" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⓕ 테크 쏠림은 착시의 주범이 **아니었다** — 테크 여부 단독 η² 0.186 → 시총 통제 후 0.086 으로 반 이상이 규모였다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     다만 **규모 효과의 세기가 진영마다 다르다**: 시총 ρ 가 테크 -0.506 vs 비테크 -0.260 로 두 배 차이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="43" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="43" t="inlineStr">
+        <is>
+          <t>⚠ 이 시트가 말하지 않는 것 — **인과가 아니다.** '무엇과 같이 움직이는가' 까지다. 그리고 ⑦ 의 '왜 방향까지 갈리는가' 는 여전히 **미규명**이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="43" t="inlineStr">
+        <is>
+          <t>⚠ 재무는 종목별 최신 유효 연도의 DART 단면(매출 183 / 영업이익 168종목)이라 결측이 무작위가 아닐 수 있다. 업력은 위 ⓓ 의 절단 문제를 안고 있다.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/holdtiming/results/cell12_R2xYZxRSI.xlsx
+++ b/docs/holdtiming/results/cell12_R2xYZxRSI.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="수익률_평균" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시대별_23-24_중앙" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시대별_25-26_중앙" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YZ상주_검증" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="YZ안정성_검증" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,13 +22,14 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.0%"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="167" formatCode="0.0&quot;%&quot;"/>
+    <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -114,6 +115,12 @@
       <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
@@ -223,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -447,28 +454,31 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -852,7 +862,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성 2026-09-09 12:13 KST   ·   MagicFormula/scripts/cell12_report.py  (원자료: LLV core+extend parquet)</t>
+          <t>생성 2026-09-09 23:02 KST   ·   MagicFormula/scripts/cell12_report.py  (원자료: LLV core+extend parquet)</t>
         </is>
       </c>
     </row>
@@ -5844,726 +5854,1223 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J63"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="11" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="73" t="inlineStr">
         <is>
-          <t>YZ 상주는 무엇의 속성인가 — 재검증</t>
+          <t>YZ 高/低 는 종목의 특성인가 — 안정성 검증</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성기 scripts/yz_persistence_probe.py   ·   206종목 (BM 제외)</t>
+          <t>생성기 scripts/yz_persistence_probe.py   ·   206종목 / 839일 / 167,208관측 (BM 제외)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="74" t="inlineStr">
         <is>
-          <t>왜 다시 했나 (케인 지적 2026-09-08)</t>
+          <t>질문의 내력 — 케인 지적 2회, 둘 다 옳았다</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   초판 주석 ⑩ 은 '항상 高/低' 29종목의 **이름을 눈으로 훑고** "YZ 분할은 사실상 스타일(섹터) 분할" 이라고 단정했다. 세 가지가 틀렸다 —</t>
+          <t xml:space="preserve">   초판: '항상 高/低' 29종목의 **이름을 눈으로 훑고** "사실상 스타일(섹터) 분할" 이라 단정.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ① 29종목으로 섹터 37개를 가를 수 없다(자유도 부족)  ② 업종만 보고 시총·매출·영업이익·업력을 안 봤다</t>
+          <t xml:space="preserve">   1차(09-08): 29종목으로 섹터 37개를 못 가른다 · 시총·매출·영업이익·업력도 봐야 한다 · 테크 쏠림으로 섹터와 규모가 교란된다 → 206종목 횡단면으로 재검증 (아래 [참고]).</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ③ 유니버스가 테크 계열에 쏠려 있다(69종목 33.5%, 유효섹터수 27.0/37) — 섹터와 규모가 애초에 교란돼 있다</t>
+          <t xml:space="preserve">   2차(09-09): ⚠ **질문을 바꿔치기했다.** 케인이 물은 것은 '수준이 안정적이냐'(시계열)인데 나는 '어떤 회사가 변동성이 높냐'(횡단면)로 답했다.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="43" t="inlineStr"/>
+      <c r="A8" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        게다가 그 답 — 작고·어리고·매출 적은 회사가 더 변동적 — 은 **교과서적 사실**이라 안 나오는 게 이상한 것이지 발견이 아니다.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="74" t="inlineStr">
-        <is>
-          <t>그래서 어떻게 고쳤나</t>
-        </is>
-      </c>
+      <c r="A9" s="43" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   종속변수를 **206종목 각각의 YZ高 비율**(0~1 연속)로 바꿨다. 29종목은 이 분포의 양 끝 꼬리로 자연히 포함된다.</t>
+      <c r="A10" s="74" t="inlineStr">
+        <is>
+          <t>그래서 이렇게 고쳤다 — **외부 변수가 아예 필요 없다**</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   검정은 단독 설명력 → **교란 통제 후 증분** → 순열검정. 섹터는 수준이 37개라 우연히도 η² 가 커지므로 귀무분포로 판정한다.</t>
+          <t xml:space="preserve">   그 종목의 YZ **순위가 시간에 대해 안 움직이는지**를 재고, **같은 잣대로 R²·RSI 와 비교**한다.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="43" t="inlineStr"/>
+      <c r="A12" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   R² 축은 206종목 전부가 양쪽을 오간다는 것을 이미 알고 있으므로 **자연스러운 대조군**이 된다.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="74" t="inlineStr">
-        <is>
-          <t>⚠ 교란의 크기 — 케인 지적이 옳았다는 증거</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   섹터가 이미 설명하고 있는 분산 η²: log_mcap 0.516 · log_rev 0.560 · age_yrs 0.259 · log_turnover 0.602</t>
+      <c r="A13" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   세 축 모두 **그날 전 종목 백분위**(0~1)로 바꿔서 잰다 — 단위를 맞추고, 시장이 함께 움직인 몫을 빼서 순수한 종목 간 상대 위치만 남긴다.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   즉 섹터를 알면 시총·매출·회전율의 절반 이상이 따라온다. **통제 없이 '섹터 때문' 이라 말할 수 없다.**</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>[A] 단독 설명력과 통제 후 — 연속변수는 스피어만 ρ, 범주형은 η²</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>변수</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C19" s="6" t="inlineStr">
-        <is>
-          <t>ρ</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>ρ²</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>회전율 통제 후 ρ</t>
-        </is>
-      </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>시총 통제 후 ρ</t>
-        </is>
-      </c>
-      <c r="G19" s="6" t="inlineStr">
-        <is>
-          <t>η²</t>
-        </is>
-      </c>
-      <c r="H19" s="6" t="inlineStr">
-        <is>
-          <t>회전율 통제 후 η²</t>
-        </is>
-      </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>시총 통제 후 η²</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
-        <is>
-          <t>순열 p</t>
-        </is>
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>[A] 지속성 — 네 가지 잣대로 같은 것을 잰다</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>축</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>ICC</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>종목간 σ</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>종목내 σ</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>1년 전이 대각%</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>시대 ρ</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>高만</t>
+        </is>
+      </c>
+      <c r="H17" s="6" t="inlineStr">
+        <is>
+          <t>低만</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>양쪽</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>YZ_60</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="n">
+        <v>0.6605125030145269</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>0.2352976246765022</v>
+      </c>
+      <c r="D18" s="10" t="n">
+        <v>0.1686898350939093</v>
+      </c>
+      <c r="E18" s="75" t="n">
+        <v>37.1704552055547</v>
+      </c>
+      <c r="F18" s="10" t="n">
+        <v>0.773144712217153</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>R²(60)</t>
+        </is>
+      </c>
+      <c r="B19" s="10" t="n">
+        <v>0.03337745918820539</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>0.05271555589863194</v>
+      </c>
+      <c r="D19" s="10" t="n">
+        <v>0.2836877697179101</v>
+      </c>
+      <c r="E19" s="75" t="n">
+        <v>19.76243017602216</v>
+      </c>
+      <c r="F19" s="10" t="n">
+        <v>0.1265602455544317</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="8" t="n">
+        <v>206</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>회전율(로그)</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="n">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="n">
+        <v>0.04747242048476285</v>
+      </c>
+      <c r="C20" s="20" t="n">
+        <v>0.063018738096076</v>
+      </c>
+      <c r="D20" s="20" t="n">
+        <v>0.282284995366429</v>
+      </c>
+      <c r="E20" s="76" t="n">
+        <v>20.65098901256574</v>
+      </c>
+      <c r="F20" s="20" t="n">
+        <v>0.203816323771662</v>
+      </c>
+      <c r="G20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="18" t="n">
         <v>206</v>
       </c>
-      <c r="C20" s="75" t="n">
-        <v>0.7738674323464441</v>
-      </c>
-      <c r="D20" s="10" t="n">
-        <v>0.5988708028464782</v>
-      </c>
-      <c r="E20" s="75" t="n">
-        <v>0.1340945203457944</v>
-      </c>
-      <c r="F20" s="75" t="n">
-        <v>0.6581384893629434</v>
-      </c>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="10" t="n"/>
-      <c r="I20" s="10" t="n"/>
-      <c r="J20" s="76" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>매출(로그)</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n">
-        <v>183</v>
-      </c>
-      <c r="C21" s="77" t="n">
-        <v>-0.6749096408208531</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <v>0.455503023272933</v>
-      </c>
-      <c r="E21" s="77" t="n">
-        <v>-0.449358909088061</v>
-      </c>
-      <c r="F21" s="77" t="n">
-        <v>-0.4290844579511722</v>
-      </c>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="10" t="n"/>
-      <c r="I21" s="10" t="n"/>
-      <c r="J21" s="76" t="n"/>
+      <c r="A21" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ICC = 순위 분산 중 **종목 간** 몫. 1.0 이면 순위가 종목마다 고정, 0.0 이면 매일 새로 뽑는 것과 같다.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>영업이익(로그·흑자만)</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n">
-        <v>168</v>
-      </c>
-      <c r="C22" s="77" t="n">
-        <v>-0.6054238571341927</v>
-      </c>
-      <c r="D22" s="10" t="n">
-        <v>0.3665380467872433</v>
-      </c>
-      <c r="E22" s="77" t="n">
-        <v>-0.3488239075526041</v>
-      </c>
-      <c r="F22" s="77" t="n">
-        <v>-0.3254387252544784</v>
-      </c>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
-      <c r="J22" s="76" t="n"/>
+      <c r="A22" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1년 전이 대각% = 5분위가 250거래일 뒤에도 같은 분위에 남는 비율. **무작위면 20%** 다.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="inlineStr">
-        <is>
-          <t>시총(로그)</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n">
-        <v>206</v>
-      </c>
-      <c r="C23" s="77" t="n">
-        <v>-0.5021767770369202</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <v>0.2521815153951887</v>
-      </c>
-      <c r="E23" s="77" t="n">
-        <v>-0.2828835878059076</v>
-      </c>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="10" t="n"/>
-      <c r="I23" s="10" t="n"/>
-      <c r="J23" s="76" t="n"/>
+      <c r="A23" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   시대 ρ = 전반기(23-24) 종목 순위 vs 후반기(25-26) 순위의 스피어만.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>업력(년·우측절단)</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n">
-        <v>204</v>
-      </c>
-      <c r="C24" s="77" t="n">
-        <v>-0.2532626350361538</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <v>0.06414196230545602</v>
-      </c>
-      <c r="E24" s="77" t="n">
-        <v>-0.2141871843911729</v>
-      </c>
-      <c r="F24" s="77" t="n">
-        <v>-0.244630208786202</v>
-      </c>
-      <c r="G24" s="10" t="n"/>
-      <c r="H24" s="10" t="n"/>
-      <c r="I24" s="10" t="n"/>
-      <c r="J24" s="76" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>영업이익률</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n">
-        <v>183</v>
-      </c>
-      <c r="C25" s="77" t="n">
-        <v>-0.1203317092993867</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <v>0.01447972026291211</v>
-      </c>
-      <c r="E25" s="77" t="n">
-        <v>-0.01615650920711505</v>
-      </c>
-      <c r="F25" s="77" t="n">
-        <v>-0.01273957688783063</v>
-      </c>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
-      <c r="I25" s="10" t="n"/>
-      <c r="J25" s="76" t="n"/>
+      <c r="A24" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   高만/低만 = 3.3년 내내 한쪽 절반에만 있었던 종목 수 (반대편에 한 번도 안 갔다).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>주가 수준</t>
-        </is>
-      </c>
-      <c r="B26" s="18" t="n">
-        <v>206</v>
-      </c>
-      <c r="C26" s="78" t="n">
-        <v>-0.1183833819804707</v>
-      </c>
-      <c r="D26" s="20" t="n">
-        <v>0.01401462512913404</v>
-      </c>
-      <c r="E26" s="78" t="n">
-        <v>-0.03669761293237209</v>
-      </c>
-      <c r="F26" s="79" t="n">
-        <v>0.140618586703343</v>
-      </c>
-      <c r="G26" s="20" t="n"/>
-      <c r="H26" s="20" t="n"/>
-      <c r="I26" s="20" t="n"/>
-      <c r="J26" s="80" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="25" t="inlineStr">
-        <is>
-          <t>섹터 (37개)</t>
-        </is>
-      </c>
-      <c r="B27" s="26" t="n">
-        <v>206</v>
-      </c>
-      <c r="C27" s="28" t="n"/>
-      <c r="D27" s="28" t="n"/>
-      <c r="E27" s="28" t="n"/>
-      <c r="F27" s="28" t="n"/>
-      <c r="G27" s="28" t="n">
-        <v>0.6120409539236005</v>
-      </c>
-      <c r="H27" s="28" t="n">
-        <v>0.3293645653429033</v>
-      </c>
-      <c r="I27" s="28" t="n">
-        <v>0.5868784135162091</v>
-      </c>
-      <c r="J27" s="81" t="n">
-        <v>0.0003332222592469177</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="25" t="inlineStr">
-        <is>
-          <t>시장 (KOSPI/KOSDAQ)</t>
-        </is>
-      </c>
-      <c r="B28" s="26" t="n">
-        <v>206</v>
-      </c>
-      <c r="C28" s="28" t="n"/>
-      <c r="D28" s="28" t="n"/>
-      <c r="E28" s="28" t="n"/>
-      <c r="F28" s="28" t="n"/>
-      <c r="G28" s="28" t="n">
-        <v>0.3783991360448898</v>
-      </c>
-      <c r="H28" s="28" t="n">
-        <v>0.1081882142326798</v>
-      </c>
-      <c r="I28" s="28" t="n">
-        <v>0.1598536679350999</v>
-      </c>
-      <c r="J28" s="81" t="n">
-        <v>0.0003332222592469177</v>
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>[B] 순위 자기상관 — 오늘 순위가 h거래일 뒤에도 유지되나</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>축</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>ρ(5일)</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>ρ(20일)</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>ρ(60일)</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>ρ(120일)</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>ρ(250일)</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>ρ(500일)</t>
+        </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="25" t="inlineStr">
-        <is>
-          <t>테크 계열 여부</t>
-        </is>
-      </c>
-      <c r="B29" s="26" t="n">
-        <v>206</v>
-      </c>
-      <c r="C29" s="28" t="n"/>
-      <c r="D29" s="28" t="n"/>
-      <c r="E29" s="28" t="n"/>
-      <c r="F29" s="28" t="n"/>
-      <c r="G29" s="28" t="n">
-        <v>0.1855391450359637</v>
-      </c>
-      <c r="H29" s="28" t="n">
-        <v>0.03544505258059982</v>
-      </c>
-      <c r="I29" s="28" t="n">
-        <v>0.08612769712434436</v>
-      </c>
-      <c r="J29" s="81" t="n">
-        <v>0.0003332222592469177</v>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>YZ_60</t>
+        </is>
+      </c>
+      <c r="B29" s="77" t="n">
+        <v>0.9897537849750553</v>
+      </c>
+      <c r="C29" s="77" t="n">
+        <v>0.9412590504854719</v>
+      </c>
+      <c r="D29" s="77" t="n">
+        <v>0.7836484105411087</v>
+      </c>
+      <c r="E29" s="77" t="n">
+        <v>0.7058507943001757</v>
+      </c>
+      <c r="F29" s="77" t="n">
+        <v>0.6255653469002024</v>
+      </c>
+      <c r="G29" s="77" t="n">
+        <v>0.5459660236599715</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="inlineStr">
-        <is>
-          <t>영업적자 여부</t>
-        </is>
-      </c>
-      <c r="B30" s="26" t="n">
-        <v>206</v>
-      </c>
-      <c r="C30" s="28" t="n"/>
-      <c r="D30" s="28" t="n"/>
-      <c r="E30" s="28" t="n"/>
-      <c r="F30" s="28" t="n"/>
-      <c r="G30" s="28" t="n">
-        <v>0.1368531639520141</v>
-      </c>
-      <c r="H30" s="28" t="n">
-        <v>0.06315174347246741</v>
-      </c>
-      <c r="I30" s="28" t="n">
-        <v>0.07512081253859247</v>
-      </c>
-      <c r="J30" s="81" t="n">
-        <v>0.0003332222592469177</v>
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>R²(60)</t>
+        </is>
+      </c>
+      <c r="B30" s="77" t="n">
+        <v>0.864991822645006</v>
+      </c>
+      <c r="C30" s="77" t="n">
+        <v>0.1650022737485345</v>
+      </c>
+      <c r="D30" s="77" t="n">
+        <v>0.01659489791914334</v>
+      </c>
+      <c r="E30" s="77" t="n">
+        <v>0.001159509602888533</v>
+      </c>
+      <c r="F30" s="78" t="n">
+        <v>-0.01472800846403322</v>
+      </c>
+      <c r="G30" s="77" t="n">
+        <v>0.0111603317765139</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="33" t="inlineStr">
-        <is>
-          <t>2010년 이전 상장</t>
-        </is>
-      </c>
-      <c r="B31" s="34" t="n">
-        <v>206</v>
-      </c>
-      <c r="C31" s="36" t="n"/>
-      <c r="D31" s="36" t="n"/>
-      <c r="E31" s="36" t="n"/>
-      <c r="F31" s="36" t="n"/>
-      <c r="G31" s="36" t="n">
-        <v>0.0647778250863848</v>
-      </c>
-      <c r="H31" s="36" t="n">
-        <v>0.0593447377557628</v>
-      </c>
-      <c r="I31" s="36" t="n">
-        <v>0.04471884977853955</v>
-      </c>
-      <c r="J31" s="82" t="n">
-        <v>0.0006664445184938354</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="43" t="inlineStr">
-        <is>
-          <t>읽기 — ⓐ 단일 최강은 **회전율**(ρ +0.774). 다만 거래량과 변동성은 정보 도착에 함께 반응하므로 **설명이라기보다 재진술**에 가깝다. 그래서 아래에서 이걸 통제한다.</t>
-        </is>
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="B31" s="79" t="n">
+        <v>0.6644161142367285</v>
+      </c>
+      <c r="C31" s="79" t="n">
+        <v>0.2163603680041757</v>
+      </c>
+      <c r="D31" s="79" t="n">
+        <v>0.02691797910159656</v>
+      </c>
+      <c r="E31" s="79" t="n">
+        <v>0.006370561430771074</v>
+      </c>
+      <c r="F31" s="79" t="n">
+        <v>0.02625729268720681</v>
+      </c>
+      <c r="G31" s="79" t="n">
+        <v>0.009243507980988797</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="43" t="inlineStr">
-        <is>
-          <t>ⓑ 규모 축에서 **매출(−0.675)이 시총(−0.502)보다 강하다.** 시총에는 기대(밸류에이션)가 섞여 있고 매출은 사업 규모 그 자체라, 사업이 작을수록 변동성이 크다는 쪽이 더 직접적이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="43" t="inlineStr">
-        <is>
-          <t>ⓒ **영업이익률(−0.120)·주가 수준(−0.118)은 사실상 무관하다.** '얼마나 잘 버느냐' 가 아니라 **'얼마나 크냐'** 가 가른다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="43" t="inlineStr">
-        <is>
-          <t>ⓓ 업력 −0.253 — 약하지만 있다. 다만 fundamentals 가 2010 시작이라 그 이전 상장이 전부 한 점에 몰리는 **우측중도절단**이라 과소추정이다.</t>
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>[C] 귀무 대조 — '高 비율' 이 매일 동전던지기보다 얼마나 퍼져 있나</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>축</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>高비율 σ(실측)</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>高비율 σ(귀무)</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>극단 비율(실측)</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>극단 비율(귀무)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="43" t="inlineStr">
-        <is>
-          <t>ⓔ 회전율을 통제해도 매출 −0.449, 섹터 η² 0.329(순열 p&lt;0.001)가 남는다 — **동어반복만은 아니다.**</t>
-        </is>
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>YZ_60</t>
+        </is>
+      </c>
+      <c r="B36" s="10" t="n">
+        <v>0.3588987752611864</v>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>0.01869139679467659</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0.2718446601941747</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="7" t="inlineStr">
+        <is>
+          <t>R²(60)</t>
+        </is>
+      </c>
+      <c r="B37" s="10" t="n">
+        <v>0.07957266159472032</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>0.01874219042323191</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>[B] 누적 설명력 (OLS R²)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>설명변수 묶음</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>R²</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>n</t>
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="n">
+        <v>0.09605454338755848</v>
+      </c>
+      <c r="C38" s="20" t="n">
+        <v>0.01768212602149145</v>
+      </c>
+      <c r="D38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   귀무 = 종목별 관측일수로 동전던지기(이항). 극단 = 高비율이 5% 미만이거나 95% 초과인 종목 비율.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>회전율</t>
-        </is>
-      </c>
-      <c r="B41" s="10" t="n">
-        <v>0.5693076051602309</v>
-      </c>
-      <c r="C41" s="8" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>시총</t>
-        </is>
-      </c>
-      <c r="B42" s="10" t="n">
-        <v>0.2563199474273175</v>
-      </c>
-      <c r="C42" s="8" t="n">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>매출</t>
-        </is>
-      </c>
-      <c r="B43" s="10" t="n">
-        <v>0.4074207973445131</v>
-      </c>
-      <c r="C43" s="8" t="n">
-        <v>183</v>
+      <c r="A41" s="80" t="inlineStr">
+        <is>
+          <t>[D] 1년 뒤 5분위 전이확률 (%) — YZ_60</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>현재</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>→1분위</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>→2분위</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>→3분위</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
+        <is>
+          <t>→4분위</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>→5분위</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>시총+매출</t>
-        </is>
-      </c>
-      <c r="B44" s="10" t="n">
-        <v>0.4348527095223351</v>
-      </c>
-      <c r="C44" s="8" t="n">
+          <t>1분위</t>
+        </is>
+      </c>
+      <c r="B44" s="81" t="n">
+        <v>54.12927955396811</v>
+      </c>
+      <c r="C44" s="81" t="n">
+        <v>25.8036414321805</v>
+      </c>
+      <c r="D44" s="81" t="n">
+        <v>11.49925951737956</v>
+      </c>
+      <c r="E44" s="81" t="n">
+        <v>5.675581496646049</v>
+      </c>
+      <c r="F44" s="81" t="n">
+        <v>2.892237999825769</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
+        <is>
+          <t>2분위</t>
+        </is>
+      </c>
+      <c r="B45" s="81" t="n">
+        <v>27.28334703413664</v>
+      </c>
+      <c r="C45" s="81" t="n">
+        <v>30.87872625795007</v>
+      </c>
+      <c r="D45" s="81" t="n">
+        <v>24.13793103448276</v>
+      </c>
+      <c r="E45" s="81" t="n">
+        <v>11.94565828754381</v>
+      </c>
+      <c r="F45" s="81" t="n">
+        <v>5.75433738588673</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>3분위</t>
+        </is>
+      </c>
+      <c r="B46" s="81" t="n">
+        <v>13.70754348674793</v>
+      </c>
+      <c r="C46" s="81" t="n">
+        <v>23.97084978093957</v>
+      </c>
+      <c r="D46" s="81" t="n">
+        <v>25.62790092395784</v>
+      </c>
+      <c r="E46" s="81" t="n">
+        <v>20.3400858890383</v>
+      </c>
+      <c r="F46" s="81" t="n">
+        <v>16.35361991931636</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>4분위</t>
+        </is>
+      </c>
+      <c r="B47" s="81" t="n">
+        <v>4.54742312689476</v>
+      </c>
+      <c r="C47" s="81" t="n">
+        <v>15.50021654395842</v>
+      </c>
+      <c r="D47" s="81" t="n">
+        <v>24.56907752273711</v>
+      </c>
+      <c r="E47" s="81" t="n">
+        <v>29.15547856214812</v>
+      </c>
+      <c r="F47" s="81" t="n">
+        <v>26.22780424426159</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>5분위</t>
+        </is>
+      </c>
+      <c r="B48" s="82" t="n">
+        <v>1.887356420000854</v>
+      </c>
+      <c r="C48" s="82" t="n">
+        <v>4.919082796020326</v>
+      </c>
+      <c r="D48" s="82" t="n">
+        <v>14.5779068277894</v>
+      </c>
+      <c r="E48" s="82" t="n">
+        <v>32.55476322644007</v>
+      </c>
+      <c r="F48" s="82" t="n">
+        <v>46.06089072974935</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="80" t="inlineStr">
+        <is>
+          <t>[D] 1년 뒤 5분위 전이확률 (%) — R²(60)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>현재</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="inlineStr">
+        <is>
+          <t>→1분위</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>→2분위</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>→3분위</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>→4분위</t>
+        </is>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
+        <is>
+          <t>→5분위</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="7" t="inlineStr">
+        <is>
+          <t>1분위</t>
+        </is>
+      </c>
+      <c r="B53" s="81" t="n">
+        <v>18.91608849325828</v>
+      </c>
+      <c r="C53" s="81" t="n">
+        <v>19.63607802068334</v>
+      </c>
+      <c r="D53" s="81" t="n">
+        <v>20.27752323602566</v>
+      </c>
+      <c r="E53" s="81" t="n">
+        <v>20.80115198324388</v>
+      </c>
+      <c r="F53" s="81" t="n">
+        <v>20.36915826678885</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="inlineStr">
+        <is>
+          <t>2분위</t>
+        </is>
+      </c>
+      <c r="B54" s="81" t="n">
+        <v>19.37046004842615</v>
+      </c>
+      <c r="C54" s="81" t="n">
+        <v>20.13576617087513</v>
+      </c>
+      <c r="D54" s="81" t="n">
+        <v>20.10549982704946</v>
+      </c>
+      <c r="E54" s="81" t="n">
+        <v>20.0492909028018</v>
+      </c>
+      <c r="F54" s="81" t="n">
+        <v>20.33898305084746</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>3분위</t>
+        </is>
+      </c>
+      <c r="B55" s="81" t="n">
+        <v>19.44420396502467</v>
+      </c>
+      <c r="C55" s="81" t="n">
+        <v>20.40948835598649</v>
+      </c>
+      <c r="D55" s="81" t="n">
+        <v>19.81213747727469</v>
+      </c>
+      <c r="E55" s="81" t="n">
+        <v>19.91602458661588</v>
+      </c>
+      <c r="F55" s="81" t="n">
+        <v>20.41814561509826</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="inlineStr">
+        <is>
+          <t>4분위</t>
+        </is>
+      </c>
+      <c r="B56" s="81" t="n">
+        <v>20.23964010727572</v>
+      </c>
+      <c r="C56" s="81" t="n">
+        <v>19.73354096375119</v>
+      </c>
+      <c r="D56" s="81" t="n">
+        <v>19.14092914611991</v>
+      </c>
+      <c r="E56" s="81" t="n">
+        <v>20.43429362401592</v>
+      </c>
+      <c r="F56" s="81" t="n">
+        <v>20.45159615883727</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
+        <is>
+          <t>5분위</t>
+        </is>
+      </c>
+      <c r="B57" s="82" t="n">
+        <v>20.75059910989387</v>
+      </c>
+      <c r="C57" s="82" t="n">
+        <v>20.13437179048271</v>
+      </c>
+      <c r="D57" s="82" t="n">
+        <v>20.3226634714139</v>
+      </c>
+      <c r="E57" s="82" t="n">
+        <v>19.27850051352277</v>
+      </c>
+      <c r="F57" s="82" t="n">
+        <v>19.51386511468675</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="80" t="inlineStr">
+        <is>
+          <t>[D] 1년 뒤 5분위 전이확률 (%) — RSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>현재</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>→1분위</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>→2분위</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>→3분위</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>→4분위</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
+        <is>
+          <t>→5분위</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="inlineStr">
+        <is>
+          <t>1분위</t>
+        </is>
+      </c>
+      <c r="B62" s="81" t="n">
+        <v>22.04228126231015</v>
+      </c>
+      <c r="C62" s="81" t="n">
+        <v>20.79922965816081</v>
+      </c>
+      <c r="D62" s="81" t="n">
+        <v>18.91276754059614</v>
+      </c>
+      <c r="E62" s="81" t="n">
+        <v>18.58887381275441</v>
+      </c>
+      <c r="F62" s="81" t="n">
+        <v>19.65684772617849</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="7" t="inlineStr">
+        <is>
+          <t>2분위</t>
+        </is>
+      </c>
+      <c r="B63" s="81" t="n">
+        <v>19.44672929564051</v>
+      </c>
+      <c r="C63" s="81" t="n">
+        <v>20.32988441058055</v>
+      </c>
+      <c r="D63" s="81" t="n">
+        <v>20.18269189142387</v>
+      </c>
+      <c r="E63" s="81" t="n">
+        <v>19.93592796224945</v>
+      </c>
+      <c r="F63" s="81" t="n">
+        <v>20.10476644010563</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="inlineStr">
+        <is>
+          <t>3분위</t>
+        </is>
+      </c>
+      <c r="B64" s="81" t="n">
+        <v>19.34688581314879</v>
+      </c>
+      <c r="C64" s="81" t="n">
+        <v>19.71453287197232</v>
+      </c>
+      <c r="D64" s="81" t="n">
+        <v>19.92214532871972</v>
+      </c>
+      <c r="E64" s="81" t="n">
+        <v>20.29411764705882</v>
+      </c>
+      <c r="F64" s="81" t="n">
+        <v>20.72231833910035</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>4분위</t>
+        </is>
+      </c>
+      <c r="B65" s="81" t="n">
+        <v>18.90407404203788</v>
+      </c>
+      <c r="C65" s="81" t="n">
+        <v>19.66525387077242</v>
+      </c>
+      <c r="D65" s="81" t="n">
+        <v>20.47833232419341</v>
+      </c>
+      <c r="E65" s="81" t="n">
+        <v>20.81134849926477</v>
+      </c>
+      <c r="F65" s="81" t="n">
+        <v>20.14099126373151</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>5분위</t>
+        </is>
+      </c>
+      <c r="B66" s="82" t="n">
+        <v>18.68202175303903</v>
+      </c>
+      <c r="C66" s="82" t="n">
+        <v>19.71422478140328</v>
+      </c>
+      <c r="D66" s="82" t="n">
+        <v>20.52889741949243</v>
+      </c>
+      <c r="E66" s="82" t="n">
+        <v>20.92557048411175</v>
+      </c>
+      <c r="F66" s="82" t="n">
+        <v>20.14928556195351</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>★ 결론</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   **YZ 수준은 이 기간(3.3년) 종목의 안정적 특성이다.** 네 잣대가 전부 같은 방향이고 차이가 크다 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ICC  YZ 0.661  vs  R² 0.033 / RSI 0.047</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      1년 뒤 순위상관  YZ +0.626  vs  R² -0.015 / RSI +0.026   (2년 뒤에도 YZ +0.546)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      1년 전이 대각  YZ 37.2%  vs  R² 19.8% / RSI 20.7%   (무작위 20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      시대 ρ  YZ 0.773  vs  R² 0.127 / RSI 0.204</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   **R²·RSI 는 정반대다** — ICC 가 0.03~0.05 이고, 60거래일이면 자기상관이 0 으로 떨어지며, 전이 대각이 정확히 무작위(20%)다. 206종목 전부가 양쪽을 오간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="43" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⇒ **12셀 표의 세 축은 성격이 같지 않다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     R²·RSI 축은 진짜 **상태** 축이다 — 같은 종목이 날마다 다른 칸에 들어간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     **YZ 축은 사실상 종목 그룹 축**이다 — YZ高 vs YZ低 비교는 같은 종목의 다른 상태를 비교하는 게 아니라 **대체로 다른 회사들을 비교**하는 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     그래서 YZ 로 갈린 두 집단 사이에 무엇이 달라 보이든, 그것은 **구성의 차이**일 수 있고 변동성의 효과라고 단정할 수 없다(주석 ⑦ 이 그 함정이었다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="43" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ 이것은 '안정적이다' 까지다. **왜 안정적인지는 이 시트가 답하지 않는다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ 다만 완전 고정은 아니다 — 177종목은 양쪽을 오갔고 종목내 σ 도 0.169 로 0 이 아니다. '고정' 이 아니라 '느리게 움직이는 서열' 이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>[참고] 어떤 회사가 변동성이 높나 — 답이 아니고, 결과도 예상 범위다</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1차 지적 때 한 횡단면 분석. 우회의 기록으로 남긴다 — 종속변수는 종목별 YZ高 비율(0~1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="30" customHeight="1">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>변수</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>ρ</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>η²</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="7" t="inlineStr">
+        <is>
+          <t>회전율(로그)</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="n">
+        <v>206</v>
+      </c>
+      <c r="C88" s="77" t="n">
+        <v>0.7746380819215893</v>
+      </c>
+      <c r="D88" s="10" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="7" t="inlineStr">
+        <is>
+          <t>매출(로그)</t>
+        </is>
+      </c>
+      <c r="B89" s="8" t="n">
         <v>183</v>
       </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="17" t="inlineStr">
-        <is>
-          <t>시총+매출+업력</t>
-        </is>
-      </c>
-      <c r="B45" s="20" t="n">
-        <v>0.454496614233509</v>
-      </c>
-      <c r="C45" s="18" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="25" t="inlineStr">
-        <is>
-          <t>회전율+시총</t>
-        </is>
-      </c>
-      <c r="B46" s="28" t="n">
-        <v>0.6095228506358021</v>
-      </c>
-      <c r="C46" s="26" t="n">
+      <c r="C89" s="78" t="n">
+        <v>-0.674437901632432</v>
+      </c>
+      <c r="D89" s="10" t="n"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="7" t="inlineStr">
+        <is>
+          <t>영업이익(로그·흑자만)</t>
+        </is>
+      </c>
+      <c r="B90" s="8" t="n">
+        <v>168</v>
+      </c>
+      <c r="C90" s="78" t="n">
+        <v>-0.6042532553929978</v>
+      </c>
+      <c r="D90" s="10" t="n"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="7" t="inlineStr">
+        <is>
+          <t>시총(로그)</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="n">
         <v>206</v>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="25" t="inlineStr">
-        <is>
-          <t>회전율+시총+매출</t>
-        </is>
-      </c>
-      <c r="B47" s="28" t="n">
-        <v>0.6845328914900005</v>
-      </c>
-      <c r="C47" s="26" t="n">
+      <c r="C91" s="78" t="n">
+        <v>-0.501744381052689</v>
+      </c>
+      <c r="D91" s="10" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>업력(년·우측절단)</t>
+        </is>
+      </c>
+      <c r="B92" s="8" t="n">
+        <v>204</v>
+      </c>
+      <c r="C92" s="78" t="n">
+        <v>-0.2537273358977453</v>
+      </c>
+      <c r="D92" s="10" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>영업이익률</t>
+        </is>
+      </c>
+      <c r="B93" s="8" t="n">
         <v>183</v>
       </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="33" t="inlineStr">
-        <is>
-          <t>연속 4변수 전부</t>
-        </is>
-      </c>
-      <c r="B48" s="36" t="n">
-        <v>0.6847139722125093</v>
-      </c>
-      <c r="C48" s="34" t="n">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="3" t="inlineStr">
-        <is>
-          <t>[C] 최종 판정 — 규모를 전부 통제한 뒤에도 섹터가 남는가</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   연속 4변수(회전율·시총·매출·업력) R² = **0.685**  →  섹터 더미 추가 R² = **0.829**   증분 **+0.144** (n=182)</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   섹터 라벨을 1,000회 섞은 귀무분포: 중앙 +0.062 · 95%분위 +0.087  →  **p = 0.0010**</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   반대 방향도 확인 — 시총 ρ 는 원자료 -0.502 에서 **섹터 내 편차만 쓰면 -0.426** 로, 거의 그대로 남는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="43" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⇒ **섹터와 규모는 서로를 대체하지 못한다. 둘 다 독립적으로 기여한다.**</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     내 초판 문장 "**사실상** 스타일 분할" 은 이 점에서 **틀렸다** — 규모를 지운 자리에 섹터만 남는 구조가 아니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     동시에 "섹터는 규모의 그림자일 뿐" 이라는 반대편 주장도 성립하지 않는다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="43" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⓕ 테크 쏠림은 착시의 주범이 **아니었다** — 테크 여부 단독 η² 0.186 → 시총 통제 후 0.086 으로 반 이상이 규모였다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     다만 **규모 효과의 세기가 진영마다 다르다**: 시총 ρ 가 테크 -0.506 vs 비테크 -0.260 로 두 배 차이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="43" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="43" t="inlineStr">
-        <is>
-          <t>⚠ 이 시트가 말하지 않는 것 — **인과가 아니다.** '무엇과 같이 움직이는가' 까지다. 그리고 ⑦ 의 '왜 방향까지 갈리는가' 는 여전히 **미규명**이다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="43" t="inlineStr">
-        <is>
-          <t>⚠ 재무는 종목별 최신 유효 연도의 DART 단면(매출 183 / 영업이익 168종목)이라 결측이 무작위가 아닐 수 있다. 업력은 위 ⓓ 의 절단 문제를 안고 있다.</t>
+      <c r="C93" s="78" t="n">
+        <v>-0.1206510519719697</v>
+      </c>
+      <c r="D93" s="10" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="17" t="inlineStr">
+        <is>
+          <t>주가 수준</t>
+        </is>
+      </c>
+      <c r="B94" s="18" t="n">
+        <v>206</v>
+      </c>
+      <c r="C94" s="83" t="n">
+        <v>-0.1165625142102794</v>
+      </c>
+      <c r="D94" s="20" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="25" t="inlineStr">
+        <is>
+          <t>섹터 (37개)</t>
+        </is>
+      </c>
+      <c r="B95" s="26" t="n">
+        <v>206</v>
+      </c>
+      <c r="C95" s="28" t="n"/>
+      <c r="D95" s="28" t="n">
+        <v>0.6128985719768835</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="33" t="inlineStr">
+        <is>
+          <t>테크 계열 여부</t>
+        </is>
+      </c>
+      <c r="B96" s="34" t="n">
+        <v>206</v>
+      </c>
+      <c r="C96" s="36" t="n"/>
+      <c r="D96" s="36" t="n">
+        <v>0.1847222808896685</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ **작고·어리고·매출 적은 회사가 더 변동적** 이라는 건 교과서적 사실이다. 이 표가 그걸 재확인했을 뿐, '무엇의 속성인가' 를 답하지는 못한다 (케인 2차 지적).</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   회전율(+0.775)이 가장 강한 것도 마찬가지다 — 거래량과 변동성은 정보 도착에 함께 반응하므로 설명이라기보다 재진술이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   섹터가 이미 먹고 있는 분산 η²: log_mcap 0.516 · log_rev 0.560 · age_yrs 0.259 · log_turnover 0.602  → 섹터와 규모는 애초에 교란돼 있다(케인 1차 지적).</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   규모 4변수 R² 0.684 → 섹터 더미 추가 0.829 (증분 +0.145, 순열 귀무 중앙 +0.062, p=0.0010) — 섹터와 규모는 서로를 대체하지 못한다.</t>
         </is>
       </c>
     </row>

--- a/docs/holdtiming/results/cell12_R2xYZxRSI.xlsx
+++ b/docs/holdtiming/results/cell12_R2xYZxRSI.xlsx
@@ -230,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -477,6 +477,12 @@
     </xf>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -862,7 +868,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성 2026-09-09 23:02 KST   ·   MagicFormula/scripts/cell12_report.py  (원자료: LLV core+extend parquet)</t>
+          <t>생성 2026-09-09 23:35 KST   ·   MagicFormula/scripts/cell12_report.py  (원자료: LLV core+extend parquet)</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2324,96 +2330,110 @@
     <row r="48">
       <c r="A48" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ⚠⚠ **원인은 미규명이다.** 초판은 여기서 '섹터·스타일 효과' 라고 단정했는데 근거가 종목명 훑기뿐이었고, 재검증(YZ상주_검증 시트)에서 **틀린 것으로 판명**됐다 —</t>
+          <t xml:space="preserve">   ⚠⚠ 초판은 여기서 '섹터·스타일 효과' 라고 단정했는데 근거가 종목명 훑기뿐이었다. 재검증(**YZ안정성_검증** 시트) 결과 —</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   YZ 상주를 가르는 것은 섹터 하나가 아니라 회전율·규모·섹터가 함께다. 그중 무엇이 방향까지 만드는지는 **이 표로 판정할 수 없다.**</t>
+          <t xml:space="preserve">   **YZ 순위는 3.3년 내내 종목에 붙어 있다**(ICC 0.66, 1년 뒤 순위상관 +0.63). 즉 YZ高 vs YZ低 는 같은 종목의 다른 상태가 아니라 **대체로 다른 회사들**이다.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   → 원인이 무엇이든 **YZ 를 방향 신호로 쓰지 말 것.** 부호 없는 지표에서 나온 방향성은 표본의 성질일 뿐 지표의 성질이 아니다. 진폭 축으로만 쓴다.</t>
+          <t xml:space="preserve">   그래서 두 집단 사이의 어떤 차이든 **구성의 차이**일 수 있다 — 변동성의 효과라고 단정할 수 없고, 그 원인이 섹터인지 규모인지도 이 표로는 못 가린다.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="43" t="inlineStr">
         <is>
-          <t>⑧ R²축은 방향은 못 가르지만 **크기**를 가른다: 기울기 중앙 R²高 +0.00236 / R²低 +0.00021 (11배), 과거60일 +10.4% / +2.1%.</t>
+          <t xml:space="preserve">   → **YZ 를 방향 신호로 쓰지 말 것.** 부호 없는 지표에서 나온 방향성은 표본 구성의 성질이지 지표의 성질이 아니다. 진폭 축으로만 쓴다.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   즉 R² 가 높다는 건 '오른다'가 아니라 '**한 방향으로 크게 간다**'는 뜻이다 — 방향은 RSI 가, 진폭은 YZ 가, 크기·순도는 R² 가 담당한다. 세 축이 겹치지 않는다.</t>
+          <t>⑧ R²축은 방향은 못 가르지만 **크기**를 가른다: 기울기 중앙 R²高 +0.00236 / R²低 +0.00021 (11배), 과거60일 +10.4% / +2.1%.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="43" t="inlineStr">
         <is>
-          <t>⑨ 사분면 4개는 건수가 23.4%~26.6% 로 고르다. 상대 분할이라 당연하지만, 덕분에 사분면 간 비교는 표본 크기 차이를 걱정하지 않아도 된다.</t>
+          <t xml:space="preserve">   즉 R² 가 높다는 건 '오른다'가 아니라 '**한 방향으로 크게 간다**'는 뜻이다 — 방향은 RSI 가, 진폭은 YZ 가, 크기·순도는 R² 가 담당한다. 세 축이 겹치지 않는다.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="43" t="inlineStr">
         <is>
-          <t>⑩ ★ **YZ 는 상태가 아니라 종목의 속성이다 — 이게 R²·RSI 와 결정적으로 다르다.**</t>
+          <t>⑨ 사분면 4개는 건수가 23.4%~26.6% 로 고르다. 상대 분할이라 당연하지만, 덕분에 사분면 간 비교는 표본 크기 차이를 걱정하지 않아도 된다.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   종목수를 보면 R²축은 高·低 모두 **206**(전 종목이 양쪽을 오간다)인데 YZ축은 **192 / 191** 다. 즉</t>
+          <t>⑩ ★ **YZ 는 상태가 아니라 종목의 속성이다 — 이게 R²·RSI 와 결정적으로 다르다.**</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   **15종목은 3.3년 내내 YZ高, 14종목은 내내 YZ低** 였다. 한 번도 반대편에 간 적이 없다.</t>
+          <t xml:space="preserve">   종목수를 보면 R²축은 高·低 모두 **206**(전 종목이 양쪽을 오간다)인데 YZ축은 **192 / 191** 다. 즉</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      항상 高 — 하이젠알앤엠 · 태성 · 펩트론 · 디앤디파마텍 · 보로노이 · 이수페타시스 · 삼천당제약 · 파두 · 브이엠 · 일진전기 · 제주반도체 · 엘앤에프 · 케어젠 · 이오테크닉스 · 유진테크</t>
+          <t xml:space="preserve">   **15종목은 3.3년 내내 YZ高, 14종목은 내내 YZ低** 였다. 한 번도 반대편에 간 적이 없다.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      항상 低 — 삼성바이오로직스 · BNK금융지주 · 에스원 · CJ제일제당 · KT&amp;G · 삼성카드 · 우리금융지주 · 대한항공 · KT · iM금융지주 · 강원랜드 · 기업은행 · LG유플러스 · 맥쿼리인프라</t>
+          <t xml:space="preserve">      항상 高 — 하이젠알앤엠 · 태성 · 펩트론 · 디앤디파마텍 · 보로노이 · 이수페타시스 · 삼천당제약 · 파두 · 브이엠 · 일진전기 · 제주반도체 · 엘앤에프 · 케어젠 · 이오테크닉스 · 유진테크</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ⚠ **다만 '무엇의 속성인가' 는 이 명단으로 답할 수 없다** — 29종목으로 섹터 37개를 가를 수 없고, 우리 유니버스는 테크 계열에 쏠려 있어 섹터와 규모가 교란된다.</t>
+          <t xml:space="preserve">      항상 低 — 삼성바이오로직스 · BNK금융지주 · 에스원 · CJ제일제당 · KT&amp;G · 삼성카드 · 우리금융지주 · 대한항공 · KT · iM금융지주 · 강원랜드 · 기업은행 · LG유플러스 · 맥쿼리인프라</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   206종목 전부를 놓고 재검증한 결과는 **YZ상주_검증 시트**에 있다. 요약: 회전율 &gt; 매출 &gt; 영업이익 &gt; 시총 &gt; 업력 순이고, 섹터는 규모로 환원되지 않는다.</t>
+          <t xml:space="preserve">   ⚠ **이 명단은 현상이지 답이 아니다** — 29종목으로 섹터 37개를 가를 수 없다. 206종목 전부로 다시 잰 결과가 **YZ안정성_검증** 시트에 있다.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   요약: **YZ 순위는 종목에 붙어 있다**(ICC 0.66 · 1년 뒤 순위상관 +0.63 · 5분위 1년 유지 37% vs 무작위 20%). R²·RSI 는 정반대로 60일이면 기억이 사라진다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⇒ **R²·RSI 는 상태 축, YZ 는 사실상 종목 그룹 축**이다. 세 축을 같은 성격으로 읽으면 안 된다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">   ※ BM(102110) 자신은 표본에서 제외했다 — 자기 대비 초과수익이 정의상 0 이고, 지수 ETF 라 내내 YZ低 에 상주해 편향이 한쪽에 몰리기 때문.</t>
         </is>
@@ -5854,15 +5874,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
@@ -6788,287 +6808,503 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>★ 결론</t>
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>[E] 창 길이를 바꾸면 안정성이 달라지나 — 중첩 0 재측정</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   **YZ 수준은 이 기간(3.3년) 종목의 안정적 특성이다.** 네 잣대가 전부 같은 방향이고 차이가 크다 —</t>
+          <t xml:space="preserve">   ⚠ **롤링 창은 자기상관을 기계적으로 만든다** — 60일 창이면 어제와 오늘이 데이터의 59/60 를 공유한다. 창이 길수록 안정적으로 *보인다*.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ICC  YZ 0.661  vs  R² 0.033 / RSI 0.047</t>
+          <t xml:space="preserve">   실제로 [A] 의 ICC 는 창에 따라 크게 움직인다 (YZ 0.519@10일 → 0.740@120일). **ICC 만으로 판단하면 안 된다.**</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      1년 뒤 순위상관  YZ +0.626  vs  R² -0.015 / RSI +0.026   (2년 뒤에도 YZ +0.546)</t>
+          <t xml:space="preserve">   그래서 겹치지 않는 n일 블록을 잡고 **각 블록의 데이터만으로** 계산해 인접 블록끼리 순위를 비교한다 — 중첩이 정확히 0 이다.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      1년 전이 대각  YZ 37.2%  vs  R² 19.8% / RSI 20.7%   (무작위 20%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      시대 ρ  YZ 0.773  vs  R² 0.127 / RSI 0.204</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   **R²·RSI 는 정반대다** — ICC 가 0.03~0.05 이고, 60거래일이면 자기상관이 0 으로 떨어지며, 전이 대각이 정확히 무작위(20%)다. 206종목 전부가 양쪽을 오간다.</t>
+          <t xml:space="preserve">   (롤링값의 블록 중앙값을 쓰면 블록 앞부분 창이 이전 블록을 물어 여전히 오염된다 — 초판이 그렇게 쟀다가 고쳤다.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="30" customHeight="1">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>창(거래일)</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="inlineStr">
+        <is>
+          <t>블록 수</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>YZ ρ(다음 블록)</t>
+        </is>
+      </c>
+      <c r="D74" s="6" t="inlineStr">
+        <is>
+          <t>YZ ρ(한 블록 건너)</t>
+        </is>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
+        <is>
+          <t>R² ρ(다음 블록)</t>
+        </is>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>R² ρ(한 블록 건너)</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="43" t="inlineStr"/>
+      <c r="A75" s="83" t="n">
+        <v>10</v>
+      </c>
+      <c r="B75" s="8" t="n">
+        <v>89</v>
+      </c>
+      <c r="C75" s="77" t="n">
+        <v>0.7607006076365543</v>
+      </c>
+      <c r="D75" s="77" t="n">
+        <v>0.7078445088843064</v>
+      </c>
+      <c r="E75" s="77" t="n">
+        <v>0.0007728983455076305</v>
+      </c>
+      <c r="F75" s="77" t="n">
+        <v>0.001988596522691421</v>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⇒ **12셀 표의 세 축은 성격이 같지 않다.**</t>
-        </is>
+      <c r="A76" s="83" t="n">
+        <v>20</v>
+      </c>
+      <c r="B76" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="C76" s="77" t="n">
+        <v>0.7813102405183503</v>
+      </c>
+      <c r="D76" s="77" t="n">
+        <v>0.7092714466755501</v>
+      </c>
+      <c r="E76" s="78" t="n">
+        <v>-0.02395108598228774</v>
+      </c>
+      <c r="F76" s="78" t="n">
+        <v>-0.01677632944869677</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     R²·RSI 축은 진짜 **상태** 축이다 — 같은 종목이 날마다 다른 칸에 들어간다.</t>
-        </is>
+      <c r="A77" s="83" t="n">
+        <v>40</v>
+      </c>
+      <c r="B77" s="8" t="n">
+        <v>22</v>
+      </c>
+      <c r="C77" s="77" t="n">
+        <v>0.7829611317028954</v>
+      </c>
+      <c r="D77" s="77" t="n">
+        <v>0.7129294372857451</v>
+      </c>
+      <c r="E77" s="77" t="n">
+        <v>0.01533611572899538</v>
+      </c>
+      <c r="F77" s="77" t="n">
+        <v>0.0194973257696304</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     **YZ 축은 사실상 종목 그룹 축**이다 — YZ高 vs YZ低 비교는 같은 종목의 다른 상태를 비교하는 게 아니라 **대체로 다른 회사들을 비교**하는 것이다.</t>
-        </is>
+      <c r="A78" s="83" t="n">
+        <v>60</v>
+      </c>
+      <c r="B78" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C78" s="77" t="n">
+        <v>0.7904436529067442</v>
+      </c>
+      <c r="D78" s="77" t="n">
+        <v>0.7058020434078417</v>
+      </c>
+      <c r="E78" s="77" t="n">
+        <v>0.03703845033932317</v>
+      </c>
+      <c r="F78" s="78" t="n">
+        <v>-0.01024092983126564</v>
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     그래서 YZ 로 갈린 두 집단 사이에 무엇이 달라 보이든, 그것은 **구성의 차이**일 수 있고 변동성의 효과라고 단정할 수 없다(주석 ⑦ 이 그 함정이었다).</t>
-        </is>
+      <c r="A79" s="84" t="n">
+        <v>120</v>
+      </c>
+      <c r="B79" s="18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C79" s="79" t="n">
+        <v>0.8038020504476253</v>
+      </c>
+      <c r="D79" s="79" t="n">
+        <v>0.6984596856993102</v>
+      </c>
+      <c r="E79" s="85" t="n">
+        <v>-0.02537439943224269</v>
+      </c>
+      <c r="F79" s="79" t="n">
+        <v>0.006008645293842654</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="43" t="inlineStr"/>
+      <c r="A80" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⇒ **창을 10일로 줄여도 결론이 안 바뀐다.** YZ 인접 블록 순위상관이 0.761~0.804 로 창에 거의 무관하다.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ⚠ 이것은 '안정적이다' 까지다. **왜 안정적인지는 이 시트가 답하지 않는다.**</t>
+          <t xml:space="preserve">     창 10일은 '지난 2주 변동성 순위' 로 '다음 2주' 를 맞히는 것인데도 0.761 다. 한 블록 건너뛰어도 0.70 대를 유지한다.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ⚠ 다만 완전 고정은 아니다 — 177종목은 양쪽을 오갔고 종목내 σ 도 0.169 로 0 이 아니다. '고정' 이 아니라 '느리게 움직이는 서열' 이다.</t>
+          <t xml:space="preserve">   ⇒ **R² 는 어느 창에서도 0 이다** — 불안정한 것도 창의 산물이 아니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ※ 이건 놀라운 결과가 아니다. **변동성 군집(volatility clustering)은 금융에서 가장 견고한 정형적 사실 중 하나**이고, ARCH·GARCH 가 존재하는 이유다.</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>[참고] 어떤 회사가 변동성이 높나 — 답이 아니고, 결과도 예상 범위다</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   1차 지적 때 한 횡단면 분석. 우회의 기록으로 남긴다 — 종속변수는 종목별 YZ高 비율(0~1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="6" t="inlineStr">
-        <is>
-          <t>변수</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="inlineStr">
-        <is>
-          <t>ρ</t>
-        </is>
-      </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>η²</t>
+      <c r="A84" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     여기서 값어치 있는 것은 'YZ 가 지속적이다' 가 아니라 **'R²·RSI 와 성격이 다르다'** 와 그것이 축 설계에 갖는 함의다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="5" t="inlineStr">
+        <is>
+          <t>★ 결론</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   **YZ 수준은 이 기간(3.3년) 종목의 안정적 특성이다.** 네 잣대가 전부 같은 방향이고 차이가 크다 —</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="7" t="inlineStr">
-        <is>
-          <t>회전율(로그)</t>
-        </is>
-      </c>
-      <c r="B88" s="8" t="n">
-        <v>206</v>
-      </c>
-      <c r="C88" s="77" t="n">
-        <v>0.7746380819215893</v>
-      </c>
-      <c r="D88" s="10" t="n"/>
+      <c r="A88" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ICC  YZ 0.661  vs  R² 0.033 / RSI 0.047</t>
+        </is>
+      </c>
     </row>
     <row r="89">
-      <c r="A89" s="7" t="inlineStr">
-        <is>
-          <t>매출(로그)</t>
-        </is>
-      </c>
-      <c r="B89" s="8" t="n">
-        <v>183</v>
-      </c>
-      <c r="C89" s="78" t="n">
-        <v>-0.674437901632432</v>
-      </c>
-      <c r="D89" s="10" t="n"/>
+      <c r="A89" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      1년 뒤 순위상관  YZ +0.626  vs  R² -0.015 / RSI +0.026   (2년 뒤에도 YZ +0.546)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
-      <c r="A90" s="7" t="inlineStr">
-        <is>
-          <t>영업이익(로그·흑자만)</t>
-        </is>
-      </c>
-      <c r="B90" s="8" t="n">
-        <v>168</v>
-      </c>
-      <c r="C90" s="78" t="n">
-        <v>-0.6042532553929978</v>
-      </c>
-      <c r="D90" s="10" t="n"/>
+      <c r="A90" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      1년 전이 대각  YZ 37.2%  vs  R² 19.8% / RSI 20.7%   (무작위 20%)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t>시총(로그)</t>
-        </is>
-      </c>
-      <c r="B91" s="8" t="n">
-        <v>206</v>
-      </c>
-      <c r="C91" s="78" t="n">
-        <v>-0.501744381052689</v>
-      </c>
-      <c r="D91" s="10" t="n"/>
+      <c r="A91" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      시대 ρ  YZ 0.773  vs  R² 0.127 / RSI 0.204</t>
+        </is>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="7" t="inlineStr">
-        <is>
-          <t>업력(년·우측절단)</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="n">
-        <v>204</v>
-      </c>
-      <c r="C92" s="78" t="n">
-        <v>-0.2537273358977453</v>
-      </c>
-      <c r="D92" s="10" t="n"/>
+      <c r="A92" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   **R²·RSI 는 정반대다** — ICC 가 0.03~0.05 이고, 60거래일이면 자기상관이 0 으로 떨어지며, 전이 대각이 정확히 무작위(20%)다. 206종목 전부가 양쪽을 오간다.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
-      <c r="A93" s="7" t="inlineStr">
-        <is>
-          <t>영업이익률</t>
-        </is>
-      </c>
-      <c r="B93" s="8" t="n">
-        <v>183</v>
-      </c>
-      <c r="C93" s="78" t="n">
-        <v>-0.1206510519719697</v>
-      </c>
-      <c r="D93" s="10" t="n"/>
+      <c r="A93" s="43" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="17" t="inlineStr">
-        <is>
-          <t>주가 수준</t>
-        </is>
-      </c>
-      <c r="B94" s="18" t="n">
-        <v>206</v>
-      </c>
-      <c r="C94" s="83" t="n">
-        <v>-0.1165625142102794</v>
-      </c>
-      <c r="D94" s="20" t="n"/>
+      <c r="A94" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⇒ **12셀 표의 세 축은 성격이 같지 않다.**</t>
+        </is>
+      </c>
     </row>
     <row r="95">
-      <c r="A95" s="25" t="inlineStr">
-        <is>
-          <t>섹터 (37개)</t>
-        </is>
-      </c>
-      <c r="B95" s="26" t="n">
-        <v>206</v>
-      </c>
-      <c r="C95" s="28" t="n"/>
-      <c r="D95" s="28" t="n">
-        <v>0.6128985719768835</v>
+      <c r="A95" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     R²·RSI 축은 진짜 **상태** 축이다 — 같은 종목이 날마다 다른 칸에 들어간다.</t>
+        </is>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="33" t="inlineStr">
-        <is>
-          <t>테크 계열 여부</t>
-        </is>
-      </c>
-      <c r="B96" s="34" t="n">
-        <v>206</v>
-      </c>
-      <c r="C96" s="36" t="n"/>
-      <c r="D96" s="36" t="n">
-        <v>0.1847222808896685</v>
+      <c r="A96" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     **YZ 축은 사실상 종목 그룹 축**이다 — YZ高 vs YZ低 비교는 같은 종목의 다른 상태를 비교하는 게 아니라 **대체로 다른 회사들을 비교**하는 것이다.</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ⚠ **작고·어리고·매출 적은 회사가 더 변동적** 이라는 건 교과서적 사실이다. 이 표가 그걸 재확인했을 뿐, '무엇의 속성인가' 를 답하지는 못한다 (케인 2차 지적).</t>
+          <t xml:space="preserve">     그래서 YZ 로 갈린 두 집단 사이에 무엇이 달라 보이든, 그것은 **구성의 차이**일 수 있고 변동성의 효과라고 단정할 수 없다(주석 ⑦ 이 그 함정이었다).</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   회전율(+0.775)이 가장 강한 것도 마찬가지다 — 거래량과 변동성은 정보 도착에 함께 반응하므로 설명이라기보다 재진술이다.</t>
-        </is>
-      </c>
+      <c r="A98" s="43" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   섹터가 이미 먹고 있는 분산 η²: log_mcap 0.516 · log_rev 0.560 · age_yrs 0.259 · log_turnover 0.602  → 섹터와 규모는 애초에 교란돼 있다(케인 1차 지적).</t>
+          <t xml:space="preserve">   ⚠ **ICC 는 창 길이에 오염된다** ([E] 참조) — 단독으로 인용하지 말 것. 창에 견고한 증거는 비중첩 블록 상관과 시대 ρ 다.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ **창을 바꿔도 이 결론은 안 바뀐다** — YZ 는 10일 창에서도 인접 블록 순위상관 0.761 이고, R² 는 어느 창에서도 0 이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ 이것은 '안정적이다' 까지다. **왜 안정적인지는 이 시트가 답하지 않는다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ 다만 완전 고정은 아니다 — 177종목은 양쪽을 오갔고 종목내 σ 도 0.169 로 0 이 아니다. '고정' 이 아니라 '느리게 움직이는 서열' 이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>[참고] 어떤 회사가 변동성이 높나 — 답이 아니고, 결과도 예상 범위다</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1차 지적 때 한 횡단면 분석. 우회의 기록으로 남긴다 — 종속변수는 종목별 YZ高 비율(0~1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="30" customHeight="1">
+      <c r="A107" s="6" t="inlineStr">
+        <is>
+          <t>변수</t>
+        </is>
+      </c>
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>ρ</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="inlineStr">
+        <is>
+          <t>η²</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="7" t="inlineStr">
+        <is>
+          <t>회전율(로그)</t>
+        </is>
+      </c>
+      <c r="B108" s="8" t="n">
+        <v>206</v>
+      </c>
+      <c r="C108" s="77" t="n">
+        <v>0.7746380819215893</v>
+      </c>
+      <c r="D108" s="10" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t>매출(로그)</t>
+        </is>
+      </c>
+      <c r="B109" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="C109" s="78" t="n">
+        <v>-0.674437901632432</v>
+      </c>
+      <c r="D109" s="10" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="7" t="inlineStr">
+        <is>
+          <t>영업이익(로그·흑자만)</t>
+        </is>
+      </c>
+      <c r="B110" s="8" t="n">
+        <v>168</v>
+      </c>
+      <c r="C110" s="78" t="n">
+        <v>-0.6042532553929978</v>
+      </c>
+      <c r="D110" s="10" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="7" t="inlineStr">
+        <is>
+          <t>시총(로그)</t>
+        </is>
+      </c>
+      <c r="B111" s="8" t="n">
+        <v>206</v>
+      </c>
+      <c r="C111" s="78" t="n">
+        <v>-0.501744381052689</v>
+      </c>
+      <c r="D111" s="10" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="7" t="inlineStr">
+        <is>
+          <t>업력(년·우측절단)</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="n">
+        <v>204</v>
+      </c>
+      <c r="C112" s="78" t="n">
+        <v>-0.2537273358977453</v>
+      </c>
+      <c r="D112" s="10" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="7" t="inlineStr">
+        <is>
+          <t>영업이익률</t>
+        </is>
+      </c>
+      <c r="B113" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="C113" s="78" t="n">
+        <v>-0.1206510519719697</v>
+      </c>
+      <c r="D113" s="10" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="17" t="inlineStr">
+        <is>
+          <t>주가 수준</t>
+        </is>
+      </c>
+      <c r="B114" s="18" t="n">
+        <v>206</v>
+      </c>
+      <c r="C114" s="85" t="n">
+        <v>-0.1165625142102794</v>
+      </c>
+      <c r="D114" s="20" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="25" t="inlineStr">
+        <is>
+          <t>섹터 (37개)</t>
+        </is>
+      </c>
+      <c r="B115" s="26" t="n">
+        <v>206</v>
+      </c>
+      <c r="C115" s="28" t="n"/>
+      <c r="D115" s="28" t="n">
+        <v>0.6128985719768835</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="33" t="inlineStr">
+        <is>
+          <t>테크 계열 여부</t>
+        </is>
+      </c>
+      <c r="B116" s="34" t="n">
+        <v>206</v>
+      </c>
+      <c r="C116" s="36" t="n"/>
+      <c r="D116" s="36" t="n">
+        <v>0.1847222808896685</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ **작고·어리고·매출 적은 회사가 더 변동적** 이라는 건 교과서적 사실이다. 이 표가 그걸 재확인했을 뿐, '무엇의 속성인가' 를 답하지는 못한다 (케인 2차 지적).</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   회전율(+0.775)이 가장 강한 것도 마찬가지다 — 거래량과 변동성은 정보 도착에 함께 반응하므로 설명이라기보다 재진술이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   섹터가 이미 먹고 있는 분산 η²: log_mcap 0.516 · log_rev 0.560 · age_yrs 0.259 · log_turnover 0.602  → 섹터와 규모는 애초에 교란돼 있다(케인 1차 지적).</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">   규모 4변수 R² 0.684 → 섹터 더미 추가 0.829 (증분 +0.145, 순열 귀무 중앙 +0.062, p=0.0010) — 섹터와 규모는 서로를 대체하지 못한다.</t>
         </is>

--- a/docs/holdtiming/results/cell12_R2xYZxRSI.xlsx
+++ b/docs/holdtiming/results/cell12_R2xYZxRSI.xlsx
@@ -230,7 +230,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -485,6 +485,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -868,7 +877,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성 2026-09-09 23:35 KST   ·   MagicFormula/scripts/cell12_report.py  (원자료: LLV core+extend parquet)</t>
+          <t>생성 2026-09-09 23:42 KST   ·   MagicFormula/scripts/cell12_report.py  (원자료: LLV core+extend parquet)</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I120"/>
+  <dimension ref="A1:I164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -7010,301 +7019,676 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>★ 결론</t>
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>[F] 무엇을 재기에 안정적인가 — 성분 분해</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   **YZ 수준은 이 기간(3.3년) 종목의 안정적 특성이다.** 네 잣대가 전부 같은 방향이고 차이가 크다 —</t>
+          <t xml:space="preserve">   YZ 는 세 성분의 합이고 **셋 다 2차 모멘트(분산·제곱)** 다: σ²_YZ = V(갭) + k·V(장중 드리프트) + (1−k)·V(장중 레인지).</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ICC  YZ 0.661  vs  R² 0.033 / RSI 0.047</t>
+          <t xml:space="preserve">   2차 모멘트에는 **부호가 없다** — ±5% 로 움직이면 오르든 내리든 같은 값이다. 즉 YZ 가 재는 것은 방향이 아니라 **하루 움직임의 크기(scale)** 하나뿐이다.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      1년 뒤 순위상관  YZ +0.626  vs  R² -0.015 / RSI +0.026   (2년 뒤에도 YZ +0.546)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      1년 전이 대각  YZ 37.2%  vs  R² 19.8% / RSI 20.7%   (무작위 20%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">      시대 ρ  YZ 0.773  vs  R² 0.127 / RSI 0.204</t>
+          <t xml:space="preserve">   아래는 중첩 0 · 60일 블록에서 성분별로 따로 잰 지속성이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="30" customHeight="1">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>지표</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>ρ(다음 블록)</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>ρ(한 블록 건너)</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   **R²·RSI 는 정반대다** — ICC 가 0.03~0.05 이고, 60거래일이면 자기상관이 0 으로 떨어지며, 전이 대각이 정확히 무작위(20%)다. 206종목 전부가 양쪽을 오간다.</t>
-        </is>
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t>YZ</t>
+        </is>
+      </c>
+      <c r="B92" s="77" t="n">
+        <v>0.7904436529067442</v>
+      </c>
+      <c r="C92" s="77" t="n">
+        <v>0.7058020434078417</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="43" t="inlineStr"/>
+      <c r="A93" s="7" t="inlineStr">
+        <is>
+          <t>├ 갭 (overnight)</t>
+        </is>
+      </c>
+      <c r="B93" s="77" t="n">
+        <v>0.6561481076992204</v>
+      </c>
+      <c r="C93" s="77" t="n">
+        <v>0.571640059872469</v>
+      </c>
     </row>
     <row r="94">
-      <c r="A94" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⇒ **12셀 표의 세 축은 성격이 같지 않다.**</t>
-        </is>
+      <c r="A94" s="7" t="inlineStr">
+        <is>
+          <t>├ 장중 드리프트 (O→C)</t>
+        </is>
+      </c>
+      <c r="B94" s="77" t="n">
+        <v>0.7255124517601879</v>
+      </c>
+      <c r="C94" s="77" t="n">
+        <v>0.6392243905407318</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     R²·RSI 축은 진짜 **상태** 축이다 — 같은 종목이 날마다 다른 칸에 들어간다.</t>
-        </is>
+      <c r="A95" s="17" t="inlineStr">
+        <is>
+          <t>└ 장중 레인지 (RS)</t>
+        </is>
+      </c>
+      <c r="B95" s="79" t="n">
+        <v>0.8063033337941801</v>
+      </c>
+      <c r="C95" s="79" t="n">
+        <v>0.7162495715549841</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     **YZ 축은 사실상 종목 그룹 축**이다 — YZ高 vs YZ低 비교는 같은 종목의 다른 상태를 비교하는 게 아니라 **대체로 다른 회사들을 비교**하는 것이다.</t>
-        </is>
+      <c r="A96" s="25" t="inlineStr">
+        <is>
+          <t>단순 종가변동성 (CC)</t>
+        </is>
+      </c>
+      <c r="B96" s="86" t="n">
+        <v>0.7166520443414675</v>
+      </c>
+      <c r="C96" s="86" t="n">
+        <v>0.6434384130714084</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     그래서 YZ 로 갈린 두 집단 사이에 무엇이 달라 보이든, 그것은 **구성의 차이**일 수 있고 변동성의 효과라고 단정할 수 없다(주석 ⑦ 이 그 함정이었다).</t>
-        </is>
+      <c r="A97" s="25" t="inlineStr">
+        <is>
+          <t>평균 |일간수익률|</t>
+        </is>
+      </c>
+      <c r="B97" s="86" t="n">
+        <v>0.7671495988178935</v>
+      </c>
+      <c r="C97" s="86" t="n">
+        <v>0.6901067493484102</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="43" t="inlineStr"/>
+      <c r="A98" s="25" t="inlineStr">
+        <is>
+          <t>고저 레인지 (H−L)/C</t>
+        </is>
+      </c>
+      <c r="B98" s="86" t="n">
+        <v>0.8297734993232234</v>
+      </c>
+      <c r="C98" s="86" t="n">
+        <v>0.737023336252396</v>
+      </c>
     </row>
     <row r="99">
-      <c r="A99" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⚠ **ICC 는 창 길이에 오염된다** ([E] 참조) — 단독으로 인용하지 말 것. 창에 견고한 증거는 비중첩 블록 상관과 시대 ρ 다.</t>
-        </is>
+      <c r="A99" s="33" t="inlineStr">
+        <is>
+          <t>시총</t>
+        </is>
+      </c>
+      <c r="B99" s="87" t="n">
+        <v>0.9843777872821859</v>
+      </c>
+      <c r="C99" s="87" t="n">
+        <v>0.9654866627502496</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⚠ **창을 바꿔도 이 결론은 안 바뀐다** — YZ 는 10일 창에서도 인접 블록 순위상관 0.761 이고, R² 는 어느 창에서도 0 이다.</t>
-        </is>
+      <c r="A100" s="7" t="inlineStr">
+        <is>
+          <t>R² (추세 순도)</t>
+        </is>
+      </c>
+      <c r="B100" s="77" t="n">
+        <v>0.03703845033932317</v>
+      </c>
+      <c r="C100" s="78" t="n">
+        <v>-0.01024092983126564</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⚠ 이것은 '안정적이다' 까지다. **왜 안정적인지는 이 시트가 답하지 않는다.**</t>
-        </is>
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t>├ |기울기| b</t>
+        </is>
+      </c>
+      <c r="B101" s="77" t="n">
+        <v>0.1542171672792637</v>
+      </c>
+      <c r="C101" s="77" t="n">
+        <v>0.09368593939261444</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⚠ 다만 완전 고정은 아니다 — 177종목은 양쪽을 오갔고 종목내 σ 도 0.169 로 0 이 아니다. '고정' 이 아니라 '느리게 움직이는 서열' 이다.</t>
-        </is>
+      <c r="A102" s="17" t="inlineStr">
+        <is>
+          <t>└ 잔차 σ (추세 제거 후)</t>
+        </is>
+      </c>
+      <c r="B102" s="79" t="n">
+        <v>0.4983672053989459</v>
+      </c>
+      <c r="C102" s="79" t="n">
+        <v>0.4754239048519299</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
-        <is>
-          <t>[참고] 어떤 회사가 변동성이 높나 — 답이 아니고, 결과도 예상 범위다</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   1차 지적 때 한 횡단면 분석. 우회의 기록으로 남긴다 — 종속변수는 종목별 YZ高 비율(0~1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="107" ht="30" customHeight="1">
-      <c r="A107" s="6" t="inlineStr">
-        <is>
-          <t>변수</t>
-        </is>
-      </c>
-      <c r="B107" s="6" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C107" s="6" t="inlineStr">
+      <c r="A104" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   같은 블록 안에서 서로 얼마나 같은 것을 재나</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>쌍</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="inlineStr">
         <is>
           <t>ρ</t>
         </is>
       </c>
-      <c r="D107" s="6" t="inlineStr">
-        <is>
-          <t>η²</t>
-        </is>
+    </row>
+    <row r="107">
+      <c r="A107" s="7" t="inlineStr">
+        <is>
+          <t>YZ × 단순 종가변동성 (CC)</t>
+        </is>
+      </c>
+      <c r="B107" s="77" t="n">
+        <v>0.9379540798345463</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="inlineStr">
         <is>
-          <t>회전율(로그)</t>
-        </is>
-      </c>
-      <c r="B108" s="8" t="n">
-        <v>206</v>
-      </c>
-      <c r="C108" s="77" t="n">
-        <v>0.7746380819215893</v>
-      </c>
-      <c r="D108" s="10" t="n"/>
+          <t>YZ × 평균 |일간수익률|</t>
+        </is>
+      </c>
+      <c r="B108" s="77" t="n">
+        <v>0.9405423725644668</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="inlineStr">
         <is>
-          <t>매출(로그)</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="n">
-        <v>183</v>
-      </c>
-      <c r="C109" s="78" t="n">
-        <v>-0.674437901632432</v>
-      </c>
-      <c r="D109" s="10" t="n"/>
+          <t>YZ × 고저 레인지 (H−L)/C</t>
+        </is>
+      </c>
+      <c r="B109" s="77" t="n">
+        <v>0.9731691974049852</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="inlineStr">
         <is>
-          <t>영업이익(로그·흑자만)</t>
-        </is>
-      </c>
-      <c r="B110" s="8" t="n">
-        <v>168</v>
-      </c>
-      <c r="C110" s="78" t="n">
-        <v>-0.6042532553929978</v>
-      </c>
-      <c r="D110" s="10" t="n"/>
+          <t>YZ × └ 잔차 σ (추세 제거 후)</t>
+        </is>
+      </c>
+      <c r="B110" s="77" t="n">
+        <v>0.8054894572714477</v>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="7" t="inlineStr">
-        <is>
-          <t>시총(로그)</t>
-        </is>
-      </c>
-      <c r="B111" s="8" t="n">
-        <v>206</v>
-      </c>
-      <c r="C111" s="78" t="n">
-        <v>-0.501744381052689</v>
-      </c>
-      <c r="D111" s="10" t="n"/>
+      <c r="A111" s="17" t="inlineStr">
+        <is>
+          <t>YZ × 시총</t>
+        </is>
+      </c>
+      <c r="B111" s="85" t="n">
+        <v>-0.3664518604630352</v>
+      </c>
     </row>
     <row r="112">
-      <c r="A112" s="7" t="inlineStr">
-        <is>
-          <t>업력(년·우측절단)</t>
-        </is>
-      </c>
-      <c r="B112" s="8" t="n">
-        <v>204</v>
-      </c>
-      <c r="C112" s="78" t="n">
-        <v>-0.2537273358977453</v>
-      </c>
-      <c r="D112" s="10" t="n"/>
+      <c r="A112" s="25" t="inlineStr">
+        <is>
+          <t>R² (추세 순도) × ├ |기울기| b</t>
+        </is>
+      </c>
+      <c r="B112" s="86" t="n">
+        <v>0.8506751761244873</v>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" s="7" t="inlineStr">
-        <is>
-          <t>영업이익률</t>
-        </is>
-      </c>
-      <c r="B113" s="8" t="n">
-        <v>183</v>
-      </c>
-      <c r="C113" s="78" t="n">
-        <v>-0.1206510519719697</v>
-      </c>
-      <c r="D113" s="10" t="n"/>
+      <c r="A113" s="33" t="inlineStr">
+        <is>
+          <t>R² (추세 순도) × └ 잔차 σ (추세 제거 후)</t>
+        </is>
+      </c>
+      <c r="B113" s="88" t="n">
+        <v>-0.04265174146742142</v>
+      </c>
     </row>
     <row r="114">
-      <c r="A114" s="17" t="inlineStr">
-        <is>
-          <t>주가 수준</t>
-        </is>
-      </c>
-      <c r="B114" s="18" t="n">
-        <v>206</v>
-      </c>
-      <c r="C114" s="85" t="n">
-        <v>-0.1165625142102794</v>
-      </c>
-      <c r="D114" s="20" t="n"/>
+      <c r="A114" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   읽기 — ⓐ **세 성분이 전부 지속적이다**(갭 0.66 · 드리프트 0.73 · 레인지 0.81). 한 채널의 특성이 아니라 전방위다.</t>
+        </is>
+      </c>
     </row>
     <row r="115">
-      <c r="A115" s="25" t="inlineStr">
-        <is>
-          <t>섹터 (37개)</t>
-        </is>
-      </c>
-      <c r="B115" s="26" t="n">
-        <v>206</v>
-      </c>
-      <c r="C115" s="28" t="n"/>
-      <c r="D115" s="28" t="n">
-        <v>0.6128985719768835</v>
+      <c r="A115" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⓑ **YZ 식이 특별해서가 아니다.** 단순 종가변동성 0.72 · 평균 |수익률| 0.77 · 고저 레인지 0.83 으로 다 비슷하고, 블록 내 상관이 0.94~0.97 이다 —</t>
+        </is>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="33" t="inlineStr">
-        <is>
-          <t>테크 계열 여부</t>
-        </is>
-      </c>
-      <c r="B116" s="34" t="n">
-        <v>206</v>
-      </c>
-      <c r="C116" s="36" t="n"/>
-      <c r="D116" s="36" t="n">
-        <v>0.1847222808896685</v>
+      <c r="A116" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     **어떤 방식으로 재든 '하루 움직임의 크기' 는 지속적이다.** YZ 는 그걸 좀 더 정밀하게 잴 뿐이다.</t>
+        </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ⚠ **작고·어리고·매출 적은 회사가 더 변동적** 이라는 건 교과서적 사실이다. 이 표가 그걸 재확인했을 뿐, '무엇의 속성인가' 를 답하지는 못한다 (케인 2차 지적).</t>
+          <t xml:space="preserve">   ⓒ ★ **R² 가 왜 아닌지가 산수로 설명된다.** R² ≈ b²Var(x) / (b²Var(x) + σ²) 를 분자·분모로 쪼개면 —</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   회전율(+0.775)이 가장 강한 것도 마찬가지다 — 거래량과 변동성은 정보 도착에 함께 반응하므로 설명이라기보다 재진술이다.</t>
+          <t xml:space="preserve">        **분모 σ(잔차 변동성) ρ = 0.498** → 지속적 (변동성이니까 당연하다)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   섹터가 이미 먹고 있는 분산 η²: log_mcap 0.516 · log_rev 0.560 · age_yrs 0.259 · log_turnover 0.602  → 섹터와 규모는 애초에 교란돼 있다(케인 1차 지적).</t>
+          <t xml:space="preserve">        **분자 |b|(기울기) ρ = 0.154** → 거의 지속 없음</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        그런데 R² 를 실제로 결정하는 건 분자다 — 블록 내 상관이 R²×|b| **+0.851** vs R²×잔차σ **−0.043**.</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     ⇒ **YZ 는 분모만 재고, R² 는 분자에 지배된다.** 분모는 종목의 성질이고 분자는 그때그때의 국면이라, 두 축의 성격 차이가 여기서 갈린다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⓓ 시총은 ρ 0.984 로 거의 상수인데 YZ 와의 블록 내 상관은 **−0.366** 뿐이다 — YZ 의 지속성이 시총에서 오는 게 아니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>[G] 절대 수준 vs 순위 — 우리가 가르는 건 순위다</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   시장 전체 YZ_60 중앙값은 0.0221(2023-04-11) → 0.0588(2026-08-03) 로 **2.66배** 움직였다. 절대 수준은 전혀 안정적이지 않다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   그런데 그 최저일과 최고일(3.4년 간격) 사이에도 종목 **순위** 상관은 ρ = 0.486 이고, 전·후반기로 나누면 0.776 다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⇒ **시장 변동성이 통째로 오르내려도 '누가 더 흔들리는가' 의 서열은 유지된다.** 우리 분할(그날 전 종목 중앙값)은 절대 수준이 아니라 이 서열을 가른다 — 그래서 안정적으로 나오는 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ 다만 0.486 은 완전하지 않다 — 극단적으로 다른 두 시점을 비교하면 서열도 절반쯤은 뒤섞인다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>★ 결론</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   **YZ 수준은 이 기간(3.3년) 종목의 안정적 특성이다.** 네 잣대가 전부 같은 방향이고 차이가 크다 —</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ICC  YZ 0.661  vs  R² 0.033 / RSI 0.047</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      1년 뒤 순위상관  YZ +0.626  vs  R² -0.015 / RSI +0.026   (2년 뒤에도 YZ +0.546)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      1년 전이 대각  YZ 37.2%  vs  R² 19.8% / RSI 20.7%   (무작위 20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      시대 ρ  YZ 0.773  vs  R² 0.127 / RSI 0.204</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   **R²·RSI 는 정반대다** — ICC 가 0.03~0.05 이고, 60거래일이면 자기상관이 0 으로 떨어지며, 전이 대각이 정확히 무작위(20%)다. 206종목 전부가 양쪽을 오간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="43" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⇒ **12셀 표의 세 축은 성격이 같지 않다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     R²·RSI 축은 진짜 **상태** 축이다 — 같은 종목이 날마다 다른 칸에 들어간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     **YZ 축은 사실상 종목 그룹 축**이다 — YZ高 vs YZ低 비교는 같은 종목의 다른 상태를 비교하는 게 아니라 **대체로 다른 회사들을 비교**하는 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     그래서 YZ 로 갈린 두 집단 사이에 무엇이 달라 보이든, 그것은 **구성의 차이**일 수 있고 변동성의 효과라고 단정할 수 없다(주석 ⑦ 이 그 함정이었다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="43" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ **ICC 는 창 길이에 오염된다** ([E] 참조) — 단독으로 인용하지 말 것. 창에 견고한 증거는 비중첩 블록 상관과 시대 ρ 다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ **창을 바꿔도 이 결론은 안 바뀐다** — YZ 는 10일 창에서도 인접 블록 순위상관 0.761 이고, R² 는 어느 창에서도 0 이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ 이것은 '안정적이다' 까지다. **왜 안정적인지는 이 시트가 답하지 않는다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ 다만 완전 고정은 아니다 — 177종목은 양쪽을 오갔고 종목내 σ 도 0.169 로 0 이 아니다. '고정' 이 아니라 '느리게 움직이는 서열' 이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>[참고] 어떤 회사가 변동성이 높나 — 답이 아니고, 결과도 예상 범위다</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1차 지적 때 한 횡단면 분석. 우회의 기록으로 남긴다 — 종속변수는 종목별 YZ高 비율(0~1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="30" customHeight="1">
+      <c r="A151" s="6" t="inlineStr">
+        <is>
+          <t>변수</t>
+        </is>
+      </c>
+      <c r="B151" s="6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C151" s="6" t="inlineStr">
+        <is>
+          <t>ρ</t>
+        </is>
+      </c>
+      <c r="D151" s="6" t="inlineStr">
+        <is>
+          <t>η²</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="7" t="inlineStr">
+        <is>
+          <t>회전율(로그)</t>
+        </is>
+      </c>
+      <c r="B152" s="8" t="n">
+        <v>206</v>
+      </c>
+      <c r="C152" s="77" t="n">
+        <v>0.7746380819215893</v>
+      </c>
+      <c r="D152" s="10" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t>매출(로그)</t>
+        </is>
+      </c>
+      <c r="B153" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="C153" s="78" t="n">
+        <v>-0.674437901632432</v>
+      </c>
+      <c r="D153" s="10" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="7" t="inlineStr">
+        <is>
+          <t>영업이익(로그·흑자만)</t>
+        </is>
+      </c>
+      <c r="B154" s="8" t="n">
+        <v>168</v>
+      </c>
+      <c r="C154" s="78" t="n">
+        <v>-0.6042532553929978</v>
+      </c>
+      <c r="D154" s="10" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="7" t="inlineStr">
+        <is>
+          <t>시총(로그)</t>
+        </is>
+      </c>
+      <c r="B155" s="8" t="n">
+        <v>206</v>
+      </c>
+      <c r="C155" s="78" t="n">
+        <v>-0.501744381052689</v>
+      </c>
+      <c r="D155" s="10" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="7" t="inlineStr">
+        <is>
+          <t>업력(년·우측절단)</t>
+        </is>
+      </c>
+      <c r="B156" s="8" t="n">
+        <v>204</v>
+      </c>
+      <c r="C156" s="78" t="n">
+        <v>-0.2537273358977453</v>
+      </c>
+      <c r="D156" s="10" t="n"/>
+    </row>
+    <row r="157">
+      <c r="A157" s="7" t="inlineStr">
+        <is>
+          <t>영업이익률</t>
+        </is>
+      </c>
+      <c r="B157" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="C157" s="78" t="n">
+        <v>-0.1206510519719697</v>
+      </c>
+      <c r="D157" s="10" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="17" t="inlineStr">
+        <is>
+          <t>주가 수준</t>
+        </is>
+      </c>
+      <c r="B158" s="18" t="n">
+        <v>206</v>
+      </c>
+      <c r="C158" s="85" t="n">
+        <v>-0.1165625142102794</v>
+      </c>
+      <c r="D158" s="20" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="25" t="inlineStr">
+        <is>
+          <t>섹터 (37개)</t>
+        </is>
+      </c>
+      <c r="B159" s="26" t="n">
+        <v>206</v>
+      </c>
+      <c r="C159" s="28" t="n"/>
+      <c r="D159" s="28" t="n">
+        <v>0.6128985719768835</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="33" t="inlineStr">
+        <is>
+          <t>테크 계열 여부</t>
+        </is>
+      </c>
+      <c r="B160" s="34" t="n">
+        <v>206</v>
+      </c>
+      <c r="C160" s="36" t="n"/>
+      <c r="D160" s="36" t="n">
+        <v>0.1847222808896685</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ **작고·어리고·매출 적은 회사가 더 변동적** 이라는 건 교과서적 사실이다. 이 표가 그걸 재확인했을 뿐, '무엇의 속성인가' 를 답하지는 못한다 (케인 2차 지적).</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   회전율(+0.775)이 가장 강한 것도 마찬가지다 — 거래량과 변동성은 정보 도착에 함께 반응하므로 설명이라기보다 재진술이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   섹터가 이미 먹고 있는 분산 η²: log_mcap 0.516 · log_rev 0.560 · age_yrs 0.259 · log_turnover 0.602  → 섹터와 규모는 애초에 교란돼 있다(케인 1차 지적).</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">   규모 4변수 R² 0.684 → 섹터 더미 추가 0.829 (증분 +0.145, 순열 귀무 중앙 +0.062, p=0.0010) — 섹터와 규모는 서로를 대체하지 못한다.</t>
         </is>

--- a/docs/holdtiming/results/cell12_R2xYZxRSI.xlsx
+++ b/docs/holdtiming/results/cell12_R2xYZxRSI.xlsx
@@ -877,7 +877,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성 2026-09-09 23:42 KST   ·   MagicFormula/scripts/cell12_report.py  (원자료: LLV core+extend parquet)</t>
+          <t>생성 2026-09-10 06:44 KST   ·   MagicFormula/scripts/cell12_report.py  (원자료: LLV core+extend parquet)</t>
         </is>
       </c>
     </row>
@@ -961,7 +961,7 @@
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   수익률 시트의 노란 [전체 기준선] 행은 12셀을 합친 전체 관측의 값이다. 20일 중앙값이 **-1.40%** 다.</t>
+          <t xml:space="preserve">   수익률 시트의 노란 [전체 기준선] 행은 12셀을 합친 전체 관측의 값이다. 20일 중앙값이 **-1.41%** 다.</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   (평균으로 재면 기준선이 +0.10% 로 거의 0 인 것이 같은 사실의 뒷면이다 — 평균 종목 ≈ BM, 중앙 종목 &lt; BM).</t>
+          <t xml:space="preserve">   (평균으로 재면 기준선이 +0.09% 로 거의 0 인 것이 같은 사실의 뒷면이다 — 평균 종목 ≈ BM, 중앙 종목 &lt; BM).</t>
         </is>
       </c>
     </row>
@@ -1059,14 +1059,14 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ◎ 과매도 4셀 전부 양(+) : Δ중앙 +2.0%p~+3.3%p / Δ평균 +1.7%p~+5.1%p. 네 셀 모두, 거의 모든 창에서 양수다.</t>
+          <t xml:space="preserve">   ◎ 과매도 4셀 전부 양(+) : Δ중앙 +2.0%p~+3.3%p / Δ평균 +1.7%p~+5.0%p. 네 셀 모두, 거의 모든 창에서 양수다.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">      가장 강한 것은 **R²高·YZ高·과매도**(Δ중앙 +3.3%p, Δ평균 +5.1%p) — 곧게 내리던 고변동 종목의 반등이다. 다만 1,055건뿐이다.</t>
+          <t xml:space="preserve">      가장 강한 것은 **R²高·YZ高·과매도**(Δ중앙 +3.3%p, Δ평균 +5.0%p) — 곧게 내리던 고변동 종목의 반등이다. 다만 1,056건뿐이다.</t>
         </is>
       </c>
     </row>
@@ -1087,14 +1087,14 @@
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ○ R²低·YZ高·중간 : Δ가 양쪽 다 양수이고 창이 길수록 커진다(20일 +0.2%/+1.5%p → 120일 +1.8%/+8.4%p). 표본도 35,532건으로 크다.</t>
+          <t xml:space="preserve">   ○ R²低·YZ高·중간 : Δ가 양쪽 다 양수이고 창이 길수록 커진다(20일 +0.2%/+1.5%p → 120일 +1.8%/+8.4%p). 표본도 35,583건으로 크다.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">   △ YZ高·과매수 : 평균만 크게 양수(+4.2%p / +2.8%p), 중앙값은 ≈0(+0.0%p / -0.6%p). 위 한계 2 참조 — 아직 규칙으로 쓰지 말 것.</t>
+          <t xml:space="preserve">   △ YZ高·과매수 : 평균만 크게 양수(+4.2%p / +2.9%p), 중앙값은 ≈0(+0.0%p / -0.6%p). 위 한계 2 참조 — 아직 규칙으로 쓰지 말 것.</t>
         </is>
       </c>
     </row>
@@ -1150,7 +1150,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>전 기간 유효 관측 167,208건 (종목×일)   ·   '상승비율' = 회귀 기울기 b&gt;0 인 비율</t>
+          <t>전 기간 유효 관측 167,414건 (종목×일)   ·   '상승비율' = 회귀 기울기 b&gt;0 인 비율</t>
         </is>
       </c>
     </row>
@@ -1223,37 +1223,37 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C5" s="9" t="n">
-        <v>0.006309506722166403</v>
+        <v>0.006307716200556704</v>
       </c>
       <c r="D5" s="8" t="n">
         <v>116</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.7191663627246904</v>
+        <v>0.7189342417554233</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.03434456463160038</v>
+        <v>0.03435876992179014</v>
       </c>
       <c r="G5" s="11" t="n">
-        <v>27.20413438530548</v>
+        <v>27.20566436361801</v>
       </c>
       <c r="H5" s="12" t="n">
-        <v>-0.005807540916613316</v>
+        <v>-0.00581221711861123</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>0.01990521327014218</v>
+        <v>0.01988636363636364</v>
       </c>
       <c r="J5" s="14" t="n">
-        <v>-0.3168278529980658</v>
+        <v>-0.3168934586627756</v>
       </c>
       <c r="K5" s="8" t="n">
         <v>782</v>
       </c>
       <c r="L5" s="8" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="6">
@@ -1263,37 +1263,37 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>38986</v>
+        <v>39033</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>0.233158700540644</v>
+        <v>0.2331525439927366</v>
       </c>
       <c r="D6" s="8" t="n">
         <v>190</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.6853473965712442</v>
+        <v>0.6852450500929893</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.04022241071159036</v>
+        <v>0.04024479174454563</v>
       </c>
       <c r="G6" s="11" t="n">
-        <v>51.67520591703067</v>
+        <v>51.67319020742134</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>0.004443321984879348</v>
+        <v>0.004436944047591978</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>0.6619299235623044</v>
+        <v>0.6611841262521456</v>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.2283185840707964</v>
+        <v>0.2278481012658229</v>
       </c>
       <c r="K6" s="8" t="n">
         <v>18943</v>
       </c>
       <c r="L6" s="8" t="n">
-        <v>20043</v>
+        <v>20090</v>
       </c>
     </row>
     <row r="7">
@@ -1306,7 +1306,7 @@
         <v>4506</v>
       </c>
       <c r="C7" s="19" t="n">
-        <v>0.02694847136500646</v>
+        <v>0.02691531174214821</v>
       </c>
       <c r="D7" s="18" t="n">
         <v>165</v>
@@ -1346,7 +1346,7 @@
         <v>1401</v>
       </c>
       <c r="C8" s="27" t="n">
-        <v>0.0083787857040333</v>
+        <v>0.008368475754715854</v>
       </c>
       <c r="D8" s="26" t="n">
         <v>142</v>
@@ -1383,37 +1383,37 @@
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>35397</v>
+        <v>35451</v>
       </c>
       <c r="C9" s="27" t="n">
-        <v>0.211694416535094</v>
+        <v>0.2117564839260755</v>
       </c>
       <c r="D9" s="26" t="n">
         <v>186</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>0.6602839430029476</v>
+        <v>0.6600163575746547</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>0.02225763840568366</v>
+        <v>0.02226424060546573</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>48.93128115800169</v>
+        <v>48.929386019612</v>
       </c>
       <c r="H9" s="30" t="n">
-        <v>-0.001538427534750311</v>
+        <v>-0.001539018322350396</v>
       </c>
       <c r="I9" s="31" t="n">
-        <v>0.4468175269090601</v>
+        <v>0.4467857042114468</v>
       </c>
       <c r="J9" s="32" t="n">
-        <v>-0.04357625845229152</v>
+        <v>-0.04365904365904361</v>
       </c>
       <c r="K9" s="26" t="n">
         <v>18608</v>
       </c>
       <c r="L9" s="26" t="n">
-        <v>16789</v>
+        <v>16843</v>
       </c>
     </row>
     <row r="10">
@@ -1423,37 +1423,37 @@
         </is>
       </c>
       <c r="B10" s="34" t="n">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="C10" s="35" t="n">
-        <v>0.01435936079613416</v>
+        <v>0.0143476650698269</v>
       </c>
       <c r="D10" s="34" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E10" s="36" t="n">
-        <v>0.6960340781730814</v>
+        <v>0.6959310335807269</v>
       </c>
       <c r="F10" s="36" t="n">
-        <v>0.02219749579195968</v>
+        <v>0.02219844519532168</v>
       </c>
       <c r="G10" s="37" t="n">
-        <v>74.85702592347752</v>
+        <v>74.85564500324887</v>
       </c>
       <c r="H10" s="38" t="n">
-        <v>0.004006025752432145</v>
+        <v>0.004006728399117657</v>
       </c>
       <c r="I10" s="39" t="n">
-        <v>0.9775093710953769</v>
+        <v>0.97751873438801</v>
       </c>
       <c r="J10" s="40" t="n">
-        <v>0.3286290322580645</v>
+        <v>0.3286571456111039</v>
       </c>
       <c r="K10" s="34" t="n">
         <v>795</v>
       </c>
       <c r="L10" s="34" t="n">
-        <v>1606</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="11">
@@ -1466,7 +1466,7 @@
         <v>824</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>0.004927993875891106</v>
+        <v>0.004921930065585913</v>
       </c>
       <c r="D11" s="8" t="n">
         <v>133</v>
@@ -1503,37 +1503,37 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>35532</v>
+        <v>35583</v>
       </c>
       <c r="C12" s="9" t="n">
-        <v>0.2125017941725276</v>
+        <v>0.2125449484511451</v>
       </c>
       <c r="D12" s="8" t="n">
         <v>191</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>0.150926666391757</v>
+        <v>0.1507921683645987</v>
       </c>
       <c r="F12" s="10" t="n">
-        <v>0.03764399886264937</v>
+        <v>0.03765911303066289</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>49.2953888859128</v>
+        <v>49.30034961651962</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>0.000477295942012662</v>
+        <v>0.0004748345785341105</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>0.5740740740740741</v>
+        <v>0.5736166146755474</v>
       </c>
       <c r="J12" s="16" t="n">
-        <v>0.04298642533936659</v>
+        <v>0.04272363150867831</v>
       </c>
       <c r="K12" s="8" t="n">
         <v>18720</v>
       </c>
       <c r="L12" s="8" t="n">
-        <v>16812</v>
+        <v>16863</v>
       </c>
     </row>
     <row r="13">
@@ -1543,37 +1543,37 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>2696</v>
+        <v>2700</v>
       </c>
       <c r="C13" s="19" t="n">
-        <v>0.01612363044830391</v>
+        <v>0.01612768346733248</v>
       </c>
       <c r="D13" s="18" t="n">
         <v>161</v>
       </c>
       <c r="E13" s="20" t="n">
-        <v>0.1581573914519595</v>
+        <v>0.1575722877149224</v>
       </c>
       <c r="F13" s="20" t="n">
-        <v>0.03720138411687211</v>
+        <v>0.03721169951330462</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>75.09198966447441</v>
+        <v>75.08964133660203</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>0.001774005490129748</v>
+        <v>0.001771714934507332</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>0.7763353115727003</v>
+        <v>0.7759259259259259</v>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.2913835770528683</v>
+        <v>0.2912833264263019</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>1088</v>
       </c>
       <c r="L13" s="18" t="n">
-        <v>1608</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="14">
@@ -1586,7 +1586,7 @@
         <v>878</v>
       </c>
       <c r="C14" s="27" t="n">
-        <v>0.005250944930864552</v>
+        <v>0.005244483734932562</v>
       </c>
       <c r="D14" s="26" t="n">
         <v>136</v>
@@ -1623,37 +1623,37 @@
         </is>
       </c>
       <c r="B15" s="26" t="n">
-        <v>41209</v>
+        <v>41257</v>
       </c>
       <c r="C15" s="27" t="n">
-        <v>0.2464535189703842</v>
+        <v>0.2464369765969393</v>
       </c>
       <c r="D15" s="26" t="n">
         <v>185</v>
       </c>
       <c r="E15" s="28" t="n">
-        <v>0.1401760823943062</v>
+        <v>0.1400040161051561</v>
       </c>
       <c r="F15" s="28" t="n">
-        <v>0.02228088237773147</v>
+        <v>0.02228937167423552</v>
       </c>
       <c r="G15" s="29" t="n">
-        <v>49.98616541935175</v>
+        <v>49.98620306354442</v>
       </c>
       <c r="H15" s="41" t="n">
-        <v>4.644268798243801e-05</v>
+        <v>4.625093207450825e-05</v>
       </c>
       <c r="I15" s="31" t="n">
-        <v>0.5158581863185226</v>
+        <v>0.515815497976101</v>
       </c>
       <c r="J15" s="42" t="n">
-        <v>0.004024144869215318</v>
+        <v>0.003937007874015741</v>
       </c>
       <c r="K15" s="26" t="n">
         <v>19979</v>
       </c>
       <c r="L15" s="26" t="n">
-        <v>21230</v>
+        <v>21278</v>
       </c>
     </row>
     <row r="16">
@@ -1666,7 +1666,7 @@
         <v>2323</v>
       </c>
       <c r="C16" s="35" t="n">
-        <v>0.01389287593895029</v>
+        <v>0.01387578099800495</v>
       </c>
       <c r="D16" s="34" t="n">
         <v>158</v>
@@ -1727,7 +1727,7 @@
     <row r="22">
       <c r="A22" s="43" t="inlineStr">
         <is>
-          <t>④ R²低·YZ低·중간(41,209건, 24.6%)이 유일한 '진짜 횡보'다. 과거60일 +0.4%, 기울기 ≈0, 상승 52%. 시장의 기본값이 여기다.</t>
+          <t>④ R²低·YZ低·중간(41,257건, 24.6%)이 유일한 '진짜 횡보'다. 과거60일 +0.4%, 기울기 ≈0, 상승 52%. 시장의 기본값이 여기다.</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
         </is>
       </c>
       <c r="B29" s="45" t="n">
-        <v>167208</v>
+        <v>167414</v>
       </c>
       <c r="C29" s="46" t="n">
         <v>1</v>
@@ -1830,28 +1830,28 @@
         <v>206</v>
       </c>
       <c r="E29" s="47" t="n">
-        <v>0.4290955901431661</v>
+        <v>0.4289415918302086</v>
       </c>
       <c r="F29" s="47" t="n">
-        <v>0.02993330568541613</v>
+        <v>0.02995093985540031</v>
       </c>
       <c r="G29" s="48" t="n">
-        <v>50.70244436382978</v>
+        <v>50.70280483553206</v>
       </c>
       <c r="H29" s="49" t="n">
-        <v>0.0005544112241437126</v>
+        <v>0.00055225256462517</v>
       </c>
       <c r="I29" s="50" t="n">
-        <v>0.565164346203531</v>
+        <v>0.5648512071869736</v>
       </c>
       <c r="J29" s="51" t="n">
-        <v>0.03901524453431282</v>
+        <v>0.03877221324717284</v>
       </c>
       <c r="K29" s="45" t="n">
         <v>83649</v>
       </c>
       <c r="L29" s="45" t="n">
-        <v>83559</v>
+        <v>83765</v>
       </c>
     </row>
     <row r="30">
@@ -1861,37 +1861,37 @@
         </is>
       </c>
       <c r="B30" s="26" t="n">
-        <v>83746</v>
+        <v>83849</v>
       </c>
       <c r="C30" s="27" t="n">
-        <v>0.5008492416630783</v>
+        <v>0.5008481966860597</v>
       </c>
       <c r="D30" s="26" t="n">
         <v>206</v>
       </c>
       <c r="E30" s="28" t="n">
-        <v>0.6776731805068197</v>
+        <v>0.6774830188812133</v>
       </c>
       <c r="F30" s="28" t="n">
-        <v>0.03085119870346978</v>
+        <v>0.03087564506702425</v>
       </c>
       <c r="G30" s="29" t="n">
-        <v>51.1700136579742</v>
+        <v>51.16626918134209</v>
       </c>
       <c r="H30" s="41" t="n">
-        <v>0.002361685758504035</v>
+        <v>0.002356333298746782</v>
       </c>
       <c r="I30" s="31" t="n">
-        <v>0.5786425620328135</v>
+        <v>0.5782418394971914</v>
       </c>
       <c r="J30" s="42" t="n">
-        <v>0.1035447970501784</v>
+        <v>0.1030110935023771</v>
       </c>
       <c r="K30" s="26" t="n">
         <v>41890</v>
       </c>
       <c r="L30" s="26" t="n">
-        <v>41856</v>
+        <v>41959</v>
       </c>
     </row>
     <row r="31">
@@ -1901,37 +1901,37 @@
         </is>
       </c>
       <c r="B31" s="34" t="n">
-        <v>83462</v>
+        <v>83565</v>
       </c>
       <c r="C31" s="35" t="n">
-        <v>0.4991507583369217</v>
+        <v>0.4991518033139403</v>
       </c>
       <c r="D31" s="34" t="n">
         <v>206</v>
       </c>
       <c r="E31" s="36" t="n">
-        <v>0.1458729858544544</v>
+        <v>0.1457021642820091</v>
       </c>
       <c r="F31" s="36" t="n">
-        <v>0.02909562809432063</v>
+        <v>0.02910925081917376</v>
       </c>
       <c r="G31" s="37" t="n">
-        <v>50.25620197456221</v>
+        <v>50.259734999953</v>
       </c>
       <c r="H31" s="38" t="n">
-        <v>0.0002140252645747704</v>
+        <v>0.0002131717964513943</v>
       </c>
       <c r="I31" s="39" t="n">
-        <v>0.5516402674270926</v>
+        <v>0.551415066116197</v>
       </c>
       <c r="J31" s="40" t="n">
-        <v>0.02123249588359422</v>
+        <v>0.02111111111111108</v>
       </c>
       <c r="K31" s="34" t="n">
         <v>41759</v>
       </c>
       <c r="L31" s="34" t="n">
-        <v>41703</v>
+        <v>41806</v>
       </c>
     </row>
     <row r="32">
@@ -1941,37 +1941,37 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>83599</v>
+        <v>83702</v>
       </c>
       <c r="C32" s="9" t="n">
-        <v>0.4999700971245395</v>
+        <v>0.499970133919505</v>
       </c>
       <c r="D32" s="8" t="n">
         <v>192</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>0.4617702038606974</v>
+        <v>0.4615267707646177</v>
       </c>
       <c r="F32" s="10" t="n">
-        <v>0.03895281353942246</v>
+        <v>0.03897522679636298</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>51.56866724952538</v>
+        <v>51.57186059519522</v>
       </c>
       <c r="H32" s="15" t="n">
-        <v>0.001806449415824785</v>
+        <v>0.001800908235186991</v>
       </c>
       <c r="I32" s="13" t="n">
-        <v>0.6342061507912774</v>
+        <v>0.6336288260734511</v>
       </c>
       <c r="J32" s="16" t="n">
-        <v>0.1214754408832146</v>
+        <v>0.1209876543209876</v>
       </c>
       <c r="K32" s="8" t="n">
         <v>41825</v>
       </c>
       <c r="L32" s="8" t="n">
-        <v>41774</v>
+        <v>41877</v>
       </c>
     </row>
     <row r="33">
@@ -1981,37 +1981,37 @@
         </is>
       </c>
       <c r="B33" s="18" t="n">
-        <v>83609</v>
+        <v>83712</v>
       </c>
       <c r="C33" s="19" t="n">
-        <v>0.5000299028754605</v>
+        <v>0.500029866080495</v>
       </c>
       <c r="D33" s="18" t="n">
         <v>191</v>
       </c>
       <c r="E33" s="20" t="n">
-        <v>0.3957846265428563</v>
+        <v>0.3957694697211072</v>
       </c>
       <c r="F33" s="20" t="n">
-        <v>0.02222375393015153</v>
+        <v>0.02223259682436137</v>
       </c>
       <c r="G33" s="21" t="n">
-        <v>49.90467226347825</v>
+        <v>49.90365024583027</v>
       </c>
       <c r="H33" s="52" t="n">
-        <v>-2.269681093346081e-05</v>
+        <v>-2.283663684431875e-05</v>
       </c>
       <c r="I33" s="23" t="n">
-        <v>0.4961307993158631</v>
+        <v>0.4960818042813456</v>
       </c>
       <c r="J33" s="24" t="n">
-        <v>0.001529051987767538</v>
+        <v>0.001476015564066735</v>
       </c>
       <c r="K33" s="18" t="n">
         <v>41824</v>
       </c>
       <c r="L33" s="18" t="n">
-        <v>41785</v>
+        <v>41888</v>
       </c>
     </row>
     <row r="34">
@@ -2021,37 +2021,37 @@
         </is>
       </c>
       <c r="B34" s="26" t="n">
-        <v>4158</v>
+        <v>4159</v>
       </c>
       <c r="C34" s="27" t="n">
-        <v>0.02486723123295536</v>
+        <v>0.02484260575579103</v>
       </c>
       <c r="D34" s="26" t="n">
         <v>205</v>
       </c>
       <c r="E34" s="28" t="n">
-        <v>0.5248851487839206</v>
+        <v>0.5251869893743243</v>
       </c>
       <c r="F34" s="28" t="n">
-        <v>0.02642399775364845</v>
+        <v>0.02642548518095484</v>
       </c>
       <c r="G34" s="29" t="n">
-        <v>27.31178936200033</v>
+        <v>27.3125558973648</v>
       </c>
       <c r="H34" s="30" t="n">
-        <v>-0.002845364172733365</v>
+        <v>-0.002849820756801462</v>
       </c>
       <c r="I34" s="31" t="n">
-        <v>0.133958633958634</v>
+        <v>0.1339264246213032</v>
       </c>
       <c r="J34" s="32" t="n">
-        <v>-0.1963362272950206</v>
+        <v>-0.1963534361851332</v>
       </c>
       <c r="K34" s="26" t="n">
         <v>2955</v>
       </c>
       <c r="L34" s="26" t="n">
-        <v>1203</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="35">
@@ -2061,37 +2061,37 @@
         </is>
       </c>
       <c r="B35" s="26" t="n">
-        <v>151124</v>
+        <v>151324</v>
       </c>
       <c r="C35" s="27" t="n">
-        <v>0.9038084302186499</v>
+        <v>0.9038909529668965</v>
       </c>
       <c r="D35" s="26" t="n">
         <v>206</v>
       </c>
       <c r="E35" s="28" t="n">
-        <v>0.420749183708742</v>
+        <v>0.4205824291955358</v>
       </c>
       <c r="F35" s="28" t="n">
-        <v>0.02985090549276544</v>
+        <v>0.0298727588272014</v>
       </c>
       <c r="G35" s="29" t="n">
-        <v>50.01613738950714</v>
+        <v>50.01726053163343</v>
       </c>
       <c r="H35" s="41" t="n">
-        <v>0.0004187842260105542</v>
+        <v>0.0004158878433063126</v>
       </c>
       <c r="I35" s="31" t="n">
-        <v>0.5510574098091633</v>
+        <v>0.5507322037482488</v>
       </c>
       <c r="J35" s="42" t="n">
-        <v>0.02834467120181405</v>
+        <v>0.0280898876404494</v>
       </c>
       <c r="K35" s="26" t="n">
         <v>76250</v>
       </c>
       <c r="L35" s="26" t="n">
-        <v>74874</v>
+        <v>75074</v>
       </c>
     </row>
     <row r="36">
@@ -2101,37 +2101,37 @@
         </is>
       </c>
       <c r="B36" s="34" t="n">
-        <v>11926</v>
+        <v>11931</v>
       </c>
       <c r="C36" s="35" t="n">
-        <v>0.07132433854839482</v>
+        <v>0.07126644127731253</v>
       </c>
       <c r="D36" s="34" t="n">
         <v>205</v>
       </c>
       <c r="E36" s="36" t="n">
-        <v>0.5083502382874378</v>
+        <v>0.508233113818591</v>
       </c>
       <c r="F36" s="36" t="n">
-        <v>0.03289911970543538</v>
+        <v>0.03293048029365141</v>
       </c>
       <c r="G36" s="37" t="n">
-        <v>74.9160356344936</v>
+        <v>74.91361243466787</v>
       </c>
       <c r="H36" s="38" t="n">
-        <v>0.003886437237426723</v>
+        <v>0.003886186889273481</v>
       </c>
       <c r="I36" s="39" t="n">
-        <v>0.8942646318966962</v>
+        <v>0.8941413125471461</v>
       </c>
       <c r="J36" s="40" t="n">
-        <v>0.3817365269461077</v>
+        <v>0.3816504017672905</v>
       </c>
       <c r="K36" s="34" t="n">
         <v>4444</v>
       </c>
       <c r="L36" s="34" t="n">
-        <v>7482</v>
+        <v>7487</v>
       </c>
     </row>
     <row r="37">
@@ -2141,37 +2141,37 @@
         </is>
       </c>
       <c r="B37" s="8" t="n">
-        <v>44547</v>
+        <v>44595</v>
       </c>
       <c r="C37" s="9" t="n">
-        <v>0.2664166786278169</v>
+        <v>0.2663755719354415</v>
       </c>
       <c r="D37" s="8" t="n">
         <v>190</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.6902968346169733</v>
+        <v>0.6901122981162756</v>
       </c>
       <c r="F37" s="10" t="n">
-        <v>0.04035741324026729</v>
+        <v>0.04037661468575353</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>52.89104217709205</v>
+        <v>52.88569684906246</v>
       </c>
       <c r="H37" s="15" t="n">
-        <v>0.004752715022032841</v>
+        <v>0.004746311724497268</v>
       </c>
       <c r="I37" s="13" t="n">
-        <v>0.6795743821132736</v>
+        <v>0.6788877676869605</v>
       </c>
       <c r="J37" s="16" t="n">
-        <v>0.2615694164989939</v>
+        <v>0.2612342720191732</v>
       </c>
       <c r="K37" s="8" t="n">
         <v>21445</v>
       </c>
       <c r="L37" s="8" t="n">
-        <v>23102</v>
+        <v>23150</v>
       </c>
     </row>
     <row r="38">
@@ -2181,37 +2181,37 @@
         </is>
       </c>
       <c r="B38" s="8" t="n">
-        <v>39199</v>
+        <v>39254</v>
       </c>
       <c r="C38" s="9" t="n">
-        <v>0.2344325630352615</v>
+        <v>0.2344726247506182</v>
       </c>
       <c r="D38" s="8" t="n">
         <v>186</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>0.6637495076580315</v>
+        <v>0.6636282220654967</v>
       </c>
       <c r="F38" s="10" t="n">
-        <v>0.02224290126108189</v>
+        <v>0.02225208378014275</v>
       </c>
       <c r="G38" s="11" t="n">
-        <v>49.2776897805286</v>
+        <v>49.27586026250631</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>-0.001409727965030592</v>
+        <v>-0.001410579987198543</v>
       </c>
       <c r="I38" s="13" t="n">
-        <v>0.4639404066430266</v>
+        <v>0.4639017679726907</v>
       </c>
       <c r="J38" s="14" t="n">
-        <v>-0.03372681281618883</v>
+        <v>-0.03384355069634259</v>
       </c>
       <c r="K38" s="8" t="n">
         <v>20445</v>
       </c>
       <c r="L38" s="8" t="n">
-        <v>18754</v>
+        <v>18809</v>
       </c>
     </row>
     <row r="39">
@@ -2221,37 +2221,37 @@
         </is>
       </c>
       <c r="B39" s="8" t="n">
-        <v>39052</v>
+        <v>39107</v>
       </c>
       <c r="C39" s="9" t="n">
-        <v>0.2335534184967226</v>
+        <v>0.2335945619840634</v>
       </c>
       <c r="D39" s="8" t="n">
         <v>192</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>0.150926666391757</v>
+        <v>0.1507732830683398</v>
       </c>
       <c r="F39" s="10" t="n">
-        <v>0.03760274952458108</v>
+        <v>0.03762087463139869</v>
       </c>
       <c r="G39" s="11" t="n">
-        <v>50.0148053118144</v>
+        <v>50.02439577065638</v>
       </c>
       <c r="H39" s="15" t="n">
-        <v>0.000535719802229524</v>
+        <v>0.0005345654223086079</v>
       </c>
       <c r="I39" s="13" t="n">
-        <v>0.582454163679197</v>
+        <v>0.582018564451377</v>
       </c>
       <c r="J39" s="16" t="n">
-        <v>0.05208327963974335</v>
+        <v>0.05178365937859608</v>
       </c>
       <c r="K39" s="8" t="n">
         <v>20380</v>
       </c>
       <c r="L39" s="8" t="n">
-        <v>18672</v>
+        <v>18727</v>
       </c>
     </row>
     <row r="40">
@@ -2261,37 +2261,37 @@
         </is>
       </c>
       <c r="B40" s="18" t="n">
-        <v>44410</v>
+        <v>44458</v>
       </c>
       <c r="C40" s="19" t="n">
-        <v>0.265597339840199</v>
+        <v>0.2655572413298768</v>
       </c>
       <c r="D40" s="18" t="n">
         <v>185</v>
       </c>
       <c r="E40" s="20" t="n">
-        <v>0.1416802986224325</v>
+        <v>0.1414922314906254</v>
       </c>
       <c r="F40" s="20" t="n">
-        <v>0.02220419848902573</v>
+        <v>0.02221374656375553</v>
       </c>
       <c r="G40" s="21" t="n">
         <v>50.43839806031573</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>7.46909008204741e-05</v>
+        <v>7.455199873492159e-05</v>
       </c>
       <c r="I40" s="23" t="n">
-        <v>0.524544021616753</v>
+        <v>0.5244950290161501</v>
       </c>
       <c r="J40" s="24" t="n">
-        <v>0.007212468873333822</v>
+        <v>0.007155635062611854</v>
       </c>
       <c r="K40" s="18" t="n">
         <v>21379</v>
       </c>
       <c r="L40" s="18" t="n">
-        <v>23031</v>
+        <v>23079</v>
       </c>
     </row>
     <row r="42">
@@ -2332,7 +2332,7 @@
     <row r="47">
       <c r="A47" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   그런데 YZ高 의 과거60일이 +12.1%, YZ低 가 +0.2% 다.</t>
+          <t xml:space="preserve">   그런데 YZ高 의 과거60일이 +12.1%, YZ低 가 +0.1% 다.</t>
         </is>
       </c>
     </row>
@@ -2367,7 +2367,7 @@
     <row r="52">
       <c r="A52" s="43" t="inlineStr">
         <is>
-          <t>⑧ R²축은 방향은 못 가르지만 **크기**를 가른다: 기울기 중앙 R²高 +0.00236 / R²低 +0.00021 (11배), 과거60일 +10.4% / +2.1%.</t>
+          <t>⑧ R²축은 방향은 못 가르지만 **크기**를 가른다: 기울기 중앙 R²高 +0.00236 / R²低 +0.00021 (11배), 과거60일 +10.3% / +2.1%.</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C5" s="53" t="n">
         <v>0.005997926726841629</v>
@@ -2598,13 +2598,13 @@
         <v>0.01461904224928601</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>0.01940355475845568</v>
+        <v>0.01929846104139532</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>0.02424725379866494</v>
+        <v>0.02478263277399351</v>
       </c>
       <c r="H5" s="53" t="n">
         <v>0.01863846038448425</v>
@@ -2616,25 +2616,25 @@
         <v>0.01774212949294141</v>
       </c>
       <c r="K5" s="54" t="n">
-        <v>0.01179662044931518</v>
+        <v>0.01182349444472131</v>
       </c>
       <c r="L5" s="53" t="n">
-        <v>0.02341136967289409</v>
+        <v>0.02344700171475028</v>
       </c>
       <c r="M5" s="53" t="n">
-        <v>0.03343425729189275</v>
+        <v>0.03342807022848626</v>
       </c>
       <c r="N5" s="53" t="n">
-        <v>0.04854964081177676</v>
+        <v>0.04905132135753421</v>
       </c>
       <c r="O5" s="53" t="n">
-        <v>0.05473090156709204</v>
+        <v>0.05464601027405447</v>
       </c>
       <c r="P5" s="53" t="n">
-        <v>0.05014055709530491</v>
+        <v>0.0503763498084232</v>
       </c>
       <c r="Q5" s="53" t="n">
-        <v>0.07181359996078129</v>
+        <v>0.07213781239524675</v>
       </c>
     </row>
     <row r="6">
@@ -2644,52 +2644,52 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>38986</v>
+        <v>39033</v>
       </c>
       <c r="C6" s="55" t="n">
-        <v>-0.009365378725599172</v>
+        <v>-0.009374961008363436</v>
       </c>
       <c r="D6" s="55" t="n">
-        <v>-0.01351665019092485</v>
+        <v>-0.01361818677021298</v>
       </c>
       <c r="E6" s="55" t="n">
-        <v>-0.02104236338250609</v>
+        <v>-0.02111072709272976</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>37857</v>
+        <v>37917</v>
       </c>
       <c r="G6" s="55" t="n">
-        <v>-0.03165849221819972</v>
+        <v>-0.03163856102186063</v>
       </c>
       <c r="H6" s="55" t="n">
-        <v>-0.03816037044820297</v>
+        <v>-0.03822806715134064</v>
       </c>
       <c r="I6" s="55" t="n">
-        <v>-0.04213190504123626</v>
+        <v>-0.04240261607918683</v>
       </c>
       <c r="J6" s="55" t="n">
-        <v>-0.05317988817259178</v>
+        <v>-0.05376065693182597</v>
       </c>
       <c r="K6" s="56" t="n">
-        <v>-0.003566685003125625</v>
+        <v>-0.00354939329048376</v>
       </c>
       <c r="L6" s="55" t="n">
-        <v>-0.004724322767316769</v>
+        <v>-0.004790227304748707</v>
       </c>
       <c r="M6" s="55" t="n">
-        <v>-0.007011660849069012</v>
+        <v>-0.006981117905638823</v>
       </c>
       <c r="N6" s="55" t="n">
-        <v>-0.007356105205087893</v>
+        <v>-0.007369872438319935</v>
       </c>
       <c r="O6" s="55" t="n">
-        <v>-0.002067929265595181</v>
+        <v>-0.002220517261770416</v>
       </c>
       <c r="P6" s="53" t="n">
-        <v>0.00588890996670266</v>
+        <v>0.005853991641870393</v>
       </c>
       <c r="Q6" s="53" t="n">
-        <v>0.0008915822952481056</v>
+        <v>0.0006350259704793748</v>
       </c>
     </row>
     <row r="7">
@@ -2705,7 +2705,7 @@
         <v>-0.005946958179090633</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>-0.007279871416307926</v>
+        <v>-0.007246512352895307</v>
       </c>
       <c r="E7" s="57" t="n">
         <v>-0.01393749506542541</v>
@@ -2720,31 +2720,31 @@
         <v>-0.03083454029947896</v>
       </c>
       <c r="I7" s="57" t="n">
-        <v>-0.03696792593476339</v>
+        <v>-0.03806236887028902</v>
       </c>
       <c r="J7" s="57" t="n">
-        <v>-0.07119427328742289</v>
+        <v>-0.07109746835534347</v>
       </c>
       <c r="K7" s="58" t="n">
-        <v>-0.0001482644566170865</v>
+        <v>-0.0001213904612109573</v>
       </c>
       <c r="L7" s="59" t="n">
-        <v>0.001512456007300156</v>
+        <v>0.001581447112568968</v>
       </c>
       <c r="M7" s="59" t="n">
-        <v>9.320746801166901e-05</v>
+        <v>0.000192114121665532</v>
       </c>
       <c r="N7" s="59" t="n">
-        <v>0.0007606499522259114</v>
+        <v>0.000726951522654784</v>
       </c>
       <c r="O7" s="59" t="n">
-        <v>0.00525790088312883</v>
+        <v>0.00517300959009126</v>
       </c>
       <c r="P7" s="59" t="n">
-        <v>0.01105288907317553</v>
+        <v>0.0101942388507682</v>
       </c>
       <c r="Q7" s="57" t="n">
-        <v>-0.01712280281958301</v>
+        <v>-0.01670178545303813</v>
       </c>
     </row>
     <row r="8">
@@ -2781,25 +2781,25 @@
         <v>-0.0510550537172495</v>
       </c>
       <c r="K8" s="62" t="n">
-        <v>0.01109401979972169</v>
+        <v>0.01112089379512782</v>
       </c>
       <c r="L8" s="60" t="n">
-        <v>0.01596854704169232</v>
+        <v>0.01600417908354851</v>
       </c>
       <c r="M8" s="60" t="n">
-        <v>0.01980955058923073</v>
+        <v>0.01990845724288459</v>
       </c>
       <c r="N8" s="60" t="n">
-        <v>0.03418543501410493</v>
+        <v>0.0341517365845338</v>
       </c>
       <c r="O8" s="60" t="n">
-        <v>0.02360843531110118</v>
+        <v>0.02352354401806361</v>
       </c>
       <c r="P8" s="60" t="n">
-        <v>0.008495127691300397</v>
+        <v>0.008730920404418696</v>
       </c>
       <c r="Q8" s="60" t="n">
-        <v>0.003016416750590389</v>
+        <v>0.003340629185055843</v>
       </c>
     </row>
     <row r="9">
@@ -2809,52 +2809,52 @@
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>35397</v>
+        <v>35451</v>
       </c>
       <c r="C9" s="61" t="n">
-        <v>-0.005267673141189033</v>
+        <v>-0.005314914209929356</v>
       </c>
       <c r="D9" s="61" t="n">
-        <v>-0.008628904652316305</v>
+        <v>-0.008678906404244069</v>
       </c>
       <c r="E9" s="61" t="n">
-        <v>-0.0146475611521204</v>
+        <v>-0.0147414016496763</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>34461</v>
+        <v>34503</v>
       </c>
       <c r="G9" s="61" t="n">
-        <v>-0.02639803188433659</v>
+        <v>-0.026297815964059</v>
       </c>
       <c r="H9" s="61" t="n">
-        <v>-0.04044513390606685</v>
+        <v>-0.04030683708612615</v>
       </c>
       <c r="I9" s="61" t="n">
-        <v>-0.05238472783345127</v>
+        <v>-0.05250480508722799</v>
       </c>
       <c r="J9" s="61" t="n">
-        <v>-0.05729357036052485</v>
+        <v>-0.05736652620034216</v>
       </c>
       <c r="K9" s="62" t="n">
-        <v>0.0005310205812845137</v>
+        <v>0.0005106535079503205</v>
       </c>
       <c r="L9" s="60" t="n">
-        <v>0.0001634227712917768</v>
+        <v>0.0001490530612202057</v>
       </c>
       <c r="M9" s="61" t="n">
-        <v>-0.0006168586186833247</v>
+        <v>-0.0006117924625853588</v>
       </c>
       <c r="N9" s="61" t="n">
-        <v>-0.002095644871224767</v>
+        <v>-0.002029127380518303</v>
       </c>
       <c r="O9" s="61" t="n">
-        <v>-0.004352692723459062</v>
+        <v>-0.004299287196555923</v>
       </c>
       <c r="P9" s="61" t="n">
-        <v>-0.00436391282551235</v>
+        <v>-0.004248197366170769</v>
       </c>
       <c r="Q9" s="61" t="n">
-        <v>-0.00322209989268496</v>
+        <v>-0.002970843298036818</v>
       </c>
     </row>
     <row r="10">
@@ -2864,13 +2864,13 @@
         </is>
       </c>
       <c r="B10" s="34" t="n">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="C10" s="63" t="n">
         <v>-0.007354443812492506</v>
       </c>
       <c r="D10" s="63" t="n">
-        <v>-0.01280650269155792</v>
+        <v>-0.0130100305387838</v>
       </c>
       <c r="E10" s="63" t="n">
         <v>-0.03207481195947604</v>
@@ -2885,31 +2885,31 @@
         <v>-0.0611933895943324</v>
       </c>
       <c r="I10" s="63" t="n">
-        <v>-0.1401851199739492</v>
+        <v>-0.140656245533158</v>
       </c>
       <c r="J10" s="63" t="n">
         <v>-0.136308980458466</v>
       </c>
       <c r="K10" s="64" t="n">
-        <v>-0.001555750090018959</v>
+        <v>-0.00152887609461283</v>
       </c>
       <c r="L10" s="63" t="n">
-        <v>-0.004014175267949838</v>
+        <v>-0.004182071073319527</v>
       </c>
       <c r="M10" s="63" t="n">
-        <v>-0.01804410942603896</v>
+        <v>-0.01794520277238509</v>
       </c>
       <c r="N10" s="63" t="n">
-        <v>-0.02040060916474129</v>
+        <v>-0.02043430759431242</v>
       </c>
       <c r="O10" s="63" t="n">
-        <v>-0.02510094841172461</v>
+        <v>-0.02518583970476218</v>
       </c>
       <c r="P10" s="63" t="n">
-        <v>-0.0921643049660103</v>
+        <v>-0.09239963781210081</v>
       </c>
       <c r="Q10" s="63" t="n">
-        <v>-0.08223750999062607</v>
+        <v>-0.08191329755616061</v>
       </c>
     </row>
     <row r="11">
@@ -2928,10 +2928,10 @@
         <v>0.0104086479672541</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>0.01854093278061908</v>
+        <v>0.01846680681493118</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="G11" s="53" t="n">
         <v>0.01485807363216951</v>
@@ -2946,25 +2946,25 @@
         <v>-0.02349552485604611</v>
       </c>
       <c r="K11" s="54" t="n">
-        <v>0.01631035529849445</v>
+        <v>0.01633722929390058</v>
       </c>
       <c r="L11" s="53" t="n">
-        <v>0.01920097539086218</v>
+        <v>0.01923660743271838</v>
       </c>
       <c r="M11" s="53" t="n">
-        <v>0.03257163531405616</v>
+        <v>0.03259641600202212</v>
       </c>
       <c r="N11" s="53" t="n">
-        <v>0.03916046064528134</v>
+        <v>0.03912676221571021</v>
       </c>
       <c r="O11" s="53" t="n">
-        <v>0.04730378870684737</v>
+        <v>0.0472188974138098</v>
       </c>
       <c r="P11" s="53" t="n">
-        <v>0.01857432371633444</v>
+        <v>0.01881011642945274</v>
       </c>
       <c r="Q11" s="53" t="n">
-        <v>0.03057594561179378</v>
+        <v>0.03090015804625923</v>
       </c>
     </row>
     <row r="12">
@@ -2974,52 +2974,52 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>35532</v>
+        <v>35583</v>
       </c>
       <c r="C12" s="55" t="n">
-        <v>-0.006964210637633972</v>
+        <v>-0.006998305672306193</v>
       </c>
       <c r="D12" s="55" t="n">
-        <v>-0.009451339587625784</v>
+        <v>-0.009471162186297954</v>
       </c>
       <c r="E12" s="55" t="n">
-        <v>-0.01212377941202147</v>
+        <v>-0.01222676852015975</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>34565</v>
+        <v>34606</v>
       </c>
       <c r="G12" s="55" t="n">
-        <v>-0.01680984464844215</v>
+        <v>-0.01666330645706171</v>
       </c>
       <c r="H12" s="55" t="n">
-        <v>-0.02706392633500876</v>
+        <v>-0.02712539912212614</v>
       </c>
       <c r="I12" s="55" t="n">
-        <v>-0.03161411765961475</v>
+        <v>-0.03194406131057259</v>
       </c>
       <c r="J12" s="55" t="n">
-        <v>-0.03559329425037772</v>
+        <v>-0.03603121523417951</v>
       </c>
       <c r="K12" s="56" t="n">
-        <v>-0.001165516915160425</v>
+        <v>-0.001172737954426517</v>
       </c>
       <c r="L12" s="55" t="n">
-        <v>-0.0006590121640177027</v>
+        <v>-0.0006432027208336799</v>
       </c>
       <c r="M12" s="53" t="n">
-        <v>0.001906923121415605</v>
+        <v>0.001902840666931194</v>
       </c>
       <c r="N12" s="53" t="n">
-        <v>0.007492542364669674</v>
+        <v>0.007605382126478988</v>
       </c>
       <c r="O12" s="53" t="n">
-        <v>0.009028514847599034</v>
+        <v>0.008882150767444086</v>
       </c>
       <c r="P12" s="53" t="n">
-        <v>0.01640669734832417</v>
+        <v>0.01631254641048463</v>
       </c>
       <c r="Q12" s="53" t="n">
-        <v>0.01847817621746217</v>
+        <v>0.01836446766812583</v>
       </c>
     </row>
     <row r="13">
@@ -3029,13 +3029,13 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>2696</v>
+        <v>2700</v>
       </c>
       <c r="C13" s="57" t="n">
-        <v>-0.01069906380396934</v>
+        <v>-0.01058577062853361</v>
       </c>
       <c r="D13" s="57" t="n">
-        <v>-0.01613193823720138</v>
+        <v>-0.0167429711940319</v>
       </c>
       <c r="E13" s="57" t="n">
         <v>-0.02022315962303572</v>
@@ -3047,34 +3047,34 @@
         <v>-0.03758608064994173</v>
       </c>
       <c r="H13" s="57" t="n">
-        <v>-0.04080750218790752</v>
+        <v>-0.04106671569697729</v>
       </c>
       <c r="I13" s="57" t="n">
-        <v>-0.0523321082293533</v>
+        <v>-0.05286203655335969</v>
       </c>
       <c r="J13" s="57" t="n">
         <v>-0.06518802292877002</v>
       </c>
       <c r="K13" s="58" t="n">
-        <v>-0.004900370081495797</v>
+        <v>-0.004760202910653932</v>
       </c>
       <c r="L13" s="57" t="n">
-        <v>-0.0073396108135933</v>
+        <v>-0.007915011728567622</v>
       </c>
       <c r="M13" s="57" t="n">
-        <v>-0.006192457089598646</v>
+        <v>-0.006093550435944783</v>
       </c>
       <c r="N13" s="57" t="n">
-        <v>-0.01328369363682991</v>
+        <v>-0.01331739206640103</v>
       </c>
       <c r="O13" s="57" t="n">
-        <v>-0.004715061005299725</v>
+        <v>-0.005059165807407062</v>
       </c>
       <c r="P13" s="57" t="n">
-        <v>-0.004311293221414381</v>
+        <v>-0.004605428832302472</v>
       </c>
       <c r="Q13" s="57" t="n">
-        <v>-0.01111655246093013</v>
+        <v>-0.01079234002646468</v>
       </c>
     </row>
     <row r="14">
@@ -3090,16 +3090,16 @@
         <v>0.002560261828984167</v>
       </c>
       <c r="D14" s="60" t="n">
-        <v>0.009909938312472999</v>
+        <v>0.009894964155819808</v>
       </c>
       <c r="E14" s="60" t="n">
-        <v>0.01124445085038916</v>
+        <v>0.0112323040277032</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="G14" s="61" t="n">
-        <v>-0.003953759553274816</v>
+        <v>-0.003976504008325388</v>
       </c>
       <c r="H14" s="61" t="n">
         <v>-0.0091675668069644</v>
@@ -3111,25 +3111,25 @@
         <v>-0.01534262025889332</v>
       </c>
       <c r="K14" s="62" t="n">
-        <v>0.008358955551457714</v>
+        <v>0.008385829546863843</v>
       </c>
       <c r="L14" s="60" t="n">
-        <v>0.01870226573608108</v>
+        <v>0.01872292362128408</v>
       </c>
       <c r="M14" s="60" t="n">
-        <v>0.02527515338382624</v>
+        <v>0.02536191321479414</v>
       </c>
       <c r="N14" s="60" t="n">
-        <v>0.02034862745983701</v>
+        <v>0.02029218457521531</v>
       </c>
       <c r="O14" s="60" t="n">
-        <v>0.02692487437564339</v>
+        <v>0.02683998308260582</v>
       </c>
       <c r="P14" s="60" t="n">
-        <v>0.02751403863268848</v>
+        <v>0.02774983134580677</v>
       </c>
       <c r="Q14" s="60" t="n">
-        <v>0.03872885020894656</v>
+        <v>0.03905306264341202</v>
       </c>
     </row>
     <row r="15">
@@ -3139,52 +3139,52 @@
         </is>
       </c>
       <c r="B15" s="26" t="n">
-        <v>41209</v>
+        <v>41257</v>
       </c>
       <c r="C15" s="61" t="n">
-        <v>-0.004191757292032805</v>
+        <v>-0.004268036485405968</v>
       </c>
       <c r="D15" s="61" t="n">
-        <v>-0.006623432375192806</v>
+        <v>-0.006670224760970456</v>
       </c>
       <c r="E15" s="61" t="n">
-        <v>-0.01138990312635002</v>
+        <v>-0.01150860673185283</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>40117</v>
+        <v>40174</v>
       </c>
       <c r="G15" s="61" t="n">
-        <v>-0.02171773157362455</v>
+        <v>-0.02173224068456558</v>
       </c>
       <c r="H15" s="61" t="n">
-        <v>-0.03593547417493276</v>
+        <v>-0.03575763607523513</v>
       </c>
       <c r="I15" s="61" t="n">
-        <v>-0.05166198047840681</v>
+        <v>-0.05181203690225855</v>
       </c>
       <c r="J15" s="61" t="n">
-        <v>-0.05442961278961461</v>
+        <v>-0.05496292405982772</v>
       </c>
       <c r="K15" s="62" t="n">
-        <v>0.001606936430440742</v>
+        <v>0.001557531232473708</v>
       </c>
       <c r="L15" s="60" t="n">
-        <v>0.002168895048415276</v>
+        <v>0.002157734704493819</v>
       </c>
       <c r="M15" s="60" t="n">
-        <v>0.002640799407087058</v>
+        <v>0.002621002455238108</v>
       </c>
       <c r="N15" s="60" t="n">
-        <v>0.002584655439487271</v>
+        <v>0.002536447898975114</v>
       </c>
       <c r="O15" s="60" t="n">
-        <v>0.0001569670076750351</v>
+        <v>0.0002499138143350899</v>
       </c>
       <c r="P15" s="61" t="n">
-        <v>-0.003641165470467889</v>
+        <v>-0.003555429181201331</v>
       </c>
       <c r="Q15" s="61" t="n">
-        <v>-0.0003581423217747237</v>
+        <v>-0.0005672411575223801</v>
       </c>
     </row>
     <row r="16">
@@ -3203,10 +3203,10 @@
         <v>-0.01300242194591861</v>
       </c>
       <c r="E16" s="63" t="n">
-        <v>-0.03544546434493639</v>
+        <v>-0.0355845052366861</v>
       </c>
       <c r="F16" s="34" t="n">
-        <v>2310</v>
+        <v>2313</v>
       </c>
       <c r="G16" s="63" t="n">
         <v>-0.0608946183977071</v>
@@ -3215,31 +3215,31 @@
         <v>-0.07408635717586709</v>
       </c>
       <c r="I16" s="63" t="n">
-        <v>-0.1378459527711136</v>
+        <v>-0.1383983185922683</v>
       </c>
       <c r="J16" s="63" t="n">
         <v>-0.1699136411639642</v>
       </c>
       <c r="K16" s="64" t="n">
-        <v>-0.002958041741992212</v>
+        <v>-0.002931167746586083</v>
       </c>
       <c r="L16" s="63" t="n">
-        <v>-0.004210094522310526</v>
+        <v>-0.004174462480454333</v>
       </c>
       <c r="M16" s="63" t="n">
-        <v>-0.02141476181149932</v>
+        <v>-0.02145489604959516</v>
       </c>
       <c r="N16" s="63" t="n">
-        <v>-0.03659223138459528</v>
+        <v>-0.0366259298141664</v>
       </c>
       <c r="O16" s="63" t="n">
-        <v>-0.0379939159932593</v>
+        <v>-0.03807880728629687</v>
       </c>
       <c r="P16" s="63" t="n">
-        <v>-0.08982513776317469</v>
+        <v>-0.09014171087121103</v>
       </c>
       <c r="Q16" s="63" t="n">
-        <v>-0.1158421706961243</v>
+        <v>-0.1155179582616588</v>
       </c>
     </row>
     <row r="17">
@@ -3249,31 +3249,31 @@
         </is>
       </c>
       <c r="B17" s="45" t="n">
-        <v>167208</v>
+        <v>167414</v>
       </c>
       <c r="C17" s="65" t="n">
-        <v>-0.005798693722473547</v>
+        <v>-0.005825567717879676</v>
       </c>
       <c r="D17" s="65" t="n">
-        <v>-0.008792327423608082</v>
+        <v>-0.008827959465464275</v>
       </c>
       <c r="E17" s="65" t="n">
-        <v>-0.01403070253343708</v>
+        <v>-0.01412960918709094</v>
       </c>
       <c r="F17" s="45" t="n">
-        <v>163002</v>
+        <v>163208</v>
       </c>
       <c r="G17" s="65" t="n">
-        <v>-0.02430238701311183</v>
+        <v>-0.0242686885835407</v>
       </c>
       <c r="H17" s="65" t="n">
-        <v>-0.03609244118260779</v>
+        <v>-0.03600754988957022</v>
       </c>
       <c r="I17" s="65" t="n">
-        <v>-0.04802081500793892</v>
+        <v>-0.04825660772105722</v>
       </c>
       <c r="J17" s="65" t="n">
-        <v>-0.05407147046783989</v>
+        <v>-0.05439568290230534</v>
       </c>
       <c r="K17" s="66" t="n"/>
       <c r="L17" s="67" t="n"/>
@@ -3445,7 +3445,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C5" s="53" t="n">
         <v>0.02380360516389505</v>
@@ -3454,13 +3454,13 @@
         <v>0.03518727601534961</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>0.05161800700385025</v>
+        <v>0.0513404008652984</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>0.06539512903568963</v>
+        <v>0.06607694593961658</v>
       </c>
       <c r="H5" s="53" t="n">
         <v>0.08402157664532717</v>
@@ -3472,25 +3472,25 @@
         <v>0.1578942815183549</v>
       </c>
       <c r="K5" s="54" t="n">
-        <v>0.02354241915220472</v>
+        <v>0.02359096251772667</v>
       </c>
       <c r="L5" s="53" t="n">
-        <v>0.03461604478765869</v>
+        <v>0.03465376499767042</v>
       </c>
       <c r="M5" s="53" t="n">
-        <v>0.05059037898961761</v>
+        <v>0.05044886123679608</v>
       </c>
       <c r="N5" s="53" t="n">
-        <v>0.06408663465723881</v>
+        <v>0.06475591964004157</v>
       </c>
       <c r="O5" s="53" t="n">
-        <v>0.08294527401959891</v>
+        <v>0.08291812944889733</v>
       </c>
       <c r="P5" s="53" t="n">
-        <v>0.08269983106089047</v>
+        <v>0.08305041523604352</v>
       </c>
       <c r="Q5" s="53" t="n">
-        <v>0.1457679585477918</v>
+        <v>0.1461905181089979</v>
       </c>
     </row>
     <row r="6">
@@ -3500,52 +3500,52 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>38986</v>
+        <v>39033</v>
       </c>
       <c r="C6" s="53" t="n">
-        <v>0.001378504259317452</v>
+        <v>0.00134703228778212</v>
       </c>
       <c r="D6" s="53" t="n">
-        <v>0.00260372118947745</v>
+        <v>0.002562916797930723</v>
       </c>
       <c r="E6" s="53" t="n">
-        <v>0.005005432849139976</v>
+        <v>0.004856870808965867</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>37857</v>
+        <v>37917</v>
       </c>
       <c r="G6" s="53" t="n">
-        <v>0.01458487354058872</v>
+        <v>0.01458370286703477</v>
       </c>
       <c r="H6" s="53" t="n">
-        <v>0.03125940501674232</v>
+        <v>0.03113230692087805</v>
       </c>
       <c r="I6" s="53" t="n">
-        <v>0.05536258463314101</v>
+        <v>0.05489716692796281</v>
       </c>
       <c r="J6" s="53" t="n">
-        <v>0.08367409008405952</v>
+        <v>0.08295885176184642</v>
       </c>
       <c r="K6" s="54" t="n">
-        <v>0.001117318247627124</v>
+        <v>0.001134389641613741</v>
       </c>
       <c r="L6" s="53" t="n">
-        <v>0.002032489961786527</v>
+        <v>0.002029405780251538</v>
       </c>
       <c r="M6" s="53" t="n">
-        <v>0.003977804834907333</v>
+        <v>0.003965331180463549</v>
       </c>
       <c r="N6" s="53" t="n">
-        <v>0.0132763791621379</v>
+        <v>0.01326267656745977</v>
       </c>
       <c r="O6" s="53" t="n">
-        <v>0.03018310239101406</v>
+        <v>0.03002885972444821</v>
       </c>
       <c r="P6" s="53" t="n">
-        <v>0.05130646156769961</v>
+        <v>0.05119162803767446</v>
       </c>
       <c r="Q6" s="53" t="n">
-        <v>0.07154776711349645</v>
+        <v>0.07125508835248939</v>
       </c>
     </row>
     <row r="7">
@@ -3561,7 +3561,7 @@
         <v>0.01114235314421401</v>
       </c>
       <c r="D7" s="59" t="n">
-        <v>0.01897662983615299</v>
+        <v>0.01900654466684098</v>
       </c>
       <c r="E7" s="59" t="n">
         <v>0.04314617098035235</v>
@@ -3573,34 +3573,34 @@
         <v>0.08241813485694213</v>
       </c>
       <c r="H7" s="59" t="n">
-        <v>0.1102628285315284</v>
+        <v>0.1100361955281079</v>
       </c>
       <c r="I7" s="59" t="n">
-        <v>0.1782669677253179</v>
+        <v>0.1767175852485424</v>
       </c>
       <c r="J7" s="59" t="n">
-        <v>0.1642774201491838</v>
+        <v>0.1642247453544079</v>
       </c>
       <c r="K7" s="68" t="n">
-        <v>0.01088116713252368</v>
+        <v>0.01092971049804563</v>
       </c>
       <c r="L7" s="59" t="n">
-        <v>0.01840539860846206</v>
+        <v>0.01847303364916179</v>
       </c>
       <c r="M7" s="59" t="n">
-        <v>0.04211854296611971</v>
+        <v>0.04225463135185004</v>
       </c>
       <c r="N7" s="59" t="n">
-        <v>0.08110964047849131</v>
+        <v>0.08109710855736713</v>
       </c>
       <c r="O7" s="59" t="n">
-        <v>0.1091865259058001</v>
+        <v>0.1089327483316781</v>
       </c>
       <c r="P7" s="59" t="n">
-        <v>0.1742108446598765</v>
+        <v>0.1730120463582541</v>
       </c>
       <c r="Q7" s="59" t="n">
-        <v>0.1521510971786207</v>
+        <v>0.1525209819450508</v>
       </c>
     </row>
     <row r="8">
@@ -3637,25 +3637,25 @@
         <v>-0.03858121534941432</v>
       </c>
       <c r="K8" s="62" t="n">
-        <v>0.01035331011243566</v>
+        <v>0.0104018534779576</v>
       </c>
       <c r="L8" s="60" t="n">
-        <v>0.01258511880325768</v>
+        <v>0.01262283901326941</v>
       </c>
       <c r="M8" s="60" t="n">
-        <v>0.01711169150311473</v>
+        <v>0.01724777988884505</v>
       </c>
       <c r="N8" s="60" t="n">
-        <v>0.02782441475854965</v>
+        <v>0.02781188283742546</v>
       </c>
       <c r="O8" s="60" t="n">
-        <v>0.009245035120894919</v>
+        <v>0.00921789055019334</v>
       </c>
       <c r="P8" s="61" t="n">
-        <v>-0.04063494472156626</v>
+        <v>-0.04028436054641321</v>
       </c>
       <c r="Q8" s="61" t="n">
-        <v>-0.05070753831997738</v>
+        <v>-0.05028497875877135</v>
       </c>
     </row>
     <row r="9">
@@ -3665,52 +3665,52 @@
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>35397</v>
+        <v>35451</v>
       </c>
       <c r="C9" s="61" t="n">
-        <v>-0.002967757938527726</v>
+        <v>-0.003054643742828615</v>
       </c>
       <c r="D9" s="61" t="n">
-        <v>-0.005587032732951196</v>
+        <v>-0.005626903366859029</v>
       </c>
       <c r="E9" s="61" t="n">
-        <v>-0.01180049194715143</v>
+        <v>-0.01191613739117414</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>34461</v>
+        <v>34503</v>
       </c>
       <c r="G9" s="61" t="n">
-        <v>-0.02457043656150839</v>
+        <v>-0.02449094139533218</v>
       </c>
       <c r="H9" s="61" t="n">
-        <v>-0.04040226883355482</v>
+        <v>-0.04025419897238718</v>
       </c>
       <c r="I9" s="61" t="n">
-        <v>-0.05919517767962591</v>
+        <v>-0.05941297600838596</v>
       </c>
       <c r="J9" s="61" t="n">
-        <v>-0.05665323436827042</v>
+        <v>-0.05679253304653697</v>
       </c>
       <c r="K9" s="69" t="n">
-        <v>-0.003228943950218054</v>
+        <v>-0.003267286388996995</v>
       </c>
       <c r="L9" s="61" t="n">
-        <v>-0.006158263960642119</v>
+        <v>-0.006160414384538214</v>
       </c>
       <c r="M9" s="61" t="n">
-        <v>-0.01282811996138408</v>
+        <v>-0.01280767701967646</v>
       </c>
       <c r="N9" s="61" t="n">
-        <v>-0.02587893093995921</v>
+        <v>-0.02581196769490718</v>
       </c>
       <c r="O9" s="61" t="n">
-        <v>-0.04147857145928308</v>
+        <v>-0.04135764616881701</v>
       </c>
       <c r="P9" s="61" t="n">
-        <v>-0.06325130074506731</v>
+        <v>-0.06311851489867432</v>
       </c>
       <c r="Q9" s="61" t="n">
-        <v>-0.06877955733883348</v>
+        <v>-0.068496296455894</v>
       </c>
     </row>
     <row r="10">
@@ -3720,13 +3720,13 @@
         </is>
       </c>
       <c r="B10" s="34" t="n">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="C10" s="63" t="n">
         <v>-0.005212910715732809</v>
       </c>
       <c r="D10" s="63" t="n">
-        <v>-0.0135444304930491</v>
+        <v>-0.01368412947637952</v>
       </c>
       <c r="E10" s="63" t="n">
         <v>-0.0236597112195582</v>
@@ -3741,31 +3741,31 @@
         <v>-0.08215225110148387</v>
       </c>
       <c r="I10" s="63" t="n">
-        <v>-0.1573173986226466</v>
+        <v>-0.1576608385332882</v>
       </c>
       <c r="J10" s="63" t="n">
         <v>-0.1458278315672663</v>
       </c>
       <c r="K10" s="64" t="n">
-        <v>-0.005474096727423138</v>
+        <v>-0.005425553361901188</v>
       </c>
       <c r="L10" s="63" t="n">
-        <v>-0.01411566172074002</v>
+        <v>-0.01421764049405871</v>
       </c>
       <c r="M10" s="63" t="n">
-        <v>-0.02468733923379084</v>
+        <v>-0.02455125084806052</v>
       </c>
       <c r="N10" s="63" t="n">
-        <v>-0.04909546588838385</v>
+        <v>-0.04910799780950804</v>
       </c>
       <c r="O10" s="63" t="n">
-        <v>-0.08322855372721213</v>
+        <v>-0.08325569829791371</v>
       </c>
       <c r="P10" s="63" t="n">
-        <v>-0.161373521688088</v>
+        <v>-0.1613663774235765</v>
       </c>
       <c r="Q10" s="63" t="n">
-        <v>-0.1579541545378294</v>
+        <v>-0.1575315949766234</v>
       </c>
     </row>
     <row r="11">
@@ -3784,10 +3784,10 @@
         <v>0.02298857006202292</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>0.03951189892698089</v>
+        <v>0.03925626490375821</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="G11" s="53" t="n">
         <v>0.06318186269195827</v>
@@ -3802,25 +3802,25 @@
         <v>0.1749805077577546</v>
       </c>
       <c r="K11" s="54" t="n">
-        <v>0.01378785954242679</v>
+        <v>0.01383640290794874</v>
       </c>
       <c r="L11" s="53" t="n">
-        <v>0.02241733883433199</v>
+        <v>0.02245505904434373</v>
       </c>
       <c r="M11" s="53" t="n">
-        <v>0.03848427091274825</v>
+        <v>0.0383647252752559</v>
       </c>
       <c r="N11" s="53" t="n">
-        <v>0.06187336831350745</v>
+        <v>0.06186083639238327</v>
       </c>
       <c r="O11" s="53" t="n">
-        <v>0.07891992250545098</v>
+        <v>0.0788927779347494</v>
       </c>
       <c r="P11" s="53" t="n">
-        <v>0.09270405818083799</v>
+        <v>0.09305464235599104</v>
       </c>
       <c r="Q11" s="53" t="n">
-        <v>0.1628541847871916</v>
+        <v>0.1632767443483976</v>
       </c>
     </row>
     <row r="12">
@@ -3830,52 +3830,52 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>35532</v>
+        <v>35583</v>
       </c>
       <c r="C12" s="53" t="n">
-        <v>0.002614470094721536</v>
+        <v>0.002605214056435822</v>
       </c>
       <c r="D12" s="53" t="n">
-        <v>0.006939045591663749</v>
+        <v>0.006915344259312084</v>
       </c>
       <c r="E12" s="53" t="n">
-        <v>0.01624353894779447</v>
+        <v>0.01612999762435975</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>34565</v>
+        <v>34606</v>
       </c>
       <c r="G12" s="53" t="n">
-        <v>0.03508670945961254</v>
+        <v>0.03503562260806047</v>
       </c>
       <c r="H12" s="53" t="n">
-        <v>0.05029675172441643</v>
+        <v>0.0502015996031619</v>
       </c>
       <c r="I12" s="53" t="n">
-        <v>0.07028289721743725</v>
+        <v>0.06988331804978078</v>
       </c>
       <c r="J12" s="53" t="n">
-        <v>0.09627255566113595</v>
+        <v>0.09586971286131479</v>
       </c>
       <c r="K12" s="54" t="n">
-        <v>0.002353284083031208</v>
+        <v>0.002392571410267442</v>
       </c>
       <c r="L12" s="53" t="n">
-        <v>0.006367814363972827</v>
+        <v>0.006381833241632899</v>
       </c>
       <c r="M12" s="53" t="n">
-        <v>0.01521591093356183</v>
+        <v>0.01523845799585743</v>
       </c>
       <c r="N12" s="53" t="n">
-        <v>0.03377821508116172</v>
+        <v>0.03371459630848547</v>
       </c>
       <c r="O12" s="53" t="n">
-        <v>0.04922044909868817</v>
+        <v>0.04909815240673206</v>
       </c>
       <c r="P12" s="53" t="n">
-        <v>0.06622677415199585</v>
+        <v>0.06617777915949243</v>
       </c>
       <c r="Q12" s="53" t="n">
-        <v>0.08414623269057289</v>
+        <v>0.08416594945195777</v>
       </c>
     </row>
     <row r="13">
@@ -3885,13 +3885,13 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>2696</v>
+        <v>2700</v>
       </c>
       <c r="C13" s="59" t="n">
-        <v>0.005851036167249476</v>
+        <v>0.005863052604700735</v>
       </c>
       <c r="D13" s="59" t="n">
-        <v>0.008758892121998372</v>
+        <v>0.008614469341646438</v>
       </c>
       <c r="E13" s="59" t="n">
         <v>0.02945514740321906</v>
@@ -3903,34 +3903,34 @@
         <v>0.04758955645588826</v>
       </c>
       <c r="H13" s="59" t="n">
-        <v>0.07012096600483732</v>
+        <v>0.06995393120836434</v>
       </c>
       <c r="I13" s="59" t="n">
-        <v>0.1647927960782097</v>
+        <v>0.1636970911666753</v>
       </c>
       <c r="J13" s="59" t="n">
         <v>0.2251950020964874</v>
       </c>
       <c r="K13" s="68" t="n">
-        <v>0.005589850155559148</v>
+        <v>0.005650409958532356</v>
       </c>
       <c r="L13" s="59" t="n">
-        <v>0.00818766089430745</v>
+        <v>0.008080958323967253</v>
       </c>
       <c r="M13" s="59" t="n">
-        <v>0.02842751938898642</v>
+        <v>0.02856360777471674</v>
       </c>
       <c r="N13" s="59" t="n">
-        <v>0.04628106207743744</v>
+        <v>0.04626853015631326</v>
       </c>
       <c r="O13" s="59" t="n">
-        <v>0.06904466337910906</v>
+        <v>0.0688504840119345</v>
       </c>
       <c r="P13" s="59" t="n">
-        <v>0.1607366730127683</v>
+        <v>0.159991552276387</v>
       </c>
       <c r="Q13" s="59" t="n">
-        <v>0.2130686791259244</v>
+        <v>0.2134912386871304</v>
       </c>
     </row>
     <row r="14">
@@ -3946,16 +3946,16 @@
         <v>0.005830843023937337</v>
       </c>
       <c r="D14" s="60" t="n">
-        <v>0.01117111523526656</v>
+        <v>0.01109936439156278</v>
       </c>
       <c r="E14" s="60" t="n">
-        <v>0.02330203934499756</v>
+        <v>0.02326579907572202</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="G14" s="60" t="n">
-        <v>0.009175580645984031</v>
+        <v>0.009069246796133808</v>
       </c>
       <c r="H14" s="61" t="n">
         <v>-0.007447478882007297</v>
@@ -3967,25 +3967,25 @@
         <v>-0.0005811498185179922</v>
       </c>
       <c r="K14" s="62" t="n">
-        <v>0.005569657012247009</v>
+        <v>0.005618200377768958</v>
       </c>
       <c r="L14" s="60" t="n">
-        <v>0.01059988400757564</v>
+        <v>0.0105658533738836</v>
       </c>
       <c r="M14" s="60" t="n">
-        <v>0.02227441133076492</v>
+        <v>0.0223742594472197</v>
       </c>
       <c r="N14" s="60" t="n">
-        <v>0.00786708626753321</v>
+        <v>0.007748220496558801</v>
       </c>
       <c r="O14" s="61" t="n">
-        <v>-0.00852378150773556</v>
+        <v>-0.008550926078437139</v>
       </c>
       <c r="P14" s="61" t="n">
-        <v>-0.006876352220230201</v>
+        <v>-0.00652576804507715</v>
       </c>
       <c r="Q14" s="61" t="n">
-        <v>-0.01270747278908105</v>
+        <v>-0.01228491322787502</v>
       </c>
     </row>
     <row r="15">
@@ -3995,52 +3995,52 @@
         </is>
       </c>
       <c r="B15" s="26" t="n">
-        <v>41209</v>
+        <v>41257</v>
       </c>
       <c r="C15" s="61" t="n">
-        <v>-0.002269536626180071</v>
+        <v>-0.002352138887732187</v>
       </c>
       <c r="D15" s="61" t="n">
-        <v>-0.00459612360996666</v>
+        <v>-0.004636382052505358</v>
       </c>
       <c r="E15" s="61" t="n">
-        <v>-0.01116477180037653</v>
+        <v>-0.01134374195390526</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>40117</v>
+        <v>40174</v>
       </c>
       <c r="G15" s="61" t="n">
-        <v>-0.02861455836155558</v>
+        <v>-0.02860173423326596</v>
       </c>
       <c r="H15" s="61" t="n">
-        <v>-0.04589619668433604</v>
+        <v>-0.04566151784410896</v>
       </c>
       <c r="I15" s="61" t="n">
-        <v>-0.0617508123228831</v>
+        <v>-0.06195712306362041</v>
       </c>
       <c r="J15" s="61" t="n">
-        <v>-0.08843234430976027</v>
+        <v>-0.08897426514101416</v>
       </c>
       <c r="K15" s="69" t="n">
-        <v>-0.002530722637870399</v>
+        <v>-0.002564781533900567</v>
       </c>
       <c r="L15" s="61" t="n">
-        <v>-0.005167354837657583</v>
+        <v>-0.005169893070184543</v>
       </c>
       <c r="M15" s="61" t="n">
-        <v>-0.01219239981460917</v>
+        <v>-0.01223528158240758</v>
       </c>
       <c r="N15" s="61" t="n">
-        <v>-0.0299230527400064</v>
+        <v>-0.02992276053284096</v>
       </c>
       <c r="O15" s="61" t="n">
-        <v>-0.0469724993100643</v>
+        <v>-0.0467649650405388</v>
       </c>
       <c r="P15" s="61" t="n">
-        <v>-0.06580693538832449</v>
+        <v>-0.06566266195390877</v>
       </c>
       <c r="Q15" s="61" t="n">
-        <v>-0.1005586672803233</v>
+        <v>-0.1006780285503712</v>
       </c>
     </row>
     <row r="16">
@@ -4059,43 +4059,43 @@
         <v>-0.01178696598438872</v>
       </c>
       <c r="E16" s="63" t="n">
-        <v>-0.03346010377009126</v>
+        <v>-0.03370761940588718</v>
       </c>
       <c r="F16" s="34" t="n">
-        <v>2310</v>
+        <v>2313</v>
       </c>
       <c r="G16" s="63" t="n">
-        <v>-0.05037569031343744</v>
+        <v>-0.0503114365768469</v>
       </c>
       <c r="H16" s="63" t="n">
         <v>-0.07440509927544374</v>
       </c>
       <c r="I16" s="63" t="n">
-        <v>-0.1386752844981032</v>
+        <v>-0.1390665722748808</v>
       </c>
       <c r="J16" s="63" t="n">
         <v>-0.1317367754195199</v>
       </c>
       <c r="K16" s="64" t="n">
-        <v>-0.006706934815770134</v>
+        <v>-0.006658391450248185</v>
       </c>
       <c r="L16" s="63" t="n">
-        <v>-0.01235819721207964</v>
+        <v>-0.01232047700206791</v>
       </c>
       <c r="M16" s="63" t="n">
-        <v>-0.03448773178432391</v>
+        <v>-0.0345991590343895</v>
       </c>
       <c r="N16" s="63" t="n">
-        <v>-0.05168418469188826</v>
+        <v>-0.0516324628764219</v>
       </c>
       <c r="O16" s="63" t="n">
-        <v>-0.075481401901172</v>
+        <v>-0.07550854647187358</v>
       </c>
       <c r="P16" s="63" t="n">
-        <v>-0.1427314075635446</v>
+        <v>-0.1427721111651692</v>
       </c>
       <c r="Q16" s="63" t="n">
-        <v>-0.143863098390083</v>
+        <v>-0.143440538828877</v>
       </c>
     </row>
     <row r="17">
@@ -4105,31 +4105,31 @@
         </is>
       </c>
       <c r="B17" s="45" t="n">
-        <v>167208</v>
+        <v>167414</v>
       </c>
       <c r="C17" s="70" t="n">
-        <v>0.0002611860116903281</v>
+        <v>0.0002126426461683795</v>
       </c>
       <c r="D17" s="70" t="n">
-        <v>0.0005712312276909223</v>
+        <v>0.0005335110176791848</v>
       </c>
       <c r="E17" s="70" t="n">
-        <v>0.001027628014232643</v>
+        <v>0.0008915396285023192</v>
       </c>
       <c r="F17" s="45" t="n">
-        <v>163002</v>
+        <v>163208</v>
       </c>
       <c r="G17" s="70" t="n">
-        <v>0.001308494378450821</v>
+        <v>0.001321026299575006</v>
       </c>
       <c r="H17" s="70" t="n">
-        <v>0.001076302625728263</v>
+        <v>0.001103447196429842</v>
       </c>
       <c r="I17" s="70" t="n">
-        <v>0.004056123065441403</v>
+        <v>0.003705538890288352</v>
       </c>
       <c r="J17" s="70" t="n">
-        <v>0.01212632297056306</v>
+        <v>0.01170376340935703</v>
       </c>
       <c r="K17" s="66" t="n"/>
       <c r="L17" s="67" t="n"/>
@@ -5157,7 +5157,7 @@
         </is>
       </c>
       <c r="B5" s="8" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C5" s="53" t="n">
         <v>0.04020014386835302</v>
@@ -5166,13 +5166,13 @@
         <v>0.05829295479761742</v>
       </c>
       <c r="E5" s="53" t="n">
-        <v>0.08556346301054241</v>
+        <v>0.08534546866371706</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G5" s="53" t="n">
-        <v>0.03146431127738075</v>
+        <v>0.035052843179739</v>
       </c>
       <c r="H5" s="55" t="n">
         <v>-0.004460979274855559</v>
@@ -5184,25 +5184,25 @@
         <v>-0.02563004295794991</v>
       </c>
       <c r="K5" s="54" t="n">
-        <v>0.05110947744190719</v>
+        <v>0.05117909094505535</v>
       </c>
       <c r="L5" s="53" t="n">
-        <v>0.07601348815284481</v>
+        <v>0.07608083040104818</v>
       </c>
       <c r="M5" s="53" t="n">
-        <v>0.1179520690042908</v>
+        <v>0.117964993184457</v>
       </c>
       <c r="N5" s="53" t="n">
-        <v>0.09631221818341612</v>
+        <v>0.09966308265218848</v>
       </c>
       <c r="O5" s="53" t="n">
-        <v>0.1099958409586255</v>
+        <v>0.109297481592044</v>
       </c>
       <c r="P5" s="53" t="n">
-        <v>0.1046937503440121</v>
+        <v>0.1051134869769205</v>
       </c>
       <c r="Q5" s="53" t="n">
-        <v>0.2439334286954388</v>
+        <v>0.2445266249252026</v>
       </c>
     </row>
     <row r="6">
@@ -5212,52 +5212,52 @@
         </is>
       </c>
       <c r="B6" s="8" t="n">
-        <v>20043</v>
+        <v>20090</v>
       </c>
       <c r="C6" s="55" t="n">
-        <v>-0.0151389240783375</v>
+        <v>-0.01515649313018197</v>
       </c>
       <c r="D6" s="55" t="n">
-        <v>-0.02278075093442067</v>
+        <v>-0.0228423561756938</v>
       </c>
       <c r="E6" s="55" t="n">
-        <v>-0.0395176071921855</v>
+        <v>-0.03976439489609529</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>18930</v>
+        <v>18990</v>
       </c>
       <c r="G6" s="55" t="n">
-        <v>-0.07022136061682482</v>
+        <v>-0.07008290361857078</v>
       </c>
       <c r="H6" s="55" t="n">
-        <v>-0.107468634332899</v>
+        <v>-0.1071139206617601</v>
       </c>
       <c r="I6" s="55" t="n">
-        <v>-0.1523440609247628</v>
+        <v>-0.1528625189749867</v>
       </c>
       <c r="J6" s="55" t="n">
-        <v>-0.1792886932327209</v>
+        <v>-0.1803052942531761</v>
       </c>
       <c r="K6" s="56" t="n">
-        <v>-0.004229590504783332</v>
+        <v>-0.004177546053479642</v>
       </c>
       <c r="L6" s="55" t="n">
-        <v>-0.005060217579193282</v>
+        <v>-0.005054480572263043</v>
       </c>
       <c r="M6" s="55" t="n">
-        <v>-0.007129001198437068</v>
+        <v>-0.007144870375355383</v>
       </c>
       <c r="N6" s="55" t="n">
-        <v>-0.005373453710789455</v>
+        <v>-0.005472664146121298</v>
       </c>
       <c r="O6" s="53" t="n">
-        <v>0.006988185900582033</v>
+        <v>0.006644540205139438</v>
       </c>
       <c r="P6" s="53" t="n">
-        <v>0.04917631639964082</v>
+        <v>0.04907759498232533</v>
       </c>
       <c r="Q6" s="53" t="n">
-        <v>0.09027477842066778</v>
+        <v>0.08985137362997642</v>
       </c>
     </row>
     <row r="7">
@@ -5273,7 +5273,7 @@
         <v>-0.009363119191734492</v>
       </c>
       <c r="D7" s="57" t="n">
-        <v>-0.01252466629378551</v>
+        <v>-0.01248068452692885</v>
       </c>
       <c r="E7" s="57" t="n">
         <v>-0.02466032603290702</v>
@@ -5288,31 +5288,31 @@
         <v>-0.07578200479748665</v>
       </c>
       <c r="I7" s="57" t="n">
-        <v>-0.1162127207293353</v>
+        <v>-0.1179070519180528</v>
       </c>
       <c r="J7" s="57" t="n">
-        <v>-0.228987228987229</v>
+        <v>-0.2288694218671279</v>
       </c>
       <c r="K7" s="68" t="n">
-        <v>0.001546214381819677</v>
+        <v>0.001615827884967835</v>
       </c>
       <c r="L7" s="59" t="n">
-        <v>0.005195867061441872</v>
+        <v>0.005307191076501905</v>
       </c>
       <c r="M7" s="59" t="n">
-        <v>0.007728279960841411</v>
+        <v>0.007959198487832886</v>
       </c>
       <c r="N7" s="59" t="n">
-        <v>0.01373324669556475</v>
+        <v>0.01349557926197886</v>
       </c>
       <c r="O7" s="59" t="n">
-        <v>0.03867481543599438</v>
+        <v>0.03797645606941291</v>
       </c>
       <c r="P7" s="59" t="n">
-        <v>0.08530765659506834</v>
+        <v>0.0840330620392592</v>
       </c>
       <c r="Q7" s="59" t="n">
-        <v>0.04057624266615967</v>
+        <v>0.04128724601602463</v>
       </c>
     </row>
     <row r="8">
@@ -5349,25 +5349,25 @@
         <v>-0.3383564322553836</v>
       </c>
       <c r="K8" s="62" t="n">
-        <v>0.01717105994913259</v>
+        <v>0.01724067345228075</v>
       </c>
       <c r="L8" s="60" t="n">
-        <v>0.01895569605348169</v>
+        <v>0.01902303830168506</v>
       </c>
       <c r="M8" s="60" t="n">
-        <v>0.03774426350457272</v>
+        <v>0.03797518203156419</v>
       </c>
       <c r="N8" s="60" t="n">
-        <v>0.07344906893592651</v>
+        <v>0.07321140150234062</v>
       </c>
       <c r="O8" s="60" t="n">
-        <v>0.08280829319920002</v>
+        <v>0.08210993383261855</v>
       </c>
       <c r="P8" s="61" t="n">
-        <v>-0.003526062429440757</v>
+        <v>-0.003106325796532361</v>
       </c>
       <c r="Q8" s="61" t="n">
-        <v>-0.06879296060199491</v>
+        <v>-0.06819976437223108</v>
       </c>
     </row>
     <row r="9">
@@ -5377,52 +5377,52 @@
         </is>
       </c>
       <c r="B9" s="26" t="n">
-        <v>16789</v>
+        <v>16843</v>
       </c>
       <c r="C9" s="61" t="n">
-        <v>-0.009485199824739499</v>
+        <v>-0.009584967899094132</v>
       </c>
       <c r="D9" s="61" t="n">
-        <v>-0.01675787019929248</v>
+        <v>-0.01683155227266342</v>
       </c>
       <c r="E9" s="61" t="n">
-        <v>-0.03149427884434342</v>
+        <v>-0.0318364923885851</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>15853</v>
+        <v>15895</v>
       </c>
       <c r="G9" s="61" t="n">
-        <v>-0.06786103961504031</v>
+        <v>-0.06735456872139434</v>
       </c>
       <c r="H9" s="61" t="n">
-        <v>-0.12903753510559</v>
+        <v>-0.1281680407055441</v>
       </c>
       <c r="I9" s="61" t="n">
-        <v>-0.2426568009903758</v>
+        <v>-0.2429562625705416</v>
       </c>
       <c r="J9" s="61" t="n">
-        <v>-0.3324442265837717</v>
+        <v>-0.3320035551278796</v>
       </c>
       <c r="K9" s="62" t="n">
-        <v>0.001424133748814671</v>
+        <v>0.001393979177608196</v>
       </c>
       <c r="L9" s="60" t="n">
-        <v>0.0009626631559349064</v>
+        <v>0.0009563233307673391</v>
       </c>
       <c r="M9" s="60" t="n">
-        <v>0.0008943271494050165</v>
+        <v>0.0007830321321548039</v>
       </c>
       <c r="N9" s="61" t="n">
-        <v>-0.00301313270900494</v>
+        <v>-0.002744329248944855</v>
       </c>
       <c r="O9" s="61" t="n">
-        <v>-0.01458071487210899</v>
+        <v>-0.01440957983864455</v>
       </c>
       <c r="P9" s="61" t="n">
-        <v>-0.04113642366597214</v>
+        <v>-0.04101614861322961</v>
       </c>
       <c r="Q9" s="61" t="n">
-        <v>-0.06288075493038303</v>
+        <v>-0.06184688724472709</v>
       </c>
     </row>
     <row r="10">
@@ -5432,13 +5432,13 @@
         </is>
       </c>
       <c r="B10" s="34" t="n">
-        <v>1606</v>
+        <v>1607</v>
       </c>
       <c r="C10" s="63" t="n">
         <v>-0.01019683105203317</v>
       </c>
       <c r="D10" s="63" t="n">
-        <v>-0.02210084119906464</v>
+        <v>-0.02228239341883292</v>
       </c>
       <c r="E10" s="63" t="n">
         <v>-0.04286897717401006</v>
@@ -5453,31 +5453,31 @@
         <v>-0.116637502648999</v>
       </c>
       <c r="I10" s="63" t="n">
-        <v>-0.2536887790931559</v>
+        <v>-0.2546071411166435</v>
       </c>
       <c r="J10" s="63" t="n">
         <v>-0.2748015852896286</v>
       </c>
       <c r="K10" s="72" t="n">
-        <v>0.0007125025215209968</v>
+        <v>0.000782116024669155</v>
       </c>
       <c r="L10" s="63" t="n">
-        <v>-0.00438030784383725</v>
+        <v>-0.004494517815402166</v>
       </c>
       <c r="M10" s="63" t="n">
-        <v>-0.01048037118026163</v>
+        <v>-0.01024945265327015</v>
       </c>
       <c r="N10" s="71" t="n">
-        <v>0.001346705551590999</v>
+        <v>0.001109038118005112</v>
       </c>
       <c r="O10" s="63" t="n">
-        <v>-0.002180682415517943</v>
+        <v>-0.002879041782099412</v>
       </c>
       <c r="P10" s="63" t="n">
-        <v>-0.05216840176875226</v>
+        <v>-0.05266702715933147</v>
       </c>
       <c r="Q10" s="63" t="n">
-        <v>-0.005238113636239938</v>
+        <v>-0.004644917406476101</v>
       </c>
     </row>
     <row r="11">
@@ -5496,10 +5496,10 @@
         <v>0.01769375239461957</v>
       </c>
       <c r="E11" s="53" t="n">
-        <v>0.0268490182349731</v>
+        <v>0.0266099382064986</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G11" s="55" t="n">
         <v>-0.02039504659014701</v>
@@ -5514,25 +5514,25 @@
         <v>0.02611055286619446</v>
       </c>
       <c r="K11" s="54" t="n">
-        <v>0.02447895925379084</v>
+        <v>0.024548572756939</v>
       </c>
       <c r="L11" s="53" t="n">
-        <v>0.03541428574984695</v>
+        <v>0.03548162799805032</v>
       </c>
       <c r="M11" s="53" t="n">
-        <v>0.05923762422872153</v>
+        <v>0.0592294627272385</v>
       </c>
       <c r="N11" s="53" t="n">
-        <v>0.04445286031588835</v>
+        <v>0.04421519288230247</v>
       </c>
       <c r="O11" s="53" t="n">
-        <v>0.1049605359740859</v>
+        <v>0.1042621766075045</v>
       </c>
       <c r="P11" s="53" t="n">
-        <v>0.1452675839229169</v>
+        <v>0.1456873205558253</v>
       </c>
       <c r="Q11" s="53" t="n">
-        <v>0.2956740245195831</v>
+        <v>0.296267220749347</v>
       </c>
     </row>
     <row r="12">
@@ -5542,52 +5542,52 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>16812</v>
+        <v>16863</v>
       </c>
       <c r="C12" s="55" t="n">
-        <v>-0.01113648280459623</v>
+        <v>-0.01118208642438345</v>
       </c>
       <c r="D12" s="55" t="n">
-        <v>-0.01585478108859456</v>
+        <v>-0.01590292044636971</v>
       </c>
       <c r="E12" s="55" t="n">
-        <v>-0.02675265913290037</v>
+        <v>-0.0268706232436533</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>15880</v>
+        <v>15921</v>
       </c>
       <c r="G12" s="55" t="n">
-        <v>-0.04926451726185221</v>
+        <v>-0.04887530727411127</v>
       </c>
       <c r="H12" s="55" t="n">
-        <v>-0.09122154829567974</v>
+        <v>-0.09097613676874183</v>
       </c>
       <c r="I12" s="55" t="n">
-        <v>-0.1512578859730255</v>
+        <v>-0.1521422541720909</v>
       </c>
       <c r="J12" s="55" t="n">
-        <v>-0.1899905646404416</v>
+        <v>-0.1904375678197197</v>
       </c>
       <c r="K12" s="56" t="n">
-        <v>-0.0002271492310420564</v>
+        <v>-0.000203139347681125</v>
       </c>
       <c r="L12" s="53" t="n">
-        <v>0.001865752266632825</v>
+        <v>0.001884955157061052</v>
       </c>
       <c r="M12" s="53" t="n">
-        <v>0.005635946860848062</v>
+        <v>0.005748901277086604</v>
       </c>
       <c r="N12" s="53" t="n">
-        <v>0.01558338964418315</v>
+        <v>0.01573493219833821</v>
       </c>
       <c r="O12" s="53" t="n">
-        <v>0.02323527193780128</v>
+        <v>0.02278232409815772</v>
       </c>
       <c r="P12" s="53" t="n">
-        <v>0.05026249135137817</v>
+        <v>0.04979785978522111</v>
       </c>
       <c r="Q12" s="53" t="n">
-        <v>0.07957290701294706</v>
+        <v>0.07971910006343286</v>
       </c>
     </row>
     <row r="13">
@@ -5597,13 +5597,13 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>1608</v>
+        <v>1612</v>
       </c>
       <c r="C13" s="57" t="n">
-        <v>-0.01157704306645435</v>
+        <v>-0.01155094096414611</v>
       </c>
       <c r="D13" s="57" t="n">
-        <v>-0.02421159985992183</v>
+        <v>-0.02431542231598555</v>
       </c>
       <c r="E13" s="57" t="n">
         <v>-0.03244601579100104</v>
@@ -5615,34 +5615,34 @@
         <v>-0.07588882845319378</v>
       </c>
       <c r="H13" s="57" t="n">
-        <v>-0.1131575503036025</v>
+        <v>-0.1134978845445914</v>
       </c>
       <c r="I13" s="57" t="n">
-        <v>-0.1832947696697549</v>
+        <v>-0.1839974181228775</v>
       </c>
       <c r="J13" s="57" t="n">
         <v>-0.23256809555238</v>
       </c>
       <c r="K13" s="58" t="n">
-        <v>-0.0006677094929001814</v>
+        <v>-0.000571993887443778</v>
       </c>
       <c r="L13" s="57" t="n">
-        <v>-0.006491066504694443</v>
-      </c>
-      <c r="M13" s="57" t="n">
-        <v>-5.740979725260553e-05</v>
+        <v>-0.006527546712554788</v>
+      </c>
+      <c r="M13" s="59" t="n">
+        <v>0.0001735087297388693</v>
       </c>
       <c r="N13" s="57" t="n">
-        <v>-0.01104092154715841</v>
+        <v>-0.0112785889807443</v>
       </c>
       <c r="O13" s="59" t="n">
-        <v>0.001299269929878499</v>
+        <v>0.000260576322308137</v>
       </c>
       <c r="P13" s="59" t="n">
-        <v>0.01822560765464876</v>
+        <v>0.01794269583443453</v>
       </c>
       <c r="Q13" s="59" t="n">
-        <v>0.03699537610100867</v>
+        <v>0.03758857233077251</v>
       </c>
     </row>
     <row r="14">
@@ -5658,16 +5658,16 @@
         <v>-0.0009901874870281713</v>
       </c>
       <c r="D14" s="60" t="n">
-        <v>0.003455870557057539</v>
+        <v>0.003283266500884618</v>
       </c>
       <c r="E14" s="60" t="n">
-        <v>0.01068575441663289</v>
+        <v>0.01044488023382595</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="G14" s="61" t="n">
-        <v>-0.01490371286284775</v>
+        <v>-0.01599225386674075</v>
       </c>
       <c r="H14" s="60" t="n">
         <v>0.01668719888838466</v>
@@ -5679,25 +5679,25 @@
         <v>-0.2272541520355096</v>
       </c>
       <c r="K14" s="62" t="n">
-        <v>0.009919146086525998</v>
+        <v>0.009988759589674157</v>
       </c>
       <c r="L14" s="60" t="n">
-        <v>0.02117640391228492</v>
+        <v>0.02107114210431538</v>
       </c>
       <c r="M14" s="60" t="n">
-        <v>0.04307436041038132</v>
+        <v>0.04306440475456585</v>
       </c>
       <c r="N14" s="60" t="n">
-        <v>0.04994419404318762</v>
+        <v>0.04861798560570874</v>
       </c>
       <c r="O14" s="60" t="n">
-        <v>0.1311440191218657</v>
+        <v>0.1304456597552842</v>
       </c>
       <c r="P14" s="60" t="n">
-        <v>0.09667555671956063</v>
+        <v>0.09709529335246903</v>
       </c>
       <c r="Q14" s="60" t="n">
-        <v>0.04230931961787909</v>
+        <v>0.04290251584764293</v>
       </c>
     </row>
     <row r="15">
@@ -5707,52 +5707,52 @@
         </is>
       </c>
       <c r="B15" s="26" t="n">
-        <v>21230</v>
+        <v>21278</v>
       </c>
       <c r="C15" s="61" t="n">
-        <v>-0.01017032688710473</v>
+        <v>-0.0103227652297227</v>
       </c>
       <c r="D15" s="61" t="n">
-        <v>-0.01710038966777816</v>
+        <v>-0.01718806763198594</v>
       </c>
       <c r="E15" s="61" t="n">
-        <v>-0.03248639263481246</v>
+        <v>-0.0327886893974465</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>20142</v>
+        <v>20199</v>
       </c>
       <c r="G15" s="61" t="n">
-        <v>-0.07190022404703766</v>
+        <v>-0.07160185214483861</v>
       </c>
       <c r="H15" s="61" t="n">
-        <v>-0.1328246541459408</v>
+        <v>-0.1316879991235256</v>
       </c>
       <c r="I15" s="61" t="n">
-        <v>-0.239282484851286</v>
+        <v>-0.2392530611928376</v>
       </c>
       <c r="J15" s="61" t="n">
-        <v>-0.3346216638732686</v>
+        <v>-0.3352103728726336</v>
       </c>
       <c r="K15" s="62" t="n">
-        <v>0.0007390066864494393</v>
+        <v>0.000656181846979631</v>
       </c>
       <c r="L15" s="60" t="n">
-        <v>0.0006201436874492261</v>
+        <v>0.0005998079714448212</v>
       </c>
       <c r="M15" s="61" t="n">
-        <v>-9.778664106402379e-05</v>
+        <v>-0.0001691648767065956</v>
       </c>
       <c r="N15" s="61" t="n">
-        <v>-0.007052317141002296</v>
+        <v>-0.006991612672389125</v>
       </c>
       <c r="O15" s="61" t="n">
-        <v>-0.01836783391245977</v>
+        <v>-0.01792953825662602</v>
       </c>
       <c r="P15" s="61" t="n">
-        <v>-0.03776210752688236</v>
+        <v>-0.03731294723552558</v>
       </c>
       <c r="Q15" s="61" t="n">
-        <v>-0.06505819221987996</v>
+        <v>-0.06505370498948104</v>
       </c>
     </row>
     <row r="16">
@@ -5771,10 +5771,10 @@
         <v>-0.02264482161427489</v>
       </c>
       <c r="E16" s="63" t="n">
-        <v>-0.0576559970351298</v>
+        <v>-0.05772877985956448</v>
       </c>
       <c r="F16" s="34" t="n">
-        <v>1469</v>
+        <v>1472</v>
       </c>
       <c r="G16" s="63" t="n">
         <v>-0.07902584252915901</v>
@@ -5783,31 +5783,31 @@
         <v>-0.1230971397096432</v>
       </c>
       <c r="I16" s="63" t="n">
-        <v>-0.2598126555958944</v>
+        <v>-0.2602969018015276</v>
       </c>
       <c r="J16" s="63" t="n">
         <v>-0.3348660542707862</v>
       </c>
       <c r="K16" s="64" t="n">
-        <v>-0.001838927900715603</v>
+        <v>-0.001769314397567445</v>
       </c>
       <c r="L16" s="63" t="n">
-        <v>-0.004924288259047505</v>
+        <v>-0.004856946010844132</v>
       </c>
       <c r="M16" s="63" t="n">
-        <v>-0.02526739104138137</v>
+        <v>-0.02510925533882458</v>
       </c>
       <c r="N16" s="63" t="n">
-        <v>-0.01417793562312364</v>
+        <v>-0.01441560305670953</v>
       </c>
       <c r="O16" s="63" t="n">
-        <v>-0.008640319476162173</v>
+        <v>-0.009338678842743642</v>
       </c>
       <c r="P16" s="63" t="n">
-        <v>-0.05829227827149075</v>
+        <v>-0.05835678784421561</v>
       </c>
       <c r="Q16" s="63" t="n">
-        <v>-0.06530258261739752</v>
+        <v>-0.06470938638763368</v>
       </c>
     </row>
     <row r="17">
@@ -5817,31 +5817,31 @@
         </is>
       </c>
       <c r="B17" s="45" t="n">
-        <v>83559</v>
+        <v>83765</v>
       </c>
       <c r="C17" s="65" t="n">
-        <v>-0.01090933357355417</v>
+        <v>-0.01097894707670233</v>
       </c>
       <c r="D17" s="65" t="n">
-        <v>-0.01772053335522739</v>
+        <v>-0.01778787560343076</v>
       </c>
       <c r="E17" s="65" t="n">
-        <v>-0.03238860599374843</v>
+        <v>-0.03261952452073991</v>
       </c>
       <c r="F17" s="45" t="n">
-        <v>79416</v>
+        <v>79622</v>
       </c>
       <c r="G17" s="65" t="n">
-        <v>-0.06484790690603537</v>
+        <v>-0.06461023947244948</v>
       </c>
       <c r="H17" s="65" t="n">
-        <v>-0.114456820233481</v>
+        <v>-0.1137584608668996</v>
       </c>
       <c r="I17" s="65" t="n">
-        <v>-0.2015203773244036</v>
+        <v>-0.201940113957312</v>
       </c>
       <c r="J17" s="65" t="n">
-        <v>-0.2695634716533887</v>
+        <v>-0.2701566678831525</v>
       </c>
       <c r="K17" s="66" t="n"/>
       <c r="L17" s="67" t="n"/>
@@ -5883,7 +5883,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I164"/>
+  <dimension ref="A1:I189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -5907,7 +5907,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>생성기 scripts/yz_persistence_probe.py   ·   206종목 / 839일 / 167,208관측 (BM 제외)</t>
+          <t>생성기 scripts/yz_persistence_probe.py   ·   206종목 / 840일 / 167,414관측 (BM 제외)</t>
         </is>
       </c>
     </row>
@@ -6038,19 +6038,19 @@
         </is>
       </c>
       <c r="B18" s="10" t="n">
-        <v>0.6605125030145269</v>
+        <v>0.660457704355302</v>
       </c>
       <c r="C18" s="10" t="n">
-        <v>0.2352976246765022</v>
+        <v>0.2352841764679852</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>0.1686898350939093</v>
+        <v>0.1687008052466507</v>
       </c>
       <c r="E18" s="75" t="n">
-        <v>37.1704552055547</v>
+        <v>37.17426791421134</v>
       </c>
       <c r="F18" s="10" t="n">
-        <v>0.773144712217153</v>
+        <v>0.7728031966607084</v>
       </c>
       <c r="G18" s="8" t="n">
         <v>15</v>
@@ -6069,19 +6069,19 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>0.03337745918820539</v>
+        <v>0.03337087156969538</v>
       </c>
       <c r="C19" s="10" t="n">
-        <v>0.05271555589863194</v>
+        <v>0.05270972927395807</v>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.2836877697179101</v>
+        <v>0.2836853769051436</v>
       </c>
       <c r="E19" s="75" t="n">
-        <v>19.76243017602216</v>
+        <v>19.75353020106487</v>
       </c>
       <c r="F19" s="10" t="n">
-        <v>0.1265602455544317</v>
+        <v>0.1268859059879447</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>0</v>
@@ -6100,19 +6100,19 @@
         </is>
       </c>
       <c r="B20" s="20" t="n">
-        <v>0.04747242048476285</v>
+        <v>0.04738498563267176</v>
       </c>
       <c r="C20" s="20" t="n">
-        <v>0.063018738096076</v>
+        <v>0.06296145720126747</v>
       </c>
       <c r="D20" s="20" t="n">
-        <v>0.282284995366429</v>
+        <v>0.2823014477647073</v>
       </c>
       <c r="E20" s="76" t="n">
-        <v>20.65098901256574</v>
+        <v>20.64481486787228</v>
       </c>
       <c r="F20" s="20" t="n">
-        <v>0.203816323771662</v>
+        <v>0.2021207127138173</v>
       </c>
       <c r="G20" s="18" t="n">
         <v>0</v>
@@ -6203,22 +6203,22 @@
         </is>
       </c>
       <c r="B29" s="77" t="n">
-        <v>0.9897537849750553</v>
+        <v>0.9897608667552293</v>
       </c>
       <c r="C29" s="77" t="n">
-        <v>0.9412590504854719</v>
+        <v>0.9412807065641696</v>
       </c>
       <c r="D29" s="77" t="n">
-        <v>0.7836484105411087</v>
+        <v>0.7837543708816325</v>
       </c>
       <c r="E29" s="77" t="n">
-        <v>0.7058507943001757</v>
+        <v>0.7059879091181237</v>
       </c>
       <c r="F29" s="77" t="n">
-        <v>0.6255653469002024</v>
+        <v>0.6253621681766482</v>
       </c>
       <c r="G29" s="77" t="n">
-        <v>0.5459660236599715</v>
+        <v>0.545936716600368</v>
       </c>
     </row>
     <row r="30">
@@ -6228,22 +6228,22 @@
         </is>
       </c>
       <c r="B30" s="77" t="n">
-        <v>0.864991822645006</v>
+        <v>0.8649948388075653</v>
       </c>
       <c r="C30" s="77" t="n">
-        <v>0.1650022737485345</v>
+        <v>0.1648265693096623</v>
       </c>
       <c r="D30" s="77" t="n">
-        <v>0.01659489791914334</v>
+        <v>0.01676782080480083</v>
       </c>
       <c r="E30" s="77" t="n">
-        <v>0.001159509602888533</v>
+        <v>0.001198301162581042</v>
       </c>
       <c r="F30" s="78" t="n">
-        <v>-0.01472800846403322</v>
+        <v>-0.01471445282896061</v>
       </c>
       <c r="G30" s="77" t="n">
-        <v>0.0111603317765139</v>
+        <v>0.01102564869034226</v>
       </c>
     </row>
     <row r="31">
@@ -6253,22 +6253,22 @@
         </is>
       </c>
       <c r="B31" s="79" t="n">
-        <v>0.6644161142367285</v>
+        <v>0.6643282978799837</v>
       </c>
       <c r="C31" s="79" t="n">
-        <v>0.2163603680041757</v>
+        <v>0.2161245614798244</v>
       </c>
       <c r="D31" s="79" t="n">
-        <v>0.02691797910159656</v>
+        <v>0.02696498670390433</v>
       </c>
       <c r="E31" s="79" t="n">
-        <v>0.006370561430771074</v>
+        <v>0.006534866143610491</v>
       </c>
       <c r="F31" s="79" t="n">
-        <v>0.02625729268720681</v>
+        <v>0.02615407770334583</v>
       </c>
       <c r="G31" s="79" t="n">
-        <v>0.009243507980988797</v>
+        <v>0.008631485024205462</v>
       </c>
     </row>
     <row r="33">
@@ -6312,10 +6312,10 @@
         </is>
       </c>
       <c r="B36" s="10" t="n">
-        <v>0.3588987752611864</v>
+        <v>0.3588917478983216</v>
       </c>
       <c r="C36" s="10" t="n">
-        <v>0.01869139679467659</v>
+        <v>0.0196606487246931</v>
       </c>
       <c r="D36" s="9" t="n">
         <v>0.2718446601941747</v>
@@ -6331,10 +6331,10 @@
         </is>
       </c>
       <c r="B37" s="10" t="n">
-        <v>0.07957266159472032</v>
+        <v>0.07954931959673575</v>
       </c>
       <c r="C37" s="10" t="n">
-        <v>0.01874219042323191</v>
+        <v>0.01860641106648545</v>
       </c>
       <c r="D37" s="9" t="n">
         <v>0</v>
@@ -6350,10 +6350,10 @@
         </is>
       </c>
       <c r="B38" s="20" t="n">
-        <v>0.09605454338755848</v>
+        <v>0.09597856869201346</v>
       </c>
       <c r="C38" s="20" t="n">
-        <v>0.01768212602149145</v>
+        <v>0.01754124223809981</v>
       </c>
       <c r="D38" s="19" t="n">
         <v>0</v>
@@ -6415,19 +6415,19 @@
         </is>
       </c>
       <c r="B44" s="81" t="n">
-        <v>54.12927955396811</v>
+        <v>54.14383859466041</v>
       </c>
       <c r="C44" s="81" t="n">
-        <v>25.8036414321805</v>
+        <v>25.77615444821289</v>
       </c>
       <c r="D44" s="81" t="n">
-        <v>11.49925951737956</v>
+        <v>11.50100008696408</v>
       </c>
       <c r="E44" s="81" t="n">
-        <v>5.675581496646049</v>
+        <v>5.678754674319507</v>
       </c>
       <c r="F44" s="81" t="n">
-        <v>2.892237999825769</v>
+        <v>2.900252195843117</v>
       </c>
     </row>
     <row r="45">
@@ -6437,19 +6437,19 @@
         </is>
       </c>
       <c r="B45" s="81" t="n">
-        <v>27.28334703413664</v>
+        <v>27.26094843223633</v>
       </c>
       <c r="C45" s="81" t="n">
-        <v>30.87872625795007</v>
+        <v>30.90178802798653</v>
       </c>
       <c r="D45" s="81" t="n">
-        <v>24.13793103448276</v>
+        <v>24.12110218536754</v>
       </c>
       <c r="E45" s="81" t="n">
-        <v>11.94565828754381</v>
+        <v>11.95041893409346</v>
       </c>
       <c r="F45" s="81" t="n">
-        <v>5.75433738588673</v>
+        <v>5.765742420316144</v>
       </c>
     </row>
     <row r="46">
@@ -6459,19 +6459,19 @@
         </is>
       </c>
       <c r="B46" s="81" t="n">
-        <v>13.70754348674793</v>
+        <v>13.70485840478046</v>
       </c>
       <c r="C46" s="81" t="n">
-        <v>23.97084978093957</v>
+        <v>23.97592448254958</v>
       </c>
       <c r="D46" s="81" t="n">
-        <v>25.62790092395784</v>
+        <v>25.62570364596865</v>
       </c>
       <c r="E46" s="81" t="n">
-        <v>20.3400858890383</v>
+        <v>20.3386160907595</v>
       </c>
       <c r="F46" s="81" t="n">
-        <v>16.35361991931636</v>
+        <v>16.3548973759418</v>
       </c>
     </row>
     <row r="47">
@@ -6481,19 +6481,19 @@
         </is>
       </c>
       <c r="B47" s="81" t="n">
-        <v>4.54742312689476</v>
+        <v>4.543685962561065</v>
       </c>
       <c r="C47" s="81" t="n">
-        <v>15.50021654395842</v>
+        <v>15.4943582205698</v>
       </c>
       <c r="D47" s="81" t="n">
-        <v>24.56907752273711</v>
+        <v>24.57308374043491</v>
       </c>
       <c r="E47" s="81" t="n">
-        <v>29.15547856214812</v>
+        <v>29.15567852665254</v>
       </c>
       <c r="F47" s="81" t="n">
-        <v>26.22780424426159</v>
+        <v>26.23319354978168</v>
       </c>
     </row>
     <row r="48">
@@ -6503,19 +6503,19 @@
         </is>
       </c>
       <c r="B48" s="82" t="n">
-        <v>1.887356420000854</v>
+        <v>1.901108269394715</v>
       </c>
       <c r="C48" s="82" t="n">
-        <v>4.919082796020326</v>
+        <v>4.914748508098891</v>
       </c>
       <c r="D48" s="82" t="n">
-        <v>14.5779068277894</v>
+        <v>14.59079283887468</v>
       </c>
       <c r="E48" s="82" t="n">
-        <v>32.55476322644007</v>
+        <v>32.54901960784314</v>
       </c>
       <c r="F48" s="82" t="n">
-        <v>46.06089072974935</v>
+        <v>46.04433077578858</v>
       </c>
     </row>
     <row r="50">
@@ -6564,19 +6564,19 @@
         </is>
       </c>
       <c r="B53" s="81" t="n">
-        <v>18.91608849325828</v>
+        <v>18.90490917802849</v>
       </c>
       <c r="C53" s="81" t="n">
-        <v>19.63607802068334</v>
+        <v>19.64542405366555</v>
       </c>
       <c r="D53" s="81" t="n">
-        <v>20.27752323602566</v>
+        <v>20.27703968288539</v>
       </c>
       <c r="E53" s="81" t="n">
-        <v>20.80115198324388</v>
+        <v>20.79540009583134</v>
       </c>
       <c r="F53" s="81" t="n">
-        <v>20.36915826678885</v>
+        <v>20.37722698958923</v>
       </c>
     </row>
     <row r="54">
@@ -6586,19 +6586,19 @@
         </is>
       </c>
       <c r="B54" s="81" t="n">
-        <v>19.37046004842615</v>
+        <v>19.37071086365402</v>
       </c>
       <c r="C54" s="81" t="n">
-        <v>20.13576617087513</v>
+        <v>20.13466269584358</v>
       </c>
       <c r="D54" s="81" t="n">
-        <v>20.10549982704946</v>
+        <v>20.11739824765851</v>
       </c>
       <c r="E54" s="81" t="n">
-        <v>20.0492909028018</v>
+        <v>20.03970823082567</v>
       </c>
       <c r="F54" s="81" t="n">
-        <v>20.33898305084746</v>
+        <v>20.33751996201821</v>
       </c>
     </row>
     <row r="55">
@@ -6608,19 +6608,19 @@
         </is>
       </c>
       <c r="B55" s="81" t="n">
-        <v>19.44420396502467</v>
+        <v>19.45728730069568</v>
       </c>
       <c r="C55" s="81" t="n">
-        <v>20.40948835598649</v>
+        <v>20.40357775569287</v>
       </c>
       <c r="D55" s="81" t="n">
-        <v>19.81213747727469</v>
+        <v>19.79864321825174</v>
       </c>
       <c r="E55" s="81" t="n">
-        <v>19.91602458661588</v>
+        <v>19.92827204770341</v>
       </c>
       <c r="F55" s="81" t="n">
-        <v>20.41814561509826</v>
+        <v>20.41221967765631</v>
       </c>
     </row>
     <row r="56">
@@ -6630,19 +6630,19 @@
         </is>
       </c>
       <c r="B56" s="81" t="n">
-        <v>20.23964010727572</v>
+        <v>20.23403428472732</v>
       </c>
       <c r="C56" s="81" t="n">
-        <v>19.73354096375119</v>
+        <v>19.73746707543503</v>
       </c>
       <c r="D56" s="81" t="n">
-        <v>19.14092914611991</v>
+        <v>19.12431452135239</v>
       </c>
       <c r="E56" s="81" t="n">
-        <v>20.43429362401592</v>
+        <v>20.43266116844423</v>
       </c>
       <c r="F56" s="81" t="n">
-        <v>20.45159615883727</v>
+        <v>20.47152295004102</v>
       </c>
     </row>
     <row r="57">
@@ -6652,19 +6652,19 @@
         </is>
       </c>
       <c r="B57" s="82" t="n">
-        <v>20.75059910989387</v>
+        <v>20.75697381349054</v>
       </c>
       <c r="C57" s="82" t="n">
-        <v>20.13437179048271</v>
+        <v>20.12901020974839</v>
       </c>
       <c r="D57" s="82" t="n">
-        <v>20.3226634714139</v>
+        <v>20.33833141099577</v>
       </c>
       <c r="E57" s="82" t="n">
-        <v>19.27850051352277</v>
+        <v>19.27890982100901</v>
       </c>
       <c r="F57" s="82" t="n">
-        <v>19.51386511468675</v>
+        <v>19.49677474475629</v>
       </c>
     </row>
     <row r="59">
@@ -6713,19 +6713,19 @@
         </is>
       </c>
       <c r="B62" s="81" t="n">
-        <v>22.04228126231015</v>
+        <v>22.0343426399266</v>
       </c>
       <c r="C62" s="81" t="n">
-        <v>20.79922965816081</v>
+        <v>20.81094070869926</v>
       </c>
       <c r="D62" s="81" t="n">
-        <v>18.91276754059614</v>
+        <v>18.90592913007384</v>
       </c>
       <c r="E62" s="81" t="n">
-        <v>18.58887381275441</v>
+        <v>18.61755581771311</v>
       </c>
       <c r="F62" s="81" t="n">
-        <v>19.65684772617849</v>
+        <v>19.63123170358719</v>
       </c>
     </row>
     <row r="63">
@@ -6735,19 +6735,19 @@
         </is>
       </c>
       <c r="B63" s="81" t="n">
-        <v>19.44672929564051</v>
+        <v>19.43388072601556</v>
       </c>
       <c r="C63" s="81" t="n">
-        <v>20.32988441058055</v>
+        <v>20.31114952463267</v>
       </c>
       <c r="D63" s="81" t="n">
-        <v>20.18269189142387</v>
+        <v>20.19878997407087</v>
       </c>
       <c r="E63" s="81" t="n">
-        <v>19.93592796224945</v>
+        <v>19.92653414001729</v>
       </c>
       <c r="F63" s="81" t="n">
-        <v>20.10476644010563</v>
+        <v>20.12964563526361</v>
       </c>
     </row>
     <row r="64">
@@ -6757,19 +6757,19 @@
         </is>
       </c>
       <c r="B64" s="81" t="n">
-        <v>19.34688581314879</v>
+        <v>19.3428608436596</v>
       </c>
       <c r="C64" s="81" t="n">
-        <v>19.71453287197232</v>
+        <v>19.73576270454643</v>
       </c>
       <c r="D64" s="81" t="n">
-        <v>19.92214532871972</v>
+        <v>19.91710202495574</v>
       </c>
       <c r="E64" s="81" t="n">
-        <v>20.29411764705882</v>
+        <v>20.28409826864125</v>
       </c>
       <c r="F64" s="81" t="n">
-        <v>20.72231833910035</v>
+        <v>20.72017615819697</v>
       </c>
     </row>
     <row r="65">
@@ -6779,19 +6779,19 @@
         </is>
       </c>
       <c r="B65" s="81" t="n">
-        <v>18.90407404203788</v>
+        <v>18.90946768553296</v>
       </c>
       <c r="C65" s="81" t="n">
-        <v>19.66525387077242</v>
+        <v>19.67361740707162</v>
       </c>
       <c r="D65" s="81" t="n">
-        <v>20.47833232419341</v>
+        <v>20.46367050900142</v>
       </c>
       <c r="E65" s="81" t="n">
-        <v>20.81134849926477</v>
+        <v>20.80904891421664</v>
       </c>
       <c r="F65" s="81" t="n">
-        <v>20.14099126373151</v>
+        <v>20.14419548417735</v>
       </c>
     </row>
     <row r="66">
@@ -6801,19 +6801,19 @@
         </is>
       </c>
       <c r="B66" s="82" t="n">
-        <v>18.68202175303903</v>
+        <v>18.70050242697777</v>
       </c>
       <c r="C66" s="82" t="n">
-        <v>19.71422478140328</v>
+        <v>19.69258281529422</v>
       </c>
       <c r="D66" s="82" t="n">
-        <v>20.52889741949243</v>
+        <v>20.53989610831985</v>
       </c>
       <c r="E66" s="82" t="n">
-        <v>20.92557048411175</v>
+        <v>20.91458741377842</v>
       </c>
       <c r="F66" s="82" t="n">
-        <v>20.14928556195351</v>
+        <v>20.15243123562974</v>
       </c>
     </row>
     <row r="68">
@@ -6888,19 +6888,19 @@
         <v>10</v>
       </c>
       <c r="B75" s="8" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C75" s="77" t="n">
-        <v>0.7607006076365543</v>
+        <v>0.7612921038001222</v>
       </c>
       <c r="D75" s="77" t="n">
-        <v>0.7078445088843064</v>
+        <v>0.7087108478428411</v>
       </c>
       <c r="E75" s="77" t="n">
-        <v>0.0007728983455076305</v>
+        <v>0.001400604719466444</v>
       </c>
       <c r="F75" s="77" t="n">
-        <v>0.001988596522691421</v>
+        <v>0.003863536637215695</v>
       </c>
     </row>
     <row r="76">
@@ -6908,19 +6908,19 @@
         <v>20</v>
       </c>
       <c r="B76" s="8" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C76" s="77" t="n">
-        <v>0.7813102405183503</v>
+        <v>0.7831250211230006</v>
       </c>
       <c r="D76" s="77" t="n">
-        <v>0.7092714466755501</v>
+        <v>0.7123798614312123</v>
       </c>
       <c r="E76" s="78" t="n">
-        <v>-0.02395108598228774</v>
+        <v>-0.0231276859326879</v>
       </c>
       <c r="F76" s="78" t="n">
-        <v>-0.01677632944869677</v>
+        <v>-0.01673560966198721</v>
       </c>
     </row>
     <row r="77">
@@ -6948,19 +6948,19 @@
         <v>60</v>
       </c>
       <c r="B78" s="8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C78" s="77" t="n">
-        <v>0.7904436529067442</v>
+        <v>0.7956180173161924</v>
       </c>
       <c r="D78" s="77" t="n">
-        <v>0.7058020434078417</v>
+        <v>0.7131741540127791</v>
       </c>
       <c r="E78" s="77" t="n">
-        <v>0.03703845033932317</v>
+        <v>0.04485125036888023</v>
       </c>
       <c r="F78" s="78" t="n">
-        <v>-0.01024092983126564</v>
+        <v>-0.007241296715140746</v>
       </c>
     </row>
     <row r="79">
@@ -7070,10 +7070,10 @@
         </is>
       </c>
       <c r="B92" s="77" t="n">
-        <v>0.7904436529067442</v>
+        <v>0.7956180173161924</v>
       </c>
       <c r="C92" s="77" t="n">
-        <v>0.7058020434078417</v>
+        <v>0.7131741540127791</v>
       </c>
     </row>
     <row r="93">
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="B93" s="77" t="n">
-        <v>0.6561481076992204</v>
+        <v>0.6648237499947262</v>
       </c>
       <c r="C93" s="77" t="n">
-        <v>0.571640059872469</v>
+        <v>0.5829997315494369</v>
       </c>
     </row>
     <row r="94">
@@ -7096,10 +7096,10 @@
         </is>
       </c>
       <c r="B94" s="77" t="n">
-        <v>0.7255124517601879</v>
+        <v>0.729485788941853</v>
       </c>
       <c r="C94" s="77" t="n">
-        <v>0.6392243905407318</v>
+        <v>0.6473625884707169</v>
       </c>
     </row>
     <row r="95">
@@ -7109,10 +7109,10 @@
         </is>
       </c>
       <c r="B95" s="79" t="n">
-        <v>0.8063033337941801</v>
+        <v>0.8120501071024596</v>
       </c>
       <c r="C95" s="79" t="n">
-        <v>0.7162495715549841</v>
+        <v>0.7244313631535626</v>
       </c>
     </row>
     <row r="96">
@@ -7122,10 +7122,10 @@
         </is>
       </c>
       <c r="B96" s="86" t="n">
-        <v>0.7166520443414675</v>
+        <v>0.722985769092271</v>
       </c>
       <c r="C96" s="86" t="n">
-        <v>0.6434384130714084</v>
+        <v>0.6539571012797981</v>
       </c>
     </row>
     <row r="97">
@@ -7135,10 +7135,10 @@
         </is>
       </c>
       <c r="B97" s="86" t="n">
-        <v>0.7671495988178935</v>
+        <v>0.7728535447850021</v>
       </c>
       <c r="C97" s="86" t="n">
-        <v>0.6901067493484102</v>
+        <v>0.6994516601177356</v>
       </c>
     </row>
     <row r="98">
@@ -7148,10 +7148,10 @@
         </is>
       </c>
       <c r="B98" s="86" t="n">
-        <v>0.8297734993232234</v>
+        <v>0.8348484853513048</v>
       </c>
       <c r="C98" s="86" t="n">
-        <v>0.737023336252396</v>
+        <v>0.7446986691011721</v>
       </c>
     </row>
     <row r="99">
@@ -7161,10 +7161,10 @@
         </is>
       </c>
       <c r="B99" s="87" t="n">
-        <v>0.9843777872821859</v>
+        <v>0.9827035557367071</v>
       </c>
       <c r="C99" s="87" t="n">
-        <v>0.9654866627502496</v>
+        <v>0.962277718619152</v>
       </c>
     </row>
     <row r="100">
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="B100" s="77" t="n">
-        <v>0.03703845033932317</v>
+        <v>0.04485125036888023</v>
       </c>
       <c r="C100" s="78" t="n">
-        <v>-0.01024092983126564</v>
+        <v>-0.007241296715140746</v>
       </c>
     </row>
     <row r="101">
@@ -7187,10 +7187,10 @@
         </is>
       </c>
       <c r="B101" s="77" t="n">
-        <v>0.1542171672792637</v>
+        <v>0.1642849078927525</v>
       </c>
       <c r="C101" s="77" t="n">
-        <v>0.09368593939261444</v>
+        <v>0.1048263895294591</v>
       </c>
     </row>
     <row r="102">
@@ -7200,10 +7200,10 @@
         </is>
       </c>
       <c r="B102" s="79" t="n">
-        <v>0.4983672053989459</v>
+        <v>0.5131041299113193</v>
       </c>
       <c r="C102" s="79" t="n">
-        <v>0.4754239048519299</v>
+        <v>0.4738623661190644</v>
       </c>
     </row>
     <row r="104">
@@ -7232,7 +7232,7 @@
         </is>
       </c>
       <c r="B107" s="77" t="n">
-        <v>0.9379540798345463</v>
+        <v>0.9401430071692708</v>
       </c>
     </row>
     <row r="108">
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="B108" s="77" t="n">
-        <v>0.9405423725644668</v>
+        <v>0.9424358406294017</v>
       </c>
     </row>
     <row r="109">
@@ -7252,7 +7252,7 @@
         </is>
       </c>
       <c r="B109" s="77" t="n">
-        <v>0.9731691974049852</v>
+        <v>0.9734378314611267</v>
       </c>
     </row>
     <row r="110">
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="B110" s="77" t="n">
-        <v>0.8054894572714477</v>
+        <v>0.8128542890390613</v>
       </c>
     </row>
     <row r="111">
@@ -7272,7 +7272,7 @@
         </is>
       </c>
       <c r="B111" s="85" t="n">
-        <v>-0.3664518604630352</v>
+        <v>-0.3598285706423403</v>
       </c>
     </row>
     <row r="112">
@@ -7282,7 +7282,7 @@
         </is>
       </c>
       <c r="B112" s="86" t="n">
-        <v>0.8506751761244873</v>
+        <v>0.8507053107231743</v>
       </c>
     </row>
     <row r="113">
@@ -7292,7 +7292,7 @@
         </is>
       </c>
       <c r="B113" s="88" t="n">
-        <v>-0.04265174146742142</v>
+        <v>-0.05165100750858145</v>
       </c>
     </row>
     <row r="114">
@@ -7394,301 +7394,519 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="5" t="inlineStr">
-        <is>
-          <t>★ 결론</t>
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>[H] 왜 서열이 남는가 — 변동성은 다 같이 움직인다</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   **YZ 수준은 이 기간(3.3년) 종목의 안정적 특성이다.** 네 잣대가 전부 같은 방향이고 차이가 크다 —</t>
+          <t xml:space="preserve">   '수준은 불안정한데 서열은 안정적' 이 성립하려면 변동성이 종목마다 따로가 아니라 **다 같이, 비례적으로** 움직여야 한다. 실제로 그런지 쟀다.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      ICC  YZ 0.661  vs  R² 0.033 / RSI 0.047</t>
+          <t xml:space="preserve">   (중첩 0 인 20일 블록 사이의 변화 Δlog(YZ) — 188종목 × 44구간. 롤링값 일간 차분을 쓰면 창이 겹쳐 공통 요인이 과대 추정된다.)</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      1년 뒤 순위상관  YZ +0.626  vs  R² -0.015 / RSI +0.026   (2년 뒤에도 YZ +0.546)</t>
+          <t xml:space="preserve">      · 종목 쌍 상관 평균 **+0.313** (음수 쌍 4.7%) · 제1주성분이 분산의 **32.3%** (제2 5.4%)</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      1년 전이 대각  YZ 37.2%  vs  R² 19.8% / RSI 20.7%   (무작위 20%)</t>
+          <t xml:space="preserve">      · 시장 공통 변화는 구간마다 통째로 **±19%** (최대 +51% / 최소 -29%)</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">      시대 ρ  YZ 0.773  vs  R² 0.127 / RSI 0.204</t>
+          <t xml:space="preserve">      · **β&gt;0 인 종목 100.0%** — 시장 변동성이 내리면 **예외 없이 전 종목이 같은 방향**이다</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   **R²·RSI 는 정반대다** — ICC 가 0.03~0.05 이고, 60거래일이면 자기상관이 0 으로 떨어지며, 전이 대각이 정확히 무작위(20%)다. 206종목 전부가 양쪽을 오간다.</t>
+          <t xml:space="preserve">      · β 중앙 **1.02** (25~75% 0.78~1.20), 0.5~1.5 구간에 89.4% — 로그에서 β≈1 은 **평행 이동**, 즉 비례적 변화다</t>
         </is>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="43" t="inlineStr"/>
+      <c r="A137" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      · 종목별 R² 중앙 **0.348** — 개별 변동성 변화의 35% 가 공통분, 나머지 65% 가 종목 고유분</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ⇒ **12셀 표의 세 축은 성격이 같지 않다.**</t>
+          <t xml:space="preserve">   ⇒ **공통 요인이 방향을 정하고(β&gt;0 100%) 크기도 대체로 비례한다** — 그래서 수준이 통째로 2.66배 움직여도 서열이 남는다.</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">     R²·RSI 축은 진짜 **상태** 축이다 — 같은 종목이 날마다 다른 칸에 들어간다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     **YZ 축은 사실상 종목 그룹 축**이다 — YZ高 vs YZ低 비교는 같은 종목의 다른 상태를 비교하는 게 아니라 **대체로 다른 회사들을 비교**하는 것이다.</t>
+          <t xml:space="preserve">   ⇒ 동시에 **고유분 65% 가 서열을 조금씩 갈아엎는다** — 그래서 서열이 '영구' 가 아니라 아래처럼 감쇠한다.</t>
         </is>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">     그래서 YZ 로 갈린 두 집단 사이에 무엇이 달라 보이든, 그것은 **구성의 차이**일 수 있고 변동성의 효과라고 단정할 수 없다(주석 ⑦ 이 그 함정이었다).</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="43" t="inlineStr"/>
-    </row>
-    <row r="143">
-      <c r="A143" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⚠ **ICC 는 창 길이에 오염된다** ([E] 참조) — 단독으로 인용하지 말 것. 창에 견고한 증거는 비중첩 블록 상관과 시대 ρ 다.</t>
+      <c r="A141" s="74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   서열의 감쇠 (중첩 0 · 60일 블록, 간격별 순위상관)</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="30" customHeight="1">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>간격(거래일)</t>
+        </is>
+      </c>
+      <c r="B143" s="6" t="inlineStr">
+        <is>
+          <t>≈개월</t>
+        </is>
+      </c>
+      <c r="C143" s="6" t="inlineStr">
+        <is>
+          <t>순위상관 ρ</t>
+        </is>
+      </c>
+      <c r="D143" s="6" t="inlineStr">
+        <is>
+          <t>블록쌍</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⚠ **창을 바꿔도 이 결론은 안 바뀐다** — YZ 는 10일 창에서도 인접 블록 순위상관 0.761 이고, R² 는 어느 창에서도 0 이다.</t>
-        </is>
+      <c r="A144" s="83" t="n">
+        <v>60</v>
+      </c>
+      <c r="B144" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C144" s="10" t="n">
+        <v>0.7956180173161924</v>
+      </c>
+      <c r="D144" s="8" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⚠ 이것은 '안정적이다' 까지다. **왜 안정적인지는 이 시트가 답하지 않는다.**</t>
-        </is>
+      <c r="A145" s="83" t="n">
+        <v>120</v>
+      </c>
+      <c r="B145" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C145" s="10" t="n">
+        <v>0.7131741540127791</v>
+      </c>
+      <c r="D145" s="8" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   ⚠ 다만 완전 고정은 아니다 — 177종목은 양쪽을 오갔고 종목내 σ 도 0.169 로 0 이 아니다. '고정' 이 아니라 '느리게 움직이는 서열' 이다.</t>
-        </is>
+      <c r="A146" s="83" t="n">
+        <v>180</v>
+      </c>
+      <c r="B146" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C146" s="10" t="n">
+        <v>0.6777540917902304</v>
+      </c>
+      <c r="D146" s="8" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="83" t="n">
+        <v>240</v>
+      </c>
+      <c r="B147" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="C147" s="10" t="n">
+        <v>0.6310852347465272</v>
+      </c>
+      <c r="D147" s="8" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>[참고] 어떤 회사가 변동성이 높나 — 답이 아니고, 결과도 예상 범위다</t>
-        </is>
+      <c r="A148" s="83" t="n">
+        <v>300</v>
+      </c>
+      <c r="B148" s="8" t="n">
+        <v>15</v>
+      </c>
+      <c r="C148" s="10" t="n">
+        <v>0.6093022876607457</v>
+      </c>
+      <c r="D148" s="8" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   1차 지적 때 한 횡단면 분석. 우회의 기록으로 남긴다 — 종속변수는 종목별 YZ高 비율(0~1).</t>
-        </is>
-      </c>
-    </row>
-    <row r="151" ht="30" customHeight="1">
-      <c r="A151" s="6" t="inlineStr">
-        <is>
-          <t>변수</t>
-        </is>
-      </c>
-      <c r="B151" s="6" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C151" s="6" t="inlineStr">
-        <is>
-          <t>ρ</t>
-        </is>
-      </c>
-      <c r="D151" s="6" t="inlineStr">
-        <is>
-          <t>η²</t>
+      <c r="A149" s="83" t="n">
+        <v>360</v>
+      </c>
+      <c r="B149" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="C149" s="10" t="n">
+        <v>0.5815884416489385</v>
+      </c>
+      <c r="D149" s="8" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="84" t="n">
+        <v>420</v>
+      </c>
+      <c r="B150" s="18" t="n">
+        <v>21</v>
+      </c>
+      <c r="C150" s="20" t="n">
+        <v>0.5700081756796969</v>
+      </c>
+      <c r="D150" s="18" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ **'장기간 변하지 않는다' 는 과한 표현이다** — 3개월 0.796 에서 시작해 21개월 0.570 로 내려간다.</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="7" t="inlineStr">
-        <is>
-          <t>회전율(로그)</t>
-        </is>
-      </c>
-      <c r="B152" s="8" t="n">
-        <v>206</v>
-      </c>
-      <c r="C152" s="77" t="n">
-        <v>0.7746380819215893</v>
-      </c>
-      <c r="D152" s="10" t="n"/>
+      <c r="A152" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     첫 6개월에 빠르게 섞이고(0.80→0.71) 이후 완만해져 0.57 근처에 머문다 — **'변하지 않는다' 가 아니라 '빠르게 절반쯤 섞이고 나머지가 오래 남는다'** 다.</t>
+        </is>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="7" t="inlineStr">
-        <is>
-          <t>매출(로그)</t>
-        </is>
-      </c>
-      <c r="B153" s="8" t="n">
-        <v>183</v>
-      </c>
-      <c r="C153" s="78" t="n">
-        <v>-0.674437901632432</v>
-      </c>
-      <c r="D153" s="10" t="n"/>
-    </row>
-    <row r="154">
-      <c r="A154" s="7" t="inlineStr">
-        <is>
-          <t>영업이익(로그·흑자만)</t>
-        </is>
-      </c>
-      <c r="B154" s="8" t="n">
-        <v>168</v>
-      </c>
-      <c r="C154" s="78" t="n">
-        <v>-0.6042532553929978</v>
-      </c>
-      <c r="D154" s="10" t="n"/>
+      <c r="A153" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ 뒤쪽 간격은 블록쌍이 8~10개뿐이라 잡음이 크다. 그리고 우리 표본은 **3.3년** 이므로 그 너머는 모른다.</t>
+        </is>
+      </c>
     </row>
     <row r="155">
-      <c r="A155" s="7" t="inlineStr">
-        <is>
-          <t>시총(로그)</t>
-        </is>
-      </c>
-      <c r="B155" s="8" t="n">
-        <v>206</v>
-      </c>
-      <c r="C155" s="78" t="n">
-        <v>-0.501744381052689</v>
-      </c>
-      <c r="D155" s="10" t="n"/>
+      <c r="A155" s="5" t="inlineStr">
+        <is>
+          <t>★ 결론</t>
+        </is>
+      </c>
     </row>
     <row r="156">
-      <c r="A156" s="7" t="inlineStr">
-        <is>
-          <t>업력(년·우측절단)</t>
-        </is>
-      </c>
-      <c r="B156" s="8" t="n">
-        <v>204</v>
-      </c>
-      <c r="C156" s="78" t="n">
-        <v>-0.2537273358977453</v>
-      </c>
-      <c r="D156" s="10" t="n"/>
+      <c r="A156" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   **YZ 수준은 이 기간(3.3년) 종목의 안정적 특성이다.** 네 잣대가 전부 같은 방향이고 차이가 크다 —</t>
+        </is>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="7" t="inlineStr">
-        <is>
-          <t>영업이익률</t>
-        </is>
-      </c>
-      <c r="B157" s="8" t="n">
-        <v>183</v>
-      </c>
-      <c r="C157" s="78" t="n">
-        <v>-0.1206510519719697</v>
-      </c>
-      <c r="D157" s="10" t="n"/>
+      <c r="A157" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      ICC  YZ 0.660  vs  R² 0.033 / RSI 0.047</t>
+        </is>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="17" t="inlineStr">
-        <is>
-          <t>주가 수준</t>
-        </is>
-      </c>
-      <c r="B158" s="18" t="n">
-        <v>206</v>
-      </c>
-      <c r="C158" s="85" t="n">
-        <v>-0.1165625142102794</v>
-      </c>
-      <c r="D158" s="20" t="n"/>
+      <c r="A158" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      1년 뒤 순위상관  YZ +0.625  vs  R² -0.015 / RSI +0.026   (2년 뒤에도 YZ +0.546)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="25" t="inlineStr">
-        <is>
-          <t>섹터 (37개)</t>
-        </is>
-      </c>
-      <c r="B159" s="26" t="n">
-        <v>206</v>
-      </c>
-      <c r="C159" s="28" t="n"/>
-      <c r="D159" s="28" t="n">
-        <v>0.6128985719768835</v>
+      <c r="A159" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      1년 전이 대각  YZ 37.2%  vs  R² 19.8% / RSI 20.6%   (무작위 20%)</t>
+        </is>
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="33" t="inlineStr">
-        <is>
-          <t>테크 계열 여부</t>
-        </is>
-      </c>
-      <c r="B160" s="34" t="n">
-        <v>206</v>
-      </c>
-      <c r="C160" s="36" t="n"/>
-      <c r="D160" s="36" t="n">
-        <v>0.1847222808896685</v>
+      <c r="A160" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">      시대 ρ  YZ 0.773  vs  R² 0.127 / RSI 0.202</t>
+        </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   ⚠ **작고·어리고·매출 적은 회사가 더 변동적** 이라는 건 교과서적 사실이다. 이 표가 그걸 재확인했을 뿐, '무엇의 속성인가' 를 답하지는 못한다 (케인 2차 지적).</t>
+          <t xml:space="preserve">   **R²·RSI 는 정반대다** — ICC 가 0.03~0.05 이고, 60거래일이면 자기상관이 0 으로 떨어지며, 전이 대각이 정확히 무작위(20%)다. 206종목 전부가 양쪽을 오간다.</t>
         </is>
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   회전율(+0.775)이 가장 강한 것도 마찬가지다 — 거래량과 변동성은 정보 도착에 함께 반응하므로 설명이라기보다 재진술이다.</t>
-        </is>
-      </c>
+      <c r="A162" s="43" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="43" t="inlineStr">
         <is>
-          <t xml:space="preserve">   섹터가 이미 먹고 있는 분산 η²: log_mcap 0.516 · log_rev 0.560 · age_yrs 0.259 · log_turnover 0.602  → 섹터와 규모는 애초에 교란돼 있다(케인 1차 지적).</t>
+          <t xml:space="preserve">   ⇒ **12셀 표의 세 축은 성격이 같지 않다.**</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     R²·RSI 축은 진짜 **상태** 축이다 — 같은 종목이 날마다 다른 칸에 들어간다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     **YZ 축은 사실상 종목 그룹 축**이다 — YZ高 vs YZ低 비교는 같은 종목의 다른 상태를 비교하는 게 아니라 **대체로 다른 회사들을 비교**하는 것이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     그래서 YZ 로 갈린 두 집단 사이에 무엇이 달라 보이든, 그것은 **구성의 차이**일 수 있고 변동성의 효과라고 단정할 수 없다(주석 ⑦ 이 그 함정이었다).</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="43" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ **ICC 는 창 길이에 오염된다** ([E] 참조) — 단독으로 인용하지 말 것. 창에 견고한 증거는 비중첩 블록 상관과 시대 ρ 다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ **창을 바꿔도 이 결론은 안 바뀐다** — YZ 는 10일 창에서도 인접 블록 순위상관 0.761 이고, R² 는 어느 창에서도 0 이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ 이것은 '안정적이다' 까지다. **왜 안정적인지는 이 시트가 답하지 않는다.**</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ 다만 완전 고정은 아니다 — 177종목은 양쪽을 오갔고 종목내 σ 도 0.169 로 0 이 아니다. '고정' 이 아니라 '느리게 움직이는 서열' 이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="3" t="inlineStr">
+        <is>
+          <t>[참고] 어떤 회사가 변동성이 높나 — 답이 아니고, 결과도 예상 범위다</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   1차 지적 때 한 횡단면 분석. 우회의 기록으로 남긴다 — 종속변수는 종목별 YZ高 비율(0~1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="176" ht="30" customHeight="1">
+      <c r="A176" s="6" t="inlineStr">
+        <is>
+          <t>변수</t>
+        </is>
+      </c>
+      <c r="B176" s="6" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C176" s="6" t="inlineStr">
+        <is>
+          <t>ρ</t>
+        </is>
+      </c>
+      <c r="D176" s="6" t="inlineStr">
+        <is>
+          <t>η²</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t>회전율(로그)</t>
+        </is>
+      </c>
+      <c r="B177" s="8" t="n">
+        <v>206</v>
+      </c>
+      <c r="C177" s="77" t="n">
+        <v>0.77437103159247</v>
+      </c>
+      <c r="D177" s="10" t="n"/>
+    </row>
+    <row r="178">
+      <c r="A178" s="7" t="inlineStr">
+        <is>
+          <t>매출(로그)</t>
+        </is>
+      </c>
+      <c r="B178" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="C178" s="78" t="n">
+        <v>-0.6740647398141336</v>
+      </c>
+      <c r="D178" s="10" t="n"/>
+    </row>
+    <row r="179">
+      <c r="A179" s="7" t="inlineStr">
+        <is>
+          <t>영업이익(로그·흑자만)</t>
+        </is>
+      </c>
+      <c r="B179" s="8" t="n">
+        <v>168</v>
+      </c>
+      <c r="C179" s="78" t="n">
+        <v>-0.6034636327769355</v>
+      </c>
+      <c r="D179" s="10" t="n"/>
+    </row>
+    <row r="180">
+      <c r="A180" s="7" t="inlineStr">
+        <is>
+          <t>시총(로그)</t>
+        </is>
+      </c>
+      <c r="B180" s="8" t="n">
+        <v>206</v>
+      </c>
+      <c r="C180" s="78" t="n">
+        <v>-0.5016556327118529</v>
+      </c>
+      <c r="D180" s="10" t="n"/>
+    </row>
+    <row r="181">
+      <c r="A181" s="7" t="inlineStr">
+        <is>
+          <t>업력(년·우측절단)</t>
+        </is>
+      </c>
+      <c r="B181" s="8" t="n">
+        <v>204</v>
+      </c>
+      <c r="C181" s="78" t="n">
+        <v>-0.2536720850120763</v>
+      </c>
+      <c r="D181" s="10" t="n"/>
+    </row>
+    <row r="182">
+      <c r="A182" s="7" t="inlineStr">
+        <is>
+          <t>영업이익률</t>
+        </is>
+      </c>
+      <c r="B182" s="8" t="n">
+        <v>183</v>
+      </c>
+      <c r="C182" s="78" t="n">
+        <v>-0.1204109225228064</v>
+      </c>
+      <c r="D182" s="10" t="n"/>
+    </row>
+    <row r="183">
+      <c r="A183" s="17" t="inlineStr">
+        <is>
+          <t>주가 수준</t>
+        </is>
+      </c>
+      <c r="B183" s="18" t="n">
+        <v>206</v>
+      </c>
+      <c r="C183" s="85" t="n">
+        <v>-0.1167370177327752</v>
+      </c>
+      <c r="D183" s="20" t="n"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="25" t="inlineStr">
+        <is>
+          <t>섹터 (37개)</t>
+        </is>
+      </c>
+      <c r="B184" s="26" t="n">
+        <v>206</v>
+      </c>
+      <c r="C184" s="28" t="n"/>
+      <c r="D184" s="28" t="n">
+        <v>0.6130137375307277</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="33" t="inlineStr">
+        <is>
+          <t>테크 계열 여부</t>
+        </is>
+      </c>
+      <c r="B185" s="34" t="n">
+        <v>206</v>
+      </c>
+      <c r="C185" s="36" t="n"/>
+      <c r="D185" s="36" t="n">
+        <v>0.1849060370207659</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   ⚠ **작고·어리고·매출 적은 회사가 더 변동적** 이라는 건 교과서적 사실이다. 이 표가 그걸 재확인했을 뿐, '무엇의 속성인가' 를 답하지는 못한다 (케인 2차 지적).</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   회전율(+0.775)이 가장 강한 것도 마찬가지다 — 거래량과 변동성은 정보 도착에 함께 반응하므로 설명이라기보다 재진술이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   섹터가 이미 먹고 있는 분산 η²: log_mcap 0.516 · log_rev 0.560 · age_yrs 0.259 · log_turnover 0.602  → 섹터와 규모는 애초에 교란돼 있다(케인 1차 지적).</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="43" t="inlineStr">
         <is>
           <t xml:space="preserve">   규모 4변수 R² 0.684 → 섹터 더미 추가 0.829 (증분 +0.145, 순열 귀무 중앙 +0.062, p=0.0010) — 섹터와 규모는 서로를 대체하지 못한다.</t>
         </is>
